--- a/mistral_translate_work/split_by_prompt/excel/skill_description/lang_multi_text/lang_multi_text__skill_description__part_0024.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/skill_description/lang_multi_text/lang_multi_text__skill_description__part_0024.xlsx
@@ -574,7 +574,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>[Tấn Công] [HP] [Phòng Ngự] [Crit. DMG] [Energy Regen] [Fusion DMG Bonus]</t>
+          <t>[ATK] [HP] [Phòng Ngự] [Crit. DMG] [Hồi Năng Lượng] [Tăng Sát Thương Fusion]</t>
         </is>
       </c>
     </row>
@@ -639,7 +639,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Biến thành Fusion Warrior, chuyển sang trạng thái phòng thủ. Trong thời gian này, đòn tấn công của kẻ địch có thể kích hoạt phản đòn, nếu thành công sẽ gây Fusion DMG và giảm Cooldown chiêu của kỹ năng.</t>
+          <t>Biến hình thành Chiến Binh Fusion, chuyển sang trạng thái phòng thủ. Trong thời gian này, đòn tấn công của kẻ địch có thể kích hoạt phản đòn, nếu thành công sẽ gây Sát Thương Fusion và giảm thời gian hồi chiêu của kỹ năng.</t>
         </is>
       </c>
     </row>
@@ -704,7 +704,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Hiệu ứng kỹ năng</t>
+          <t>Hiệu ứng Kỹ năng</t>
         </is>
       </c>
     </row>
@@ -769,7 +769,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Tấn Công | HP | Phòng Ngự | Crit. Rate | Hồi Phục Năng Lượng | Fusion DMG Bonus</t>
+          <t>ATK | HP | Phòng Ngự | Crit. Rate | Hồi Phục Năng Lượng | Tăng Sát Thương Fusion</t>
         </is>
       </c>
     </row>
@@ -834,7 +834,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Summon Havoc Warrior tung cú móc trên, gây Havoc DMG và tung kẻ địch lên không.</t>
+          <t>Triệu hồi Havoc Warrior tung cú móc trên, gây DMG Havoc và tung kẻ địch lên không.</t>
         </is>
       </c>
     </row>
@@ -899,7 +899,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Hiệu ứng kỹ năng</t>
+          <t>Hiệu ứng Kỹ năng</t>
         </is>
       </c>
     </row>
@@ -964,7 +964,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Tấn Công | HP | Phòng Ngự | Crit. Rate | Hồi Phục Năng Lượng | Fusion DMG Bonus</t>
+          <t>ATK | HP | Phòng Ngự | Crit. Rate | Hồi Phục Năng Lượng | Tăng Sát Thương Fusion</t>
         </is>
       </c>
     </row>
@@ -1029,7 +1029,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Summon Snip Snap để kích nổ, gây Fusion DMG và tạo vùng cháy gây Fusion DMG.</t>
+          <t>Triệu hồi Snip Snap để kích nổ, gây Sát Thương Fusion và tạo vùng cháy gây Sát Thương Fusion.</t>
         </is>
       </c>
     </row>
@@ -1094,7 +1094,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Hiệu ứng kỹ năng</t>
+          <t>Hiệu ứng Kỹ năng</t>
         </is>
       </c>
     </row>
@@ -1159,7 +1159,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Tấn Công | HP | Phòng Ngự | Crit. Rate | Hồi Phục Năng Lượng | Spectro DMG Bonus</t>
+          <t>ATK | HP | Phòng Ngự | Crit. Rate | Hồi Phục Năng Lượng | Tăng Sát Thương Spectro</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Summon Zig Zag kích nổ, gây Spectro DMG và tạo ra khu vực trì trệ.</t>
+          <t>Triệu hồi Zig Zag kích nổ, gây Sát Thương Spectro và tạo ra khu vực trì trệ.</t>
         </is>
       </c>
     </row>
@@ -1289,7 +1289,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Hiệu ứng kỹ năng</t>
+          <t>Hiệu ứng Kỹ năng</t>
         </is>
       </c>
     </row>
@@ -1354,7 +1354,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Tấn Công | HP | Phòng Ngự | Crit. Rate | Hồi Phục Năng Lượng | Aero DMG Bonus</t>
+          <t>ATK | HP | Phòng Ngự | Crit. Rate | Hồi Phục Năng Lượng | Tăng Sát Thương Aero</t>
         </is>
       </c>
     </row>
@@ -1419,7 +1419,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Summon Whiff Whaff để kích nổ, gây Aero DMG và tạo vùng áp suất thấp, gây Aero DMG.</t>
+          <t>Triệu hồi Whiff Whaff để kích nổ, gây Sát Thương Aero và tạo vùng áp suất thấp, gây Sát Thương Aero.</t>
         </is>
       </c>
     </row>
@@ -1484,7 +1484,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Hiệu ứng kỹ năng</t>
+          <t>Hiệu ứng Kỹ năng</t>
         </is>
       </c>
     </row>
@@ -1549,7 +1549,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Tấn Công | HP | Phòng Ngự | Crit. Rate | Hồi Phục Năng Lượng | Fusion DMG Bonus</t>
+          <t>ATK | HP | Phòng Ngự | Crit. Rate | Hồi Phục Năng Lượng | Tăng Sát Thương Fusion</t>
         </is>
       </c>
     </row>
@@ -1614,7 +1614,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Summon và kích nổ, gây Havoc DMG, đồng thời tạo ra vùng năng lượng âm, gây Havoc DMG mỗi lượt. Nhân vật trong vùng này sẽ chịu một lượng sát thương nhỏ, nhưng đồng thời phục hồi Resonance Energy.</t>
+          <t>Triệu hồi và kích nổ, gây Sát Thương Havoc, đồng thời tạo ra vùng năng lượng âm, gây Sát Thương Havoc mỗi lượt. Nhân vật trong vùng này sẽ chịu một lượng DMG nhỏ, nhưng đồng thời phục hồi Resonance Energy.</t>
         </is>
       </c>
     </row>
@@ -1679,7 +1679,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Hiệu ứng kỹ năng</t>
+          <t>Hiệu ứng Kỹ năng</t>
         </is>
       </c>
     </row>
@@ -1744,7 +1744,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Tấn Công | HP | Phòng Ngự | Hồi Phục Năng Lượng | Glacio DMG Bonus</t>
+          <t>ATK | HP | Phòng Ngự | Hồi Phục Năng Lượng | Tăng Sát Thương Glacio</t>
         </is>
       </c>
     </row>
@@ -1809,7 +1809,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Summon Glacio Predator Dodgem lao băng, gây Glacio DMG trực tiếp, gây sát thương ở từng giai đoạn tích tụ năng lượng, và gây Glacio DMG khi phát nổ.</t>
+          <t>Triệu hồi Glacio Predator ném lao băng, gây DMG Glacio trực tiếp, gây DMG ở từng giai đoạn tích tụ năng lượng, và gây DMG Glacio khi phát nổ.</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>Hiệu ứng kỹ năng</t>
+          <t>Hiệu ứng Kỹ năng</t>
         </is>
       </c>
     </row>
@@ -1939,7 +1939,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>[Tấn Công] [HP] [Phòng Ngự] [Crit. DMG] [Energy Regen] [Aero DMG Bonus]</t>
+          <t>[ATK] [HP] [Phòng Ngự] [Crit. DMG] [Hồi Năng Lượng] [Tăng Sát Thương Aero]</t>
         </is>
       </c>
     </row>
@@ -2004,7 +2004,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Summon Kẻ Săn Mồi Gió để phóng phi tiêu, gây Sát Thương Gió.</t>
+          <t>Triệu hồi Kẻ Săn Mồi Gió để phóng phi tiêu, gây Sát Thương Gió.</t>
         </is>
       </c>
     </row>
@@ -2069,7 +2069,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>Hiệu ứng kỹ năng</t>
+          <t>Hiệu ứng Kỹ năng</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>Tấn Công | HP | Phòng Ngự | Healing Năng Lượng | Tăng Hiệu Suất Healing | Spectro DMG Bonus</t>
+          <t>ATK | HP | Phòng Ngự | Hồi Phục Năng Lượng | Tăng Hiệu Suất Hồi Phục | Tăng Sát Thương Spectro</t>
         </is>
       </c>
     </row>
@@ -2199,7 +2199,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>Summon Cánh Buồm, phục hồi HP cho bản thân.</t>
+          <t>Triệu hồi Cánh Buồm, phục hồi HP cho bản thân.</t>
         </is>
       </c>
     </row>
@@ -2264,7 +2264,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>Hiệu ứng kỹ năng</t>
+          <t>Hiệu ứng Kỹ năng</t>
         </is>
       </c>
     </row>
@@ -2329,7 +2329,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>[Tấn Công] [HP] [Phòng Ngự] [Crit. DMG] [Energy Regen] [Tăng Sát Thương Physical]</t>
+          <t>[ATK] [HP] [Phòng Ngự] [Crit. DMG] [Hồi Năng Lượng] [Tăng Sát Thương Vật Lý]</t>
         </is>
       </c>
     </row>
@@ -2394,7 +2394,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>Summon Sabyr Boar, lao tới tấn công gây Sát Thương vật lý.</t>
+          <t>Triệu hồi Lợn Rừng Sabyr, lao tới tấn công gây Sát Thương vật lý.</t>
         </is>
       </c>
     </row>
@@ -2459,7 +2459,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>Hiệu ứng kỹ năng</t>
+          <t>Hiệu ứng Kỹ năng</t>
         </is>
       </c>
     </row>
@@ -2524,7 +2524,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>Tấn Công | HP | Phòng Ngự | Hồi Phục Năng Lượng | Glacio DMG Bonus</t>
+          <t>ATK | HP | Phòng Ngự | Hồi Phục Năng Lượng | Tăng Sát Thương Glacio</t>
         </is>
       </c>
     </row>
@@ -2589,7 +2589,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>Summon Gulpuff phun 3 bong bóng về phía trước, kẻ địch trúng bong bóng sẽ chịu Glacio DMG và bị nâng lên, sau khi bong bóng vỡ sẽ chịu sát thương rơi.</t>
+          <t>Triệu hồi Gulpuff phun 3 bong bóng về phía trước, kẻ địch trúng bong bóng sẽ chịu DMG Glacio và bị nâng lên, sau khi bong bóng vỡ sẽ chịu DMG rơi.</t>
         </is>
       </c>
     </row>
@@ -2654,7 +2654,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>Hiệu ứng kỹ năng</t>
+          <t>Hiệu ứng Kỹ năng</t>
         </is>
       </c>
     </row>
@@ -2719,7 +2719,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>[Tấn Công] [HP] [Phòng Ngự] [Crit. DMG] [Energy Regen] [Fusion DMG Bonus]</t>
+          <t>[ATK] [HP] [Phòng Ngự] [Crit. DMG] [Hồi Năng Lượng] [Tăng Sát Thương Fusion]</t>
         </is>
       </c>
     </row>
@@ -2784,7 +2784,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>Hiệu ứng kỹ năng</t>
+          <t>Hiệu ứng Kỹ năng</t>
         </is>
       </c>
     </row>
@@ -2849,7 +2849,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>[Tấn Công] [HP] [Phòng Ngự] [Crit. DMG] [Energy Regen] [Fusion DMG Bonus]</t>
+          <t>[ATK] [HP] [Phòng Ngự] [Crit. DMG] [Hồi Năng Lượng] [Tăng Sát Thương Fusion]</t>
         </is>
       </c>
     </row>
@@ -2914,7 +2914,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>Summon Geohide Saurian vị thành niên, đập tan kẻ địch phía trước, gây Fusion DMG.</t>
+          <t>Triệu hồi Geohide Saurian vị thành niên, đập tan kẻ địch phía trước, gây Sát Thương Fusion.</t>
         </is>
       </c>
     </row>
@@ -2979,7 +2979,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>Hiệu ứng kỹ năng</t>
+          <t>Hiệu ứng Kỹ năng</t>
         </is>
       </c>
     </row>
@@ -3044,7 +3044,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>[Tấn Công] [HP] [Phòng Ngự] [Crit. DMG] [Energy Regen] [Fusion DMG Bonus]</t>
+          <t>[ATK] [HP] [Phòng Ngự] [Crit. DMG] [Hồi Năng Lượng] [Tăng Sát Thương Fusion]</t>
         </is>
       </c>
     </row>
@@ -3109,7 +3109,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>Summon Roseshroom vị thành niên bắn ra các quả cầu năng lượng, gây Havoc DMG.</t>
+          <t>Triệu hồi Roseshroom vị thành niên bắn ra các quả cầu năng lượng, gây Sát Thương Havoc.</t>
         </is>
       </c>
     </row>
@@ -3174,7 +3174,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>Hiệu ứng kỹ năng</t>
+          <t>Hiệu ứng Kỹ năng</t>
         </is>
       </c>
     </row>
@@ -3239,7 +3239,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>[Tấn Công] [HP] [Phòng Ngự] [Crit. DMG] [Energy Regen] [Fusion DMG Bonus]</t>
+          <t>[ATK] [HP] [Phòng Ngự] [Crit. DMG] [Hồi Năng Lượng] [Tăng Sát Thương Fusion]</t>
         </is>
       </c>
     </row>
@@ -3304,7 +3304,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>Summon Fusion Dreadmane con để tung cú Cắn, gây Fusion DMG.</t>
+          <t>Triệu hồi Fusion Dreadmane con để tung cú Cắn, gây DMG Fusion.</t>
         </is>
       </c>
     </row>
@@ -3369,7 +3369,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>Hiệu ứng kỹ năng</t>
+          <t>Hiệu ứng Kỹ năng</t>
         </is>
       </c>
     </row>
@@ -3434,7 +3434,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>Tấn Công | HP | Phòng Ngự | Hồi Phục Năng Lượng | Glacio DMG Bonus</t>
+          <t>ATK | HP | Phòng Ngự | Hồi Phục Năng Lượng | Tăng Sát Thương Glacio</t>
         </is>
       </c>
     </row>
@@ -3499,7 +3499,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>Biến thành Hoartoise, giảm sát thương nhận vào trong trạng thái biến hình.</t>
+          <t>Biến hình thành Hoartoise, giảm sát thương nhận vào trong trạng thái biến hình.</t>
         </is>
       </c>
     </row>
@@ -3564,7 +3564,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>Hiệu ứng kỹ năng</t>
+          <t>Hiệu ứng Kỹ năng</t>
         </is>
       </c>
     </row>
@@ -3629,7 +3629,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>[Tấn Công] [HP] [Phòng Ngự] [Crit. DMG] [Energy Regen] [Electro DMG Bonus]</t>
+          <t>[ATK] [HP] [Phòng Ngự] [Crit. DMG] [Hồi Năng Lượng] [Tăng Sát Thương Electro]</t>
         </is>
       </c>
     </row>
@@ -3694,7 +3694,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>Biến thành Violet-Feathered Heron để lao về phía trước theo đường zigzag, gây Electro DMG.</t>
+          <t>Biến thành Violet-Feathered Heron để lao về phía trước theo đường zigzag, gây DMG Electro.</t>
         </is>
       </c>
     </row>
@@ -3759,7 +3759,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>Hiệu ứng kỹ năng</t>
+          <t>Hiệu ứng Kỹ năng</t>
         </is>
       </c>
     </row>
@@ -3824,7 +3824,7 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>[Tấn Công] [HP] [Phòng Ngự] [Crit. DMG] [Energy Regen] [Aero DMG Bonus]</t>
+          <t>[ATK] [HP] [Phòng Ngự] [Crit. DMG] [Hồi Năng Lượng] [Tăng Sát Thương Aero]</t>
         </is>
       </c>
     </row>
@@ -3889,7 +3889,7 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>Biến thành Cyan-Feathered Heron và lao vào xoay tròn, mỗi lần gây Aero DMG, tối đa 3 lần.</t>
+          <t>Biến hình thành Cyan-Feathered Heron và lao vào xoay tròn, mỗi lần gây Sát Thương Aero, tối đa 3 lần.</t>
         </is>
       </c>
     </row>
@@ -3954,7 +3954,7 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>Hiệu ứng kỹ năng</t>
+          <t>Hiệu ứng Kỹ năng</t>
         </is>
       </c>
     </row>
@@ -4019,7 +4019,7 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>Tấn Công | HP | Phòng Ngự | Healing Năng Lượng | Tăng Hiệu Suất Healing | Fusion DMG Bonus</t>
+          <t>ATK | HP | Phòng Ngự | Hồi Phục Năng Lượng | Tăng Hiệu Suất Hồi Phục | Tăng Sát Thương Fusion</t>
         </is>
       </c>
     </row>
@@ -4084,7 +4084,7 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>Summon một Fusion Prism tồn tại lâu dài, liên tục hồi phục Resonance Energy cho các Resonator thuộc hệ Fusion trong phạm vi.</t>
+          <t>Triệu hồi một Lăng Kính Fusion tồn tại lâu dài, liên tục hồi phục Resonance Energy cho các Cộng Hưởng Giả thuộc hệ Fusion trong phạm vi.</t>
         </is>
       </c>
     </row>
@@ -4149,7 +4149,7 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>Hiệu ứng kỹ năng</t>
+          <t>Hiệu ứng Kỹ năng</t>
         </is>
       </c>
     </row>
@@ -4214,7 +4214,7 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>Tấn Công | HP | Phòng Ngự | Healing Năng Lượng | Tăng Hiệu Suất Healing | Glacio DMG Bonus</t>
+          <t>ATK | HP | Phòng Ngự | Hồi Phục Năng Lượng | Tăng Hiệu Suất Hồi Phục | Tăng Sát Thương Glacio</t>
         </is>
       </c>
     </row>
@@ -4279,7 +4279,7 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>Summon một Glacio Prism tồn tại lâu dài, liên tục hồi phục Resonance Energy cho các Resonator thuộc hệ Glacio trong phạm vi.</t>
+          <t>Triệu hồi một Lăng Kính Glacio tồn tại lâu dài, liên tục hồi phục Resonance Energy cho các Cộng Hưởng Giả thuộc hệ Glacio trong phạm vi.</t>
         </is>
       </c>
     </row>
@@ -4344,7 +4344,7 @@
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>Hiệu ứng kỹ năng</t>
+          <t>Hiệu ứng Kỹ năng</t>
         </is>
       </c>
     </row>
@@ -4409,7 +4409,7 @@
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>Tấn Công | HP | Phòng Ngự | Healing Năng Lượng | Tăng Hiệu Suất Healing | Spectro DMG Bonus</t>
+          <t>ATK | HP | Phòng Ngự | Hồi Phục Năng Lượng | Tăng Hiệu Suất Hồi Phục | Tăng Sát Thương Spectro</t>
         </is>
       </c>
     </row>
@@ -4474,7 +4474,7 @@
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>Summon Prism Spectro bền vững, liên tục hồi phục Resonance Energy cho các Resonator thuộc hệ Spectro trong phạm vi.</t>
+          <t>Triệu hồi Lăng Kính Spectro bền vững, liên tục hồi phục Resonance Energy cho các Cộng Hưởng Giả thuộc hệ Spectro trong phạm vi.</t>
         </is>
       </c>
     </row>
@@ -4539,7 +4539,7 @@
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>Hiệu ứng kỹ năng</t>
+          <t>Hiệu ứng Kỹ năng</t>
         </is>
       </c>
     </row>
@@ -4604,7 +4604,7 @@
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>Tấn Công | HP | Phòng Ngự | Healing Năng Lượng | Tăng Hiệu Suất Healing | Spectro DMG Bonus</t>
+          <t>ATK | HP | Phòng Ngự | Hồi Phục Năng Lượng | Tăng Hiệu Suất Hồi Phục | Tăng Sát Thương Spectro</t>
         </is>
       </c>
     </row>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>Summon một Prism Havoc tồn tại lâu dài, liên tục hồi phục Resonance Energy cho các Resonator thuộc hệ Havoc trong phạm vi.</t>
+          <t>Triệu hồi một Lăng Kính Havoc tồn tại lâu dài, liên tục hồi phục Resonance Energy cho các Cộng Hưởng Giả thuộc hệ Havoc trong phạm vi.</t>
         </is>
       </c>
     </row>
@@ -4734,7 +4734,7 @@
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>Hiệu ứng kỹ năng</t>
+          <t>Hiệu ứng Kỹ năng</t>
         </is>
       </c>
     </row>
@@ -4799,7 +4799,7 @@
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>Tấn Công | HP | Phòng Ngự | Crit. Rate | Hồi Phục Năng Lượng | Tăng Sát Thương Physical</t>
+          <t>ATK | HP | Phòng Ngự | Crit. Rate | Hồi Phục Năng Lượng | Tăng Sát Thương Vật Lý</t>
         </is>
       </c>
     </row>
@@ -4864,7 +4864,7 @@
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>Biến thành Stonewall Bracer và lao về phía trước, gây sát thương vật lý mỗi lần di chuyển, giữ kỹ năng để kéo dài thời gian lao đi.</t>
+          <t>Biến hình thành Stonewall Bracer và lao về phía trước, gây DMG vật lý mỗi lần di chuyển, giữ kỹ năng để kéo dài thời gian lao đi.</t>
         </is>
       </c>
     </row>
@@ -4929,7 +4929,7 @@
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>Hiệu ứng kỹ năng</t>
+          <t>Hiệu ứng Kỹ năng</t>
         </is>
       </c>
     </row>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>Tấn Công | HP | Phòng Ngự | Crit. Rate | Hồi Phục Năng Lượng | Electro DMG Bonus</t>
+          <t>ATK | HP | Phòng Ngự | Crit. Rate | Hồi Phục Năng Lượng | Tăng Sát Thương Electro</t>
         </is>
       </c>
     </row>
@@ -5059,7 +5059,7 @@
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>Biến thành Flautist, phóng ra tia sét xuyên thấu gây Electro DMG, sau đó thả một tia sét xuống, mỗi tia sét gây Electro DMG.</t>
+          <t>Biến hình thành Flautist, phóng ra tia sét xuyên thấu gây Sát Thương Electro, sau đó thả một tia sét xuống, mỗi tia sét gây Sát Thương Electro.</t>
         </is>
       </c>
     </row>
@@ -5124,7 +5124,7 @@
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>Hiệu ứng kỹ năng</t>
+          <t>Hiệu ứng Kỹ năng</t>
         </is>
       </c>
     </row>
@@ -5189,7 +5189,7 @@
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>Tấn Công | HP | Phòng Ngự | Crit. Rate | Hồi Phục Năng Lượng | Fusion DMG Bonus</t>
+          <t>ATK | HP | Phòng Ngự | Crit. Rate | Hồi Phục Năng Lượng | Tăng Sát Thương Fusion</t>
         </is>
       </c>
     </row>
@@ -5254,7 +5254,7 @@
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>Biến thành Tambourinist, triệu hồi các quả cầu năng lượng bao vây bản thân, mỗi quả cầu sẽ gây Havoc DMG khi chạm vào kẻ địch.</t>
+          <t>Biến hình thành Tambourinist, triệu hồi các quả cầu năng lượng bao vây bản thân, mỗi quả cầu sẽ gây Sát Thương Havoc khi chạm vào kẻ địch.</t>
         </is>
       </c>
     </row>
@@ -5319,7 +5319,7 @@
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>Hiệu ứng kỹ năng</t>
+          <t>Hiệu ứng Kỹ năng</t>
         </is>
       </c>
     </row>
@@ -5384,7 +5384,7 @@
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>Tấn Công | HP | Phòng Ngự | Crit. Rate | Hồi Phục Năng Lượng | Spectro DMG Bonus</t>
+          <t>ATK | HP | Phòng Ngự | Crit. Rate | Hồi Phục Năng Lượng | Tăng Sát Thương Spectro</t>
         </is>
       </c>
     </row>
@@ -5449,7 +5449,7 @@
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>Biến thành người bảo vệ đá, thực hiện hai cú đập mạnh gây Spectro DMG, mỗi lần đập tạo ra sóng xung kích cũng gây Spectro DMG.</t>
+          <t>Biến hình thành người bảo vệ đá, thực hiện hai cú đập mạnh gây Sát Thương Spectro, mỗi lần đập tạo ra sóng xung kích cũng gây Sát Thương Spectro.</t>
         </is>
       </c>
     </row>
@@ -5514,7 +5514,7 @@
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>Hiệu ứng kỹ năng</t>
+          <t>Hiệu ứng Kỹ năng</t>
         </is>
       </c>
     </row>
@@ -5579,7 +5579,7 @@
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>Tấn Công | HP | Phòng Ngự | Crit. Rate | Hồi Phục Năng Lượng | Fusion DMG Bonus</t>
+          <t>ATK | HP | Phòng Ngự | Crit. Rate | Hồi Phục Năng Lượng | Tăng Sát Thương Fusion</t>
         </is>
       </c>
     </row>
@@ -5644,7 +5644,7 @@
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>Biến thành Chasm Guardian, nhảy về phía trước và đập mạnh xuống đất, va chạm khi nhảy gây Havoc DMG, cú đập gây Havoc DMG.</t>
+          <t>Biến hình thành Chasm Guardian, nhảy về phía trước và đập mạnh xuống đất, va chạm khi nhảy gây Sát Thương Havoc, cú đập gây Sát Thương Havoc.</t>
         </is>
       </c>
     </row>
@@ -5709,7 +5709,7 @@
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>Hiệu ứng kỹ năng</t>
+          <t>Hiệu ứng Kỹ năng</t>
         </is>
       </c>
     </row>
@@ -5774,7 +5774,7 @@
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>[Tấn Công] [HP] [Phòng Ngự] [Crit. DMG] [Energy Regen] [Fusion DMG Bonus]</t>
+          <t>[ATK] [HP] [Phòng Ngự] [Crit. DMG] [Hồi Năng Lượng] [Tăng Sát Thương Fusion]</t>
         </is>
       </c>
     </row>
@@ -5839,7 +5839,7 @@
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>Summon Geohide Saurian trưởng thành phun hơi, mỗi lần gây Fusion DMG lên kẻ địch.</t>
+          <t>Triệu hồi Geohide Saurian trưởng thành phun hơi, mỗi lần gây Sát Thương Fusion lên kẻ địch.</t>
         </is>
       </c>
     </row>
@@ -5904,7 +5904,7 @@
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>Hiệu ứng kỹ năng</t>
+          <t>Hiệu ứng Kỹ năng</t>
         </is>
       </c>
     </row>
@@ -5969,7 +5969,7 @@
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>[Tấn Công] [HP] [Phòng Ngự] [Crit. DMG] [Energy Regen] [Fusion DMG Bonus]</t>
+          <t>[ATK] [HP] [Phòng Ngự] [Crit. DMG] [Hồi Năng Lượng] [Tăng Sát Thương Fusion]</t>
         </is>
       </c>
     </row>
@@ -6034,7 +6034,7 @@
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>Summon một Roseshroom trưởng thành phóng tia, gây Havoc DMG.</t>
+          <t>Triệu hồi một Roseshroom trưởng thành phóng tia, gây Sát Thương Havoc.</t>
         </is>
       </c>
     </row>
@@ -6099,7 +6099,7 @@
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>Hiệu ứng kỹ năng</t>
+          <t>Hiệu ứng Kỹ năng</t>
         </is>
       </c>
     </row>
@@ -6164,7 +6164,7 @@
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>[Tấn Công] [HP] [Phòng Ngự] [Crit. DMG] [Energy Regen] [Fusion DMG Bonus]</t>
+          <t>[ATK] [HP] [Phòng Ngự] [Crit. DMG] [Hồi Năng Lượng] [Tăng Sát Thương Fusion]</t>
         </is>
       </c>
     </row>
@@ -6229,7 +6229,7 @@
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>Biến thành Havoc Dreadmane, tung ra một cú quất đuôi gây Havoc DMG, đồng thời tạo ra một lưỡi kiếm khí phía trước gây Havoc DMG.</t>
+          <t>Biến hình thành Havoc Dreadmane, tung ra một cú quất đuôi gây Sát Thương Havoc, đồng thời tạo ra một lưỡi kiếm khí phía trước gây Sát Thương Havoc.</t>
         </is>
       </c>
     </row>
@@ -6294,7 +6294,7 @@
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>Hiệu ứng kỹ năng</t>
+          <t>Hiệu ứng Kỹ năng</t>
         </is>
       </c>
     </row>
@@ -6359,7 +6359,7 @@
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>[Tấn Công] [HP] [Phòng Ngự] [Crit. DMG] [Energy Regen] [Tăng Sát Thương Physical]</t>
+          <t>[ATK] [HP] [Phòng Ngự] [Crit. DMG] [Hồi Năng Lượng] [Tăng Sát Thương Vật Lý]</t>
         </is>
       </c>
     </row>
@@ -6424,7 +6424,7 @@
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>Biến thành Spearback, lao về phía trước, gây sát thương cho kẻ địch trên đường đi, mỗi lần va chạm gây Sát Thương Vật Lý.</t>
+          <t>Biến hình thành Spearback, lao về phía trước, gây DMG cho kẻ địch trên đường đi, mỗi lần va chạm gây Sát Thương Vật Lý.</t>
         </is>
       </c>
     </row>
@@ -6489,7 +6489,7 @@
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>Hiệu ứng kỹ năng</t>
+          <t>Hiệu ứng Kỹ năng</t>
         </is>
       </c>
     </row>
@@ -6554,7 +6554,7 @@
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>Tấn Công | HP | Phòng Ngự | Crit. Rate | Crit. DMG | Electro DMG Bonus</t>
+          <t>ATK | HP | Phòng Ngự | Crit. Rate | Crit. DMG | Tăng Sát Thương Electro</t>
         </is>
       </c>
     </row>
@@ -6619,7 +6619,7 @@
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>Biến thành Thundering Mephis, lao về phía trước, mỗi đoạn gây Electro DMG, rồi tung đòn cuối cùng gây Electro DMG, sét giáng xuống gây Electro DMG.</t>
+          <t>Biến thành Thundering Mephis, lao về phía trước, mỗi đoạn gây DMG Electro, rồi tung đòn cuối cùng gây DMG Electro, sét giáng xuống gây DMG Electro.</t>
         </is>
       </c>
     </row>
@@ -6684,7 +6684,7 @@
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>Hiệu ứng kỹ năng</t>
+          <t>Hiệu ứng Kỹ năng</t>
         </is>
       </c>
     </row>
@@ -6749,7 +6749,7 @@
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>Tấn Công | HP | Phòng Ngự | Crit. Rate | Healing Năng Lượng | Tăng Hiệu Suất Healing | Glacio DMG Bonus</t>
+          <t>ATK | HP | Phòng Ngự | Crit. Rate | Hồi Phục Năng Lượng | Tăng Hiệu Suất Hồi Phục | Tăng Sát Thương Glacio</t>
         </is>
       </c>
     </row>
@@ -6814,7 +6814,7 @@
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>Summon sự bảo hộ của Bell-Borne Geochelone, hất văng kẻ địch xung quanh và gây Glacio DMG. Trong thời gian hiệu ứng bảo hộ còn tác dụng, bạn bất tử, và các Resonator khác trong đội có thể kế thừa hiệu ứng này.</t>
+          <t>Triệu hồi sự bảo hộ của Bell-Borne Geochelone, hất văng kẻ địch xung quanh và gây Sát Thương Glacio. Trong thời gian hiệu ứng bảo hộ còn tác dụng, bạn bất tử, và các Cộng Hưởng Giả khác trong đội có thể kế thừa hiệu ứng này.</t>
         </is>
       </c>
     </row>
@@ -6879,7 +6879,7 @@
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>Hiệu ứng kỹ năng</t>
+          <t>Hiệu ứng Kỹ năng</t>
         </is>
       </c>
     </row>
@@ -6944,7 +6944,7 @@
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>[Tấn Công] [HP] [Phòng Ngự] [Crit. DMG] [Energy Regen] [Fusion DMG Bonus]</t>
+          <t>[ATK] [HP] [Phòng Ngự] [Crit. DMG] [Hồi Năng Lượng] [Tăng Sát Thương Fusion]</t>
         </is>
       </c>
     </row>
@@ -7009,7 +7009,7 @@
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>Biến thành Inferno Rider và thực hiện một nhát chém gây Fusion DMG. Giữ để bổ sung thêm một nhát chém nữa và kích hoạt vụ nổ, mỗi đòn tấn công đều gây Fusion DMG.</t>
+          <t>Biến hình thành Kỵ Sĩ Hỏa Ngục và thực hiện một nhát chém gây Sát Thương Fusion. Giữ để bổ sung thêm một nhát chém nữa và kích hoạt vụ nổ, mỗi đòn tấn công đều gây Sát Thương Fusion.</t>
         </is>
       </c>
     </row>
@@ -7074,7 +7074,7 @@
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>Hiệu ứng kỹ năng</t>
+          <t>Hiệu ứng Kỹ năng</t>
         </is>
       </c>
     </row>
@@ -7139,7 +7139,7 @@
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>Tấn Công | HP | Phòng Ngự | Crit. Rate | Hồi Phục Năng Lượng | Aero DMG Bonus</t>
+          <t>ATK | HP | Phòng Ngự | Crit. Rate | Hồi Phục Năng Lượng | Tăng Sát Thương Aero</t>
         </is>
       </c>
     </row>
@@ -7204,7 +7204,7 @@
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>Biến thành Hoochief non trẻ và tung đòn tấn công bằng vuốt về phía trước gây Aero DMG.</t>
+          <t>Biến hình thành Hoochief non trẻ và tung đòn tấn công bằng vuốt về phía trước gây Sát Thương Aero.</t>
         </is>
       </c>
     </row>
@@ -7269,7 +7269,7 @@
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>Hiệu ứng kỹ năng</t>
+          <t>Hiệu ứng Kỹ năng</t>
         </is>
       </c>
     </row>
@@ -7334,7 +7334,7 @@
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>Tấn Công | HP | Phòng Ngự | Crit. Rate | Crit. DMG | Electro DMG Bonus</t>
+          <t>ATK | HP | Phòng Ngự | Crit. Rate | Crit. DMG | Tăng Sát Thương Electro</t>
         </is>
       </c>
     </row>
@@ -7399,7 +7399,7 @@
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>Biến thành Thundering Mephis và tung đòn xuyên phá. Nhấn liên tục để gây Electro DMG theo từng đoạn. Thả ra để tung đòn cuối cùng gây Electro DMG. Đòn sét giáng xuống gây Electro DMG.</t>
+          <t>Biến thành Thundering Mephis và tung đòn xuyên phá. Nhấn liên tục để gây DMG Electro theo từng đoạn. Thả ra để tung đòn cuối cùng gây DMG Electro. Đòn sét giáng xuống gây DMG Electro.</t>
         </is>
       </c>
     </row>
@@ -7464,7 +7464,7 @@
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>Hiệu ứng kỹ năng</t>
+          <t>Hiệu ứng Kỹ năng</t>
         </is>
       </c>
     </row>
@@ -7529,7 +7529,7 @@
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>Tấn Công | HP | Phòng Ngự | Crit. Rate | Hồi Phục Năng Lượng | Aero DMG Bonus</t>
+          <t>ATK | HP | Phòng Ngự | Crit. Rate | Hồi Phục Năng Lượng | Tăng Sát Thương Aero</t>
         </is>
       </c>
     </row>
@@ -7594,7 +7594,7 @@
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>Biến thành Hoochief trưởng thành và tung đòn tấn công bằng lòng bàn tay gây Aero DMG.</t>
+          <t>Biến hình thành Hoochief trưởng thành và tung đòn tấn công bằng lòng bàn tay gây Sát Thương Aero.</t>
         </is>
       </c>
     </row>
@@ -7659,7 +7659,7 @@
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>Hiệu ứng kỹ năng</t>
+          <t>Hiệu ứng Kỹ năng</t>
         </is>
       </c>
     </row>
@@ -7724,7 +7724,7 @@
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>[Tấn Công] [HP] [Phòng Ngự] [Crit. DMG] [Energy Regen] [Tăng Sát Thương Physical]</t>
+          <t>[ATK] [HP] [Phòng Ngự] [Crit. DMG] [Hồi Năng Lượng] [Tăng Sát Thương Vật Lý]</t>
         </is>
       </c>
     </row>
@@ -7789,7 +7789,7 @@
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>Summon Vuốt Kim Cương để phun nọc độc, gây Sát Thương Vật Lý.</t>
+          <t>Triệu hồi Vuốt Kim Cương để phun nọc độc, gây Sát Thương Vật Lý.</t>
         </is>
       </c>
     </row>
@@ -7854,7 +7854,7 @@
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>Hiệu ứng kỹ năng</t>
+          <t>Hiệu ứng Kỹ năng</t>
         </is>
       </c>
     </row>
@@ -7919,7 +7919,7 @@
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>Tấn Công | HP | Phòng Ngự | Crit. Rate | Crit. DMG | Electro DMG Bonus</t>
+          <t>ATK | HP | Phòng Ngự | Crit. Rate | Crit. DMG | Tăng Sát Thương Electro</t>
         </is>
       </c>
     </row>
@@ -7984,7 +7984,7 @@
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t>Biến thành bản sao Crownless và tung ra một nhát chém mạnh gây Havoc DMG.</t>
+          <t>Biến hình thành bản sao Crownless và tung ra một nhát chém mạnh gây Sát Thương Havoc.</t>
         </is>
       </c>
     </row>
@@ -8049,7 +8049,7 @@
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t>Hiệu ứng kỹ năng</t>
+          <t>Hiệu ứng Kỹ năng</t>
         </is>
       </c>
     </row>
@@ -8114,7 +8114,7 @@
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>[Tấn Công] [HP] [Phòng Ngự] [Crit. DMG] [Crit. Rate] [Aero DMG Bonus]</t>
+          <t>[ATK] [HP] [Phòng Ngự] [Crit. DMG] [Crit. Rate] [Tăng Sát Thương Aero]</t>
         </is>
       </c>
     </row>
@@ -8179,7 +8179,7 @@
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>Biến thành Feilian Beringal và tung đòn tấn công bằng gậy gây Aero DMG.</t>
+          <t>Biến hình thành Feilian Beringal và tung đòn tấn công bằng gậy gây Sát Thương Aero.</t>
         </is>
       </c>
     </row>
@@ -8244,7 +8244,7 @@
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>Hiệu ứng kỹ năng</t>
+          <t>Hiệu ứng Kỹ năng</t>
         </is>
       </c>
     </row>
@@ -8309,7 +8309,7 @@
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>[Tấn Công] [HP] [Phòng Ngự] [Crit. DMG] [Crit. Rate] [Glacio DMG Bonus]</t>
+          <t>[ATK] [HP] [Phòng Ngự] [Crit. DMG] [Crit. Rate] [Tăng Sát Thương Glacio]</t>
         </is>
       </c>
     </row>
@@ -8374,7 +8374,7 @@
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t>Biến thành Lampylumen Myriad và lao về phía trước tạo ra một cú sốc đóng băng. Cú lao gây Sát Thương Băng. Cú sốc đóng băng gây Sát Thương Băng và đóng băng tất cả kẻ địch trong phạm vi.</t>
+          <t>Biến hình thành Lampylumen Myriad và lao về phía trước tạo ra một cú sốc đóng băng. Cú lao gây Sát Thương Băng. Cú sốc đóng băng gây Sát Thương Băng và đóng băng tất cả kẻ địch trong phạm vi.</t>
         </is>
       </c>
     </row>
@@ -8439,7 +8439,7 @@
       </c>
       <c r="M123" t="inlineStr">
         <is>
-          <t>Hiệu ứng kỹ năng</t>
+          <t>Hiệu ứng Kỹ năng</t>
         </is>
       </c>
     </row>
@@ -8504,7 +8504,7 @@
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t>[Tấn Công] [HP] [Phòng Ngự] [Crit. DMG] [Crit. Rate] [Spectro DMG Bonus]</t>
+          <t>[ATK] [HP] [Phòng Ngự] [Crit. DMG] [Crit. Rate] [Tăng Sát Thương Spectro]</t>
         </is>
       </c>
     </row>
@@ -8569,7 +8569,7 @@
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t>Biến thành Mourning Aix, tích năng và phóng một tia tấn công gây Sát Thương Dị Giới.</t>
+          <t>Biến hình thành Mourning Aix, tích năng và phóng một tia tấn công gây Sát Thương Dị Giới.</t>
         </is>
       </c>
     </row>
@@ -8634,7 +8634,7 @@
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t>Hiệu ứng kỹ năng</t>
+          <t>Hiệu ứng Kỹ năng</t>
         </is>
       </c>
     </row>
@@ -8699,7 +8699,7 @@
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t>Tấn Công | HP | Phòng Ngự | Crit. Rate | Hồi Phục Năng Lượng | Aero DMG Bonus</t>
+          <t>ATK | HP | Phòng Ngự | Crit. Rate | Hồi Phục Năng Lượng | Tăng Sát Thương Aero</t>
         </is>
       </c>
     </row>
@@ -8764,7 +8764,7 @@
       </c>
       <c r="M128" t="inlineStr">
         <is>
-          <t>Summon một Carapace lao vào kẻ địch, gây Aero DMG. Sau khi va chạm, thực hiện một nhát chém tiếp theo, gây Aero DMG.</t>
+          <t>Triệu hồi một Carapace lao vào kẻ địch, gây Sát Thương Aero. Sau khi va chạm, thực hiện một nhát chém tiếp theo, gây Sát Thương Aero.</t>
         </is>
       </c>
     </row>
@@ -8829,7 +8829,7 @@
       </c>
       <c r="M129" t="inlineStr">
         <is>
-          <t>Hiệu ứng kỹ năng</t>
+          <t>Hiệu ứng Kỹ năng</t>
         </is>
       </c>
     </row>
@@ -8894,7 +8894,7 @@
       </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t>Tấn Công | HP | Phòng Ngự | Crit. Rate | Hồi Phục Năng Lượng | Aero DMG Bonus</t>
+          <t>ATK | HP | Phòng Ngự | Crit. Rate | Hồi Phục Năng Lượng | Tăng Sát Thương Aero</t>
         </is>
       </c>
     </row>
@@ -8959,7 +8959,7 @@
       </c>
       <c r="M131" t="inlineStr">
         <is>
-          <t>Summon một Chirpuff phóng về phía trước, gây Aero DMG.</t>
+          <t>Triệu hồi một Chirpuff phóng về phía trước, gây DMG Aero.</t>
         </is>
       </c>
     </row>
@@ -9024,7 +9024,7 @@
       </c>
       <c r="M132" t="inlineStr">
         <is>
-          <t>Hiệu ứng kỹ năng</t>
+          <t>Hiệu ứng Kỹ năng</t>
         </is>
       </c>
     </row>
@@ -9222,8 +9222,8 @@
       </c>
       <c r="M135" t="inlineStr">
         <is>
-          <t>Augusta mời bạn cùng tham gia cuộc săn. Nhưng khi giao chiến với thực thể Hắc Triều, "False Sovereign", một thế lực vô hình đã can thiệp, khiến nỗ lực thất bại.
-Để ngăn Hắc Triều lan rộng, bạn truy đuổi False Sovereign đến Murmurstown. Tại đó, bạn và Augusta chiến đấu bên nhau và hạ gục hắn. Hắc Triều dần lắng xuống, và bạn thu hồi được Di Vật của Imperator. Nhưng ngay khi tận hưởng chiến thắng, Cristoforo đã âm thầm lên kế hoạch cho bước đi tiếp theo…</t>
+          <t>Augusta mời bạn cùng tham gia cuộc săn. Nhưng khi giao chiến với thực thể Hắc Triều, "Kẻ Giả Vương", một thế lực vô hình đã can thiệp, khiến nỗ lực thất bại.
+Để ngăn Hắc Triều lan rộng, bạn truy đuổi Kẻ Giả Vương đến Murmurstown. Tại đó, bạn và Augusta chiến đấu bên nhau và hạ gục hắn. Hắc Triều dần lắng xuống, và bạn thu hồi được Di Vật của Imperator. Nhưng ngay khi tận hưởng chiến thắng, Cristoforo đã âm thầm lên kế hoạch cho bước đi tiếp theo…</t>
         </is>
       </c>
     </row>
@@ -9354,7 +9354,7 @@
       </c>
       <c r="M137" t="inlineStr">
         <is>
-          <t>Sau khi New Solar Celebration kết thúc, Lucilla tiết lộ rằng gốc rễ của bất thường ở Dark Side vẫn chưa được giải quyết. Trong quá trình điều tra, cô phát hiện cái bẫy do Fractsidus giăng ra nhắm vào Resonators thuộc hệ nhớ. Quyết tâm nhử con thỏ ra, Lucilla tình nguyện làm mồi nhử, nhưng điều đó đồng nghĩa với việc phải đối mặt với những điểm yếu của chính mình.
+          <t>Sau khi Lễ Hội Mặt Trời Mới kết thúc, Lucilla tiết lộ rằng gốc rễ của bất thường ở Dark Side vẫn chưa được giải quyết. Trong quá trình điều tra, cô phát hiện cái bẫy do Fractsidus giăng ra nhắm vào các Resonator thuộc hệ nhớ. Quyết tâm nhử con thỏ ra, Lucilla tình nguyện làm mồi nhử, nhưng điều đó đồng nghĩa với việc phải đối mặt với những điểm yếu của chính mình.
 Tuy nhiên, Lucilla đã học cách đối diện với quá khứ một cách thẳng thắn từ lâu. Cô phá vỡ ảo ảnh, và với sự trợ giúp của ngươi, bắt được con thỏ. Nhờ vậy, gốc rễ của bất thường ở Dark Side cuối cùng cũng bị tiêu diệt.</t>
         </is>
       </c>
@@ -9420,7 +9420,7 @@
       </c>
       <c r="M138" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Companion's Aid]&lt;/color&gt; Summon Sanhua để thi triển Resonance Liberation khi Năng Lượng Khúc Tấu đạt tối đa, kích hoạt Intro Skill.</t>
+          <t>&lt;color=#ffd12f&gt;[Hỗ Trợ Đồng Hành]&lt;/color&gt; Triệu hồi Sanhua để thi triển Resonance Liberation khi Năng Lượng Khúc Tấu đạt tối đa, kích hoạt Kỹ Năng Khởi Động.</t>
         </is>
       </c>
     </row>
@@ -9485,7 +9485,7 @@
       </c>
       <c r="M139" t="inlineStr">
         <is>
-          <t>Concerto: Sanhua</t>
+          <t>Khúc Concerto: Sanhua</t>
         </is>
       </c>
     </row>
@@ -9550,7 +9550,7 @@
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t>&lt;color=#c49e55&gt;[Forte Circuit]&lt;/color&gt; &lt;color=#c49e55&gt;[Effect Replacement]&lt;/color&gt; Khi Baizhi tiêu hao Concentration bằng Resonance Skill, mỗi {0} Concentration tiêu hao sẽ tạo ra {1} "Kim Châm Bạc" tấn công mục tiêu. Mỗi "Kim Châm Bạc" gây {2} Sát Thương.</t>
+          <t>&lt;color=#c49e55&gt;[Forte Circuit]&lt;/color&gt; &lt;color=#c49e55&gt;[Thay Thế Hiệu Ứng]&lt;/color&gt; Khi Baizhi tiêu hao Tập Trung bằng Resonance Skill, mỗi {0} Tập Trung tiêu hao sẽ tạo ra {1} "Kim Châm Bạc" tấn công mục tiêu. Mỗi "Kim Châm Bạc" gây {2} Sát Thương.</t>
         </is>
       </c>
     </row>
@@ -9615,7 +9615,7 @@
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t>&lt;color=#c49e55&gt;[Forte Circuit]&lt;/color&gt; &lt;color=#c49e55&gt;[Effect Replacement]&lt;/color&gt; Khi Resonance Skill tiêu hao Concentration, "Kim Châm Bạc" sẽ được tạo ra để tấn công kẻ địch.</t>
+          <t>&lt;color=#c49e55&gt;[Forte Circuit]&lt;/color&gt; &lt;color=#c49e55&gt;[Thay Thế Hiệu Ứng]&lt;/color&gt; Khi Resonance Skill tiêu hao Tập Trung, "Kim Châm Bạc" sẽ được tạo ra để tấn công kẻ địch.</t>
         </is>
       </c>
     </row>
@@ -9681,7 +9681,7 @@
       </c>
       <c r="M142" t="inlineStr">
         <is>
-          <t>&lt;color=#c49e55&gt;[Special Enhancement]&lt;/color&gt; Sau khi "Silver Awls" hoặc "Silver Kernels" trúng mục tiêu, có 20% cơ hội tạo ra 1 "Polyphone" tồn tại trong 5 giây. Tối đa 3 "Polyphone" có thể tồn tại đồng thời. "Polyphone" sẽ cấp một hiệu ứng buff ngẫu nhiên khi nhặt;
+          <t>&lt;color=#c49e55&gt;[Tăng Cường Đặc Biệt]&lt;/color&gt; Sau khi "Silver Awls" hoặc "Silver Kernels" trúng mục tiêu, có 20% cơ hội tạo ra 1 "Polyphone" tồn tại trong 5 giây. Tối đa 3 "Polyphone" có thể tồn tại đồng thời. "Polyphone" sẽ cấp một hiệu ứng buff ngẫu nhiên khi nhặt;
 Ngoài ra, cũng có khả năng xuất hiện "Enhanced Polyphone", có thể mang lại hậu quả bất ngờ khi nhặt.</t>
         </is>
       </c>
@@ -9747,7 +9747,7 @@
       </c>
       <c r="M143" t="inlineStr">
         <is>
-          <t>&lt;color=#c49e55&gt;[Special Enhancement]&lt;/color&gt; "Polyphone" và "Enhanced Polyphone" có thể được tạo ra khi "Silver Awls" trúng mục tiêu.</t>
+          <t>&lt;color=#c49e55&gt;[Tăng Cường Đặc Biệt]&lt;/color&gt; "Polyphone" và "Enhanced Polyphone" có thể được tạo ra khi "Silver Awls" trúng mục tiêu.</t>
         </is>
       </c>
     </row>
@@ -9815,7 +9815,7 @@
       </c>
       <c r="M144" t="inlineStr">
         <is>
-          <t>&lt;color=#c49e55&gt;[Resonance Liberation]&lt;/color&gt; &lt;color=#c49e55&gt;[Effect Enhancement]&lt;/color&gt; Khi kích hoạt Resonance Liberation, Bạch Chỉ sẽ mất {0} HP hiện tại và nhận "Hộ Mệnh You'tan" trong {1} giây, mang lại hiệu ứng:
+          <t>&lt;color=#c49e55&gt;[Resonance Liberation]&lt;/color&gt; &lt;color=#c49e55&gt;[Tăng Cường Hiệu Ứng]&lt;/color&gt; Khi kích hoạt Resonance Liberation, Bạch Chỉ sẽ mất {0} HP hiện tại và nhận "Hộ Mệnh You'tan" trong {1} giây, mang lại hiệu ứng:
 Hồi phục HP {2} lần mỗi giây, và;
 Tăng gấp đôi số lượng "Kim Châm" tạo ra trong thời gian này, và;
 Biến tất cả "Kim Châm" thành "Hạt Kim", gây {3} Sát Thương.</t>
@@ -9883,7 +9883,7 @@
       </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t>&lt;color=#c49e55&gt;[Resonance Liberation]&lt;/color&gt; &lt;color=#c49e55&gt;[Effect Enhancement]&lt;/color&gt; Resonance Liberation tiêu hao HP và ban cho "Hộ Mệnh You'tan".</t>
+          <t>&lt;color=#c49e55&gt;[Resonance Liberation]&lt;/color&gt; &lt;color=#c49e55&gt;[Tăng Cường Hiệu Ứng]&lt;/color&gt; Resonance Liberation tiêu hao HP và ban cho "Hộ Mệnh You'tan".</t>
         </is>
       </c>
     </row>
@@ -9948,7 +9948,7 @@
       </c>
       <c r="M146" t="inlineStr">
         <is>
-          <t>&lt;color=#c49e55&gt;[Special Enhancement]&lt;/color&gt; "Silver Awls" và "Silver Kernels" gây thêm {0} sát thương. Hiệu ứng này có thể kích hoạt {2} lần mỗi {1} giây.</t>
+          <t>&lt;color=#c49e55&gt;[Tăng Cường Đặc Biệt]&lt;/color&gt; "Silver Awls" và "Silver Kernels" gây thêm {0} DMG. Hiệu ứng này có thể kích hoạt {2} lần mỗi {1} giây.</t>
         </is>
       </c>
     </row>
@@ -10013,7 +10013,7 @@
       </c>
       <c r="M147" t="inlineStr">
         <is>
-          <t>&lt;color=#c49e55&gt;[Special Enhancement]&lt;/color&gt; "Silver Awls" gây thêm sát thương.</t>
+          <t>&lt;color=#c49e55&gt;[Tăng Cường Đặc Biệt]&lt;/color&gt; "Silver Awls" gây thêm sát thương.</t>
         </is>
       </c>
     </row>
@@ -10080,7 +10080,7 @@
       </c>
       <c r="M148" t="inlineStr">
         <is>
-          <t>&lt;color=#c49e55&gt;[Resonance Skill]&lt;/color&gt; &lt;color=#c49e55&gt;[Effect Replacement]&lt;/color&gt; Sau khi sử dụng Resonance Skill, tối đa {0} Kim Châm Phối Hợp sẽ được tạo ra dựa trên lượng Forte đã tiêu hao, tồn tại trong {1} giây. Các Kim Châm sẽ phối hợp tấn công cùng Baizhi. Mỗi Kim Châm gây {2} sát thương.
+          <t>&lt;color=#c49e55&gt;[Resonance Skill]&lt;/color&gt; &lt;color=#c49e55&gt;[Thay Thế Hiệu Ứng]&lt;/color&gt; Sau khi sử dụng Resonance Skill, tối đa {0} Kim Châm Phối Hợp sẽ được tạo ra dựa trên lượng Forte đã tiêu hao, tồn tại trong {1} giây. Các Kim Châm sẽ phối hợp tấn công cùng Baizhi. Mỗi Kim Châm gây {2} DMG.
 Tiêu hao 2-3 Forte tạo ra 1 Kim Châm Phối Hợp.
 Tiêu hao 4 Forte tạo ra 2 Kim Châm Phối Hợp.</t>
         </is>
@@ -10147,7 +10147,7 @@
       </c>
       <c r="M149" t="inlineStr">
         <is>
-          <t>&lt;color=#c49e55&gt;[Resonance Skill]&lt;/color&gt; &lt;color=#c49e55&gt;Effect Replacement&lt;/color&gt; Sau khi sử dụng Resonance Skill, Kim Châm Phối Hợp sẽ được tạo ra dựa trên lượng Forte đã tiêu hao. Trong thời gian hiệu ứng tồn tại, sử dụng Basic Attack sẽ kích hoạt tấn công phối hợp.</t>
+          <t>&lt;color=#c49e55&gt;[Resonance Skill]&lt;/color&gt; &lt;color=#c49e55&gt;Thay Thế Hiệu Ứng&lt;/color&gt; Sau khi sử dụng Resonance Skill, Kim Châm Phối Hợp sẽ được tạo ra dựa trên lượng Forte đã tiêu hao. Trong thời gian hiệu ứng tồn tại, sử dụng Basic Attack sẽ kích hoạt tấn công phối hợp.</t>
         </is>
       </c>
     </row>
@@ -10212,7 +10212,7 @@
       </c>
       <c r="M150" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Special Enhancement]&lt;/color&gt; Tăng cường hiệu ứng "Đinh Bạc": Cứ 10 "Đinh Bạc" trúng mục tiêu, tất cả "Đinh Bạc" sẽ biến thành "Hạt Bạc" trong 3 giây tiếp theo.</t>
+          <t>&lt;color=#ffd12f&gt;[Tăng Cường Đặc Biệt]&lt;/color&gt; Tăng cường hiệu ứng "Đinh Bạc": Cứ 10 "Đinh Bạc" trúng mục tiêu, tất cả "Đinh Bạc" sẽ biến thành "Hạt Bạc" trong 3 giây tiếp theo.</t>
         </is>
       </c>
     </row>
@@ -10277,7 +10277,7 @@
       </c>
       <c r="M151" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Special Enhancement]&lt;/color&gt; Sau khi một số lượng "Đinh Bạc" nhất định trúng mục tiêu, tất cả "Đinh Bạc" sẽ tạm thời được tăng cường thành "Hạt Bạc".</t>
+          <t>&lt;color=#ffd12f&gt;[Tăng Cường Đặc Biệt]&lt;/color&gt; Sau khi một số lượng "Đinh Bạc" nhất định trúng mục tiêu, tất cả "Đinh Bạc" sẽ tạm thời được tăng cường thành "Hạt Bạc".</t>
         </is>
       </c>
     </row>
@@ -10343,7 +10343,7 @@
       </c>
       <c r="M152" t="inlineStr">
         <is>
-          <t>&lt;color=#c49e55&gt;[Special Enhancement]&lt;/color&gt; Sau khi "Silver Awls" hoặc "Silver Kernels" trúng mục tiêu, có {0}% cơ hội tạo ra {1} "Polyphone" tồn tại trong {2} giây. Tối đa {3} "Polyphone" có thể tồn tại đồng thời. "Polyphone" sẽ cấp một hiệu ứng buff ngẫu nhiên khi nhặt;
+          <t>&lt;color=#c49e55&gt;[Tăng Cường Đặc Biệt]&lt;/color&gt; Sau khi "Silver Awls" hoặc "Silver Kernels" trúng mục tiêu, có {0}% cơ hội tạo ra {1} "Polyphone" tồn tại trong {2} giây. Tối đa {3} "Polyphone" có thể tồn tại đồng thời. "Polyphone" sẽ cấp một hiệu ứng buff ngẫu nhiên khi nhặt;
 Ngoài ra, cũng có khả năng xuất hiện "Enhanced Polyphone", có thể mang lại kết quả bất ngờ khi nhặt.</t>
         </is>
       </c>
@@ -10409,7 +10409,7 @@
       </c>
       <c r="M153" t="inlineStr">
         <is>
-          <t>&lt;color=#c49e55&gt;[Special Enhancement]&lt;/color&gt; "Polyphone" và "Enhanced Polyphone" có thể được tạo ra khi "Silver Awls" trúng mục tiêu.</t>
+          <t>&lt;color=#c49e55&gt;[Tăng Cường Đặc Biệt]&lt;/color&gt; "Polyphone" và "Enhanced Polyphone" có thể được tạo ra khi "Silver Awls" trúng mục tiêu.</t>
         </is>
       </c>
     </row>
@@ -10474,7 +10474,7 @@
       </c>
       <c r="M154" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Companion's Aid]&lt;/color&gt; Summon Baizhi để tung chiêu Resonance Liberation khi Năng Lượng Khúc Tụ đã đầy, kích hoạt Kỹ Năng Khởi Đầu.</t>
+          <t>&lt;color=#ffd12f&gt;[Hỗ Trợ Đồng Hành]&lt;/color&gt; Triệu hồi Baizhi để tung chiêu Resonance Liberation khi Năng Lượng Khúc Tụ đã đầy, kích hoạt Kỹ Năng Khởi Đầu.</t>
         </is>
       </c>
     </row>
@@ -10608,7 +10608,7 @@
         <is>
           <t>&lt;color=#c49e55&gt;[Basic Attack]&lt;/color&gt;
 - Khi sử dụng Basic Attack: Feral Gyrate trong trạng thái Striding Lion, sẽ tạo ra các Cloud Blossom Poles tồn tại trong {0} giây.
-- Kích hoạt Resonance Skill Mountain Roamer trong trạng thái Striding Lion sẽ kích nổ Cloud Blossom Poles khi đi qua, gây Glacio DMG bằng {1} Attack của Lingyang và hồi {2} Lion's Spirit.</t>
+- Kích hoạt Resonance Skill Mountain Roamer trong trạng thái Striding Lion sẽ kích nổ Cloud Blossom Poles khi đi qua, gây Sát Thương Glacio bằng {1} ATK của Lingyang và hồi {2} Lion's Spirit.</t>
         </is>
       </c>
     </row>
@@ -10677,7 +10677,7 @@
         <is>
           <t>&lt;color=#c49e55&gt;[Basic Attack]&lt;/color&gt;
 - Thực hiện Basic Attack: Feral Gyrate khi ở trạng thái Striding Lion sẽ tạo ra Cloud Blossom Poles.
-- Sử dụng Resonance Skill Mountain Roamer khi ở trạng thái Striding Lion sẽ kích nổ Cloud Blossom Poles khi đi qua, gây Glacio DMG và hồi phục Lion's Spirit.</t>
+- Sử dụng Resonance Skill Mountain Roamer khi ở trạng thái Striding Lion sẽ kích nổ Cloud Blossom Poles khi đi qua, gây DMG Glacio và hồi phục Lion's Spirit.</t>
         </is>
       </c>
     </row>
@@ -10744,7 +10744,7 @@
       <c r="M158" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Resonance Skill]&lt;/color&gt;
-Mỗi lần sử dụng Basic Attack hoặc Resonance Skill khi ở trạng thái Striding Lion, Attack của Lingyang sẽ tăng thêm {0} trong {1} giây. Hiệu ứng này có thể kích hoạt mỗi giây một lần, tối đa {2} lần.</t>
+Mỗi lần sử dụng Đòn Basic Attack hoặc Resonance Skill khi ở trạng thái Sư Tử Băng Hoành, ATK của Lingyang sẽ tăng thêm {0} trong {1} giây. Hiệu ứng này có thể kích hoạt mỗi giây một lần, tối đa {2} lần.</t>
         </is>
       </c>
     </row>
@@ -10811,7 +10811,7 @@
       <c r="M159" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Resonance Skill]&lt;/color&gt;
-Mỗi lần sử dụng Basic Attack hoặc Resonance Skill khi ở trạng thái Striding Lion, Attack của Lingyang sẽ tăng lên.</t>
+Mỗi lần sử dụng Đòn Basic Attack hoặc Resonance Skill khi ở trạng thái Sư Tử Băng Hoành, ATK của Lingyang sẽ tăng lên.</t>
         </is>
       </c>
     </row>
@@ -11020,7 +11020,7 @@
           <t>&lt;color=#c49e55&gt;[Forte Circuit]&lt;/color&gt;
 - Trong trạng thái Striding Lion, cứ mỗi {0} giây, Lingyan nhận 1 tầng Lion's Charm, tối đa {1} tầng.
 - Giữ nút Normal Attack trong trạng thái Striding Lion sẽ tiêu hao toàn bộ tầng Lion's Spirit để thi triển Stormy Kicks.
-- Lion's Charm: Khi dùng Resonance Skill Furious Punches, triệu hồi One For the Pole gây Glacio DMG bằng {2} Attack của Lingyang.</t>
+- Lion's Charm: Khi dùng Resonance Skill Furious Punches, triệu hồi One For the Pole gây Sát Thương Glacio bằng {2} ATK của Lingyang.</t>
         </is>
       </c>
     </row>
@@ -11091,7 +11091,7 @@
           <t>&lt;color=#c49e55&gt;[Forte Circuit]&lt;/color&gt;
 - Khi ở trạng thái Striding Lion, Lingyan nhận được hiệu ứng Lion's Charm có thể chồng chất.
 - Giữ nút Normal Attack trong trạng thái Striding Lion sẽ tiêu hao toàn bộ tầng Lion's Spirit để tung đòn Stormy Kicks.
-- Lion's Charm: Sử dụng Resonance Skill Furious Punches sẽ triệu hồi One For the Pole gây Glacio DMG.</t>
+- Lion's Charm: Sử dụng Resonance Skill Furious Punches sẽ triệu hồi One For the Pole gây Sát Thương Glacio.</t>
         </is>
       </c>
     </row>
@@ -11158,7 +11158,7 @@
       <c r="M164" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Resonance Liberation]&lt;/color&gt;
-Khi cả Resonance Liberation - Lion's Vigor và Striding Lion đều đang hoạt động, mỗi đòn Basic Attack: Feral Gyrate sẽ triệu hồi một One For the Pole khi trúng mục tiêu, gây Glacio DMG bằng {0} Attack của Lingyang. Hiệu ứng này có thể kích hoạt mỗi {1} giây một lần.</t>
+Khi cả Resonance Liberation - Sức Mạnh Sư Tử và Bước Chạy Sư Tử đều đang hoạt động, mỗi đòn Basic Attack: Xoay Thú sẽ triệu hồi một One For the Pole khi trúng mục tiêu, gây DMG Glacio bằng {0} ATK của Lingyang. Hiệu ứng này có thể kích hoạt mỗi {1} giây một lần.</t>
         </is>
       </c>
     </row>
@@ -11225,7 +11225,7 @@
       <c r="M165" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Resonance Liberation]&lt;/color&gt;
-Khi cả Resonance Liberation: Lion's Vigor và Striding Lion đều đang hoạt động, mỗi đòn Basic Attack: Feral Gyrate sẽ triệu hồi 1 One For the Pole khi trúng mục tiêu, gây Glacio DMG.</t>
+Khi cả Resonance Liberation: Sức Mạnh Sư Tử và Bước Chạy Sư Tử đều đang hoạt động, mỗi đòn Basic Attack: Xoay Thú sẽ triệu hồi 1 One For the Pole khi trúng mục tiêu, gây DMG Glacio.</t>
         </is>
       </c>
     </row>
@@ -11298,7 +11298,7 @@
 Youhu nhận được các hiệu ứng sau sau khi kích hoạt Resonance Liberation, kéo dài trong 15 giây:
 - Nhận thêm 1 lần kích hoạt sau khi kích hoạt Mạch Năng: Bản Chất Thi Ca.
 - Các lần kích hoạt Mạch Năng: Bản Chất Thi Ca nhận được theo cách này không thể nhận thêm lần kích hoạt mới khi được kích hoạt và chắc chắn sẽ kích hoạt Giai Điệu Hoàn Hảo.
-- Có {0} xác suất Youhu miễn nhiễm mọi sát thương trong khi hiệu ứng này hoạt động. Bất kỳ mục tiêu nào tấn công Youhu sẽ nhận Glacio DMG bằng {1} Tấn Công của Youhu, được tính là sát thương Resonance Skill.</t>
+- Có {0} xác suất Youhu miễn nhiễm mọi DMG trong khi hiệu ứng này hoạt động. Bất kỳ mục tiêu nào tấn công Youhu sẽ nhận DMG Glacio bằng {1} ATK của Youhu, được tính là DMG Resonance Skill.</t>
         </is>
       </c>
     </row>
@@ -11369,7 +11369,7 @@
           <t>&lt;color=#c49e55&gt;[Resonance Liberation]&lt;/color&gt;
 Youhu nhận được các hiệu ứng sau sau khi kích hoạt Resonance Liberation, kéo dài trong 15 giây:
 - Nhận thêm 1 lần kích hoạt sau khi kích hoạt Mạch Năng: Bản Chất Thi Ca.
-- Có xác suất nhất định Youhu sẽ miễn nhiễm mọi sát thương trong khi hiệu ứng này hoạt động. Bất kỳ mục tiêu nào tấn công Youhu sẽ nhận Glacio DMG.</t>
+- Có xác suất nhất định Youhu sẽ miễn nhiễm mọi DMG trong khi hiệu ứng này hoạt động. Bất kỳ mục tiêu nào tấn công Youhu sẽ nhận DMG Glacio.</t>
         </is>
       </c>
     </row>
@@ -11437,7 +11437,7 @@
       <c r="M168" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Forte Circuit]&lt;/color&gt;
-- Increase Sát Thương Đánh Giá Cổ Vật thêm {0}.
+- Tăng Sát Thương Đánh Giá Cổ Vật thêm {0}.
 - Nhận 1 lần kích hoạt Forte Circuit: Thi Ca Tinh Túa mỗi {1} giây, mỗi lần kích hoạt đều đảm bảo tạo ra Vần Hoàn Hảo.</t>
         </is>
       </c>
@@ -11576,7 +11576,7 @@
         <is>
           <t>&lt;color=#c49e55&gt;[Basic Attack]&lt;/color&gt;
 - Hiệu suất thu thập Frost từ Heavy Attack được tăng lên đáng kể.
-- Sử dụng Heavy Attack: Frostfall sẽ tăng Attack {0} trong {1} giây.</t>
+- Sử dụng Heavy Attack: Frostfall sẽ tăng ATK {0} trong {1} giây.</t>
         </is>
       </c>
     </row>
@@ -11645,7 +11645,7 @@
         <is>
           <t>&lt;color=#c49e55&gt;[Basic Attack]&lt;/color&gt;
 - Hiệu suất thu thập Frost từ Heavy Attack được tăng lên đáng kể.
-- Sử dụng Heavy Attack: Frostfall sẽ tăng Attack.</t>
+- Sử dụng Heavy Attack: Frostfall increases ATK.</t>
         </is>
       </c>
     </row>
@@ -11716,9 +11716,9 @@
         <is>
           <t>&lt;color=#c49e55&gt;[Resonance Skill]&lt;/color&gt;
 Sau khi sử dụng Resonance Skill, ngẫu nhiên kích hoạt một trong các hiệu ứng sau (có thể chồng chất):
-- Có xác suất {0} triệu hồi 3 Mask khổng lồ tấn công, mỗi Mask gây sát thương bằng {1} sát thương của Antique Appraisal: Chime.
-- Có xác suất {2} kích nổ, gây sát thương bằng {3} Tấn Công của Youhu, được tính là sát thương Resonance Skill.
-- Có xác suất {4} đặt lại Cooldown chiêu của Resonance Skill.</t>
+- Có xác suất {0} triệu hồi 3 Mặt Nạ khổng lồ tấn công, mỗi Mặt Nạ gây DMG bằng {1} DMG của Antique Appraisal: Chime.
+- Có xác suất {2} kích nổ, gây DMG bằng {3} ATK của Youhu, được tính là DMG Resonance Skill.
+- Có xác suất {4} đặt lại Thời gian hồi chiêu của Resonance Skill.</t>
         </is>
       </c>
     </row>
@@ -11790,8 +11790,8 @@
           <t>&lt;color=#c49e55&gt;[Resonance Skill]&lt;/color&gt;
 Sau khi sử dụng Resonance Skill, ngẫu nhiên kích hoạt một trong các hiệu ứng sau (có thể chồng chất):
 - Có xác suất triệu hồi 3 Mặt Nạ khổng lồ tấn công.
-- Có xác suất kích nổ, gây Glacio DMG.
-- Có xác suất đặt lại Cooldown chiêu của Resonance Skill.</t>
+- Có xác suất kích nổ, gây DMG Glacio.
+- Có xác suất đặt lại Thời gian hồi chiêu của Resonance Skill.</t>
         </is>
       </c>
     </row>
@@ -11928,7 +11928,7 @@
       <c r="M175" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Forte Circuit]&lt;/color&gt;
-- Khi Đánh Giá Cổ Vật (Chuông, Như Ý, Đỉnh và Mask) gây Sát Thương, sẽ bỏ qua một phần Phòng Ngự của mục tiêu.
+- Khi Đánh Giá Cổ Vật (Chuông, Như Ý, Đỉnh và Mặt Nạ) gây Sát Thương, sẽ bỏ qua một phần Phòng Ngự của mục tiêu.
 - Khả năng hút mục tiêu của Forte Circuit: Thi Ca Tinh Túa được tăng cường.</t>
         </is>
       </c>
@@ -12001,7 +12001,7 @@
           <t>&lt;color=#c49e55&gt;[Resonance Liberation]&lt;/color&gt;
 Sử dụng Resonance Liberation - Era of New Wave sẽ nhận được &lt;SapTag=0&gt;{0}&lt;/SapTag&gt; {Cus:Sap,S=lớp P=lớp SapTag=0} Mirror Bloom.
 Khi ở trạng thái Resonance Liberation - Twilight Tango, sử dụng Resonance Skill - Art of Violence và Resonance Skill - Chromatic Splendor sẽ tiêu hao toàn bộ Meta Vector. Mỗi Meta Vector tiêu hao sẽ nhận được 1 lớp Mirror Bloom, và thời gian của Twilight Tango sẽ được làm mới.
-Resonance Liberation - Fatal Finale sẽ gây thêm sát thương bằng {2} Tấn Công của Carlotta &lt;SapTag=1&gt;{1}&lt;/SapTag&gt; {Cus:Sap,S=lần P=lần SapTag=1}, được tính là sát thương Resonance Skill.
+Resonance Liberation - Fatal Finale sẽ gây thêm DMG bằng {2} ATK của Carlotta &lt;SapTag=1&gt;{1}&lt;/SapTag&gt; {Cus:Sap,S=lần P=lần SapTag=1}, được tính là DMG Resonance Skill.
 [Mirror Bloom]: Sử dụng Fatal Finale sẽ tiêu hao toàn bộ lớp Mirror Bloom, mỗi lớp tăng Hệ Số Sát Thương của Fatal Finale thêm {3}, tối đa {4} lần.</t>
         </is>
       </c>
@@ -12138,7 +12138,7 @@
       <c r="M178" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Resonance Liberation]&lt;/color&gt;
-Skill Resonance Liberation - Hồi Chuông Tử Thần và Dodge Phản Công chuyển thành Resonance Liberation - An Nghỉ Cuối Cùng, gây sát thương bằng {0} sát thương Hồi Chuông Tử Thần cộng {1} Tấn Công của Carlotta, được tính là sát thương Resonance Skill.
+Kỹ năng Resonance Liberation - Hồi Chuông Tử Thần và Né Tránh Phản Công chuyển thành Resonance Liberation - An Nghỉ Cuối Cùng, gây DMG bằng {0} DMG Hồi Chuông Tử Thần cộng {1} ATK của Carlotta, được tính là DMG Resonance Skill.
 Khi thi triển An Nghỉ Cuối Cùng, Carlotta miễn nhiễm với gián đoạn.
 Hiệu ứng từ Forte Circuit - Cung Cuối trở nên hoạt động liên tục.</t>
         </is>
@@ -12207,7 +12207,7 @@
       <c r="M179" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Resonance Liberation]&lt;/color&gt;
-Kỹ năng Resonance Liberation - Hồi Chuông Tử Thần và Dodge Phản Công chuyển thành Resonance Liberation - An Nghỉ Cuối Cùng, gây thêm sát thương, trong đó Carlotta miễn nhiễm với gián đoạn.</t>
+Kỹ năng Resonance Liberation - Hồi Chuông Tử Thần và Né Tránh Phản Công chuyển thành Resonance Liberation - An Nghỉ Cuối Cùng, gây thêm sát thương, trong đó Carlotta miễn nhiễm với gián đoạn.</t>
         </is>
       </c>
     </row>
@@ -12277,9 +12277,9 @@
       <c r="M180" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Resonance Skill]&lt;/color&gt;
-Khi đánh trúng mục tiêu bằng Resonance Skill - Art of Violence, Rover sẽ hồi phục thêm &lt;SapTag=0&gt;{0}&lt;/SapTag&gt; {Cus:Sap,S=điểm P=điểm} Chất. Khi đánh trúng mục tiêu bằng Basic Attack - Biện Pháp Cần Thiết, mục tiêu sẽ bị ảnh hưởng bởi Giải Cấu.
+Khi đánh trúng mục tiêu bằng Resonance Skill - Nghệ Thuật Bạo Lực, Rover sẽ hồi phục thêm &lt;SapTag=0&gt;{0}&lt;/SapTag&gt; {Cus:Sap,S=điểm P=điểm} Chất. Khi đánh trúng mục tiêu bằng Đòn Cơ Bản - Biện Pháp Cần Thiết, mục tiêu sẽ bị ảnh hưởng bởi Giải Cấu.
 Giải Cấu được tăng cường như sau:
-Khi gây Giải Cấu lên mục tiêu, nếu Carlotta đang trong Resonatori Phóng - Vũ Điệu Hoàng Hôn, cô sẽ triệu hồi {1} Khẩu Súng Pha Lê tấn công mục tiêu, mỗi khẩu gây sát thương bằng {2} Attack của Carlotta. Nếu Carlotta không trong Vũ Điệu Hoàng Hôn, cô sẽ triệu hồi {3} Viên Ngọc Opal tấn công mục tiêu, mỗi viên gây Glacio DMG bằng {4} Attack của Carlotta, được tính là sát thương Resonance Skill.
+Khi gây Giải Cấu lên mục tiêu, nếu Carlotta đang trong Cộng Hưởng Giải Phóng - Vũ Điệu Hoàng Hôn, cô sẽ triệu hồi {1} Khẩu Súng Pha Lê tấn công mục tiêu, mỗi khẩu gây DMG bằng {2} ATK của Carlotta. Nếu Carlotta không trong Vũ Điệu Hoàng Hôn, cô sẽ triệu hồi {3} Viên Ngọc Opal tấn công mục tiêu, mỗi viên gây DMG Glacio bằng {4} ATK của Carlotta, được tính là DMG Resonance Skill.
 Hiệu ứng từ Forte Circuit - Cung Cuối trở nên luôn hoạt động.</t>
         </is>
       </c>
@@ -12348,7 +12348,7 @@
       <c r="M181" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Resonance Skill]&lt;/color&gt;
-Resonance Skill - Art of Violence hồi phục thêm Đồng Hồ Forte. Basic Attack - Biện Pháp Cần Thiết gây Giải Cấu lên mục tiêu khi trúng đòn.
+Resonance Skill - Nghệ Thuật Bạo Lực hồi phục thêm Đồng Hồ Forte. Đòn Cơ Bản - Biện Pháp Cần Thiết gây Giải Cấu lên mục tiêu khi trúng đòn.
 Giải Cấu được tăng cường.</t>
         </is>
       </c>
@@ -12418,9 +12418,9 @@
       <c r="M182" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Forte Circuit]&lt;/color&gt;
-Heavy Attack - Cận Kề Hư Vô từ Forte Circuit giờ đây sẽ gây hiệu ứng Resonance Skill - Phân Tán lên mục tiêu khi trúng đích.
-Tinh Thể Đa Sắc không còn Cooldown chiêu.
-Khi ở trạng thái Resonance Liberation - Vũ Điệu Hoàng Hôn và trong vòng {0} giây sau khi sử dụng Resonance Skill - Sắc Màu Rực Rỡ, Đòn Mid-air Attack - Lời Chào Thông Thường sẽ trở thành Heavy Attack - Cận Kề Oblivion.</t>
+Đòn Heavy Attack - Cận Kề Hư Vô từ Forte Circuit giờ đây sẽ gây hiệu ứng Resonance Skill - Phân Tán lên mục tiêu khi trúng đích.
+Tinh Thể Đa Sắc không còn Thời gian hồi chiêu.
+Khi ở trạng thái Resonance Liberation - Vũ Điệu Hoàng Hôn và trong vòng {0} giây sau khi sử dụng Resonance Skill - Sắc Màu Rực Rỡ, Đòn Mid-air Attack - Lời Chào Thông Thường sẽ trở thành Đòn Heavy Attack - Cận Kề Hư Vô.</t>
         </is>
       </c>
     </row>
@@ -12487,7 +12487,7 @@
       <c r="M183" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Forte Circuit]&lt;/color&gt;
-Heavy Attack - Cận Kề Hư Vô từ Forte Circuit được tăng cường đặc biệt.</t>
+Đòn Heavy Attack - Cận Kề Hư Vô từ Forte Circuit được tăng cường đặc biệt.</t>
         </is>
       </c>
     </row>
@@ -12556,9 +12556,9 @@
       <c r="M184" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Resonance Skill]&lt;/color&gt;
-Resonance Skill - Art of Violence có phạm vi tấn công mở rộng.
+Resonance Skill - Nghệ Thuật Bạo Lực có phạm vi tấn công mở rộng.
 Phân Tán được tăng cường hiệu ứng sau:
-Glacio RES của mục tiêu giảm {0} trong {1} giây.</t>
+Kháng Glacio của mục tiêu giảm {0} trong {1} giây.</t>
         </is>
       </c>
     </row>
@@ -12626,7 +12626,7 @@
       <c r="M185" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Resonance Skill]&lt;/color&gt;
-Resonance Skill - Art of Violence có phạm vi tấn công mở rộng.
+Resonance Skill - Nghệ Thuật Bạo Lực có phạm vi tấn công mở rộng.
 Phân Tán được tăng cường.</t>
         </is>
       </c>
@@ -12695,8 +12695,8 @@
       <c r="M186" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Resonance Skill]&lt;/color&gt;
-· Sát thương gây ra bởi Resonance Skill của Encore, Mộng Cảnh: Mây Cloudy và Mộng Cảnh: Cosmos sẽ bỏ qua {0} Phòng Ngự của mục tiêu.
-· Triệu hồi Mộng Cảnh: Mây Cloudy cũng sẽ triệu hồi Mộng Cảnh: Cosmos, gây Fusion DMG bằng {1} sức tấn công của Encore, được tính là sát thương Basic Attack. Hiệu ứng này chỉ có thể kích hoạt mỗi {2} giây một lần.</t>
+· DMG gây ra bởi Resonance Skill của Encore, Mộng Cảnh: Mây U Ám và Mộng Cảnh: Vũ Trụ sẽ bỏ qua {0} Phòng Ngự của mục tiêu.
+· Triệu hồi Mộng Cảnh: Mây U Ám cũng sẽ triệu hồi Mộng Cảnh: Vũ Trụ, gây DMG Fusion bằng {1} sức tấn công của Encore, được tính là DMG Đòn Basic Attack. Hiệu ứng này chỉ có thể kích hoạt mỗi {2} giây một lần.</t>
         </is>
       </c>
     </row>
@@ -12764,8 +12764,8 @@
       <c r="M187" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Resonance Skill]&lt;/color&gt;
-- Sát thương gây ra bởi Resonance Skill của Encore, Dreamscape: Cloudy và Dreamscape: Cosmos sẽ bỏ qua một lượng Phòng Ngự nhất định của mục tiêu.
-- Triệu hồi Dreamscape: Cloudy cũng sẽ triệu hồi Dreamscape: Cosmos, gây Fusion DMG cao, được tính là Sát Thương Basic Attack.</t>
+- DMG gây ra bởi Resonance Skill của Encore, Dreamscape: Cloudy và Dreamscape: Cosmos sẽ bỏ qua một lượng Phòng Ngự nhất định của mục tiêu.
+- Triệu hồi Dreamscape: Cloudy cũng sẽ triệu hồi Dreamscape: Cosmos, gây Sát Thương Fusion cao, được tính là Sát Thương Basic Attack.</t>
         </is>
       </c>
     </row>
@@ -12835,10 +12835,10 @@
       <c r="M188" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Resonance Skill]&lt;/color&gt;
-- Gây Sát Thương bằng Resonance Skill sẽ giảm Cooldown chiêu Resonance Skill của Encore {0} giây. Hiệu ứng này có thể kích hoạt mỗi {1} giây.
-- Trong khi sử dụng Resonance Skill, Encore chịu ít hơn {2} sát thương và khả năng chống gián đoạn được tăng cường.
+- Gây Sát Thương bằng Resonance Skill sẽ giảm Thời gian hồi chiêu Resonance Skill của Encore {0} giây. Hiệu ứng này có thể kích hoạt mỗi {1} giây.
+- Trong khi sử dụng Resonance Skill, Encore chịu ít hơn {2} DMG và khả năng chống gián đoạn được tăng cường.
 - Có thể sử dụng lại Resonance Skill Flaming Woolies bằng cách kích hoạt Resonance Skill ngay sau lần sử dụng đầu. Kích hoạt lại ngay sau lần thứ hai sẽ kích hoạt Energetic Welcome.
-- Resonance Skill Cosmos: Rampage giờ đây gây thêm 2 đòn tấn công với lượng sát thương tương đương.</t>
+- Resonance Skill Cosmos: Rampage giờ đây gây thêm 2 đòn tấn công với lượng DMG tương đương.</t>
         </is>
       </c>
     </row>
@@ -12908,10 +12908,10 @@
       <c r="M189" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Resonance Skill]&lt;/color&gt;
-- Gây Sát Thương bằng Resonance Skill sẽ giảm Cooldown chiêu của Resonance Skill của Encore.
+- Gây Sát Thương bằng Resonance Skill sẽ giảm Thời gian hồi chiêu của Resonance Skill của Encore.
 - Khi thi triển Resonance Skill, Encore chịu ít Sát Thương hơn và khả năng chống gián đoạn được tăng cường.
 - Resonance Skill Flaming Woolies có thể được thi triển lại bằng cách sử dụng Resonance Skill ngay sau lần thi triển đầu. Thi triển lại ngay sau lần thứ hai của Flaming Woolies sẽ kích hoạt Energetic Welcome.
-- Resonance Skill Cosmos: Rampage giờ gây thêm Sát Thương.</t>
+- Resonance Skill Cosmos: Rampage now deals additional DMG.</t>
         </is>
       </c>
     </row>
@@ -12979,8 +12979,8 @@
       <c r="M190" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Basic Attack]&lt;/color&gt;
-- Gây sát thương bằng Basic Attack sẽ triệu hồi Cảnh Mộng: Mây Mù lao xuống đất, gây Fusion DMG bằng {0} Sát Thương Attack của Encore, được tính là sát thương Basic Attack. Hiệu ứng này chỉ kích hoạt một lần mỗi {1}s.
-- Khi thực hiện Heavy Attack: Cuồng Phong Mây hoặc Heavy Attack: Vỡ Cosmos, Encore chịu ít hơn {2} sát thương và hút kẻ địch xung quanh, gây Fusion DMG bằng {3} Sát Thương Attack của cô, được tính là sát thương Resonance Skill.</t>
+- Gây DMG bằng Basic Attack sẽ triệu hồi Cảnh Mộng: Mây Mù lao xuống đất, gây DMG Fusion bằng {0} Sát Thương ATK của Encore, được tính là DMG Basic Attack. Hiệu ứng này chỉ kích hoạt một lần mỗi {1}s.
+- Khi thực hiện Heavy Attack: Cuồng Phong Mây hoặc Heavy Attack: Vỡ Vũ Trụ, Encore chịu ít hơn {2} DMG và hút kẻ địch xung quanh, gây DMG Fusion bằng {3} Sát Thương ATK của cô, được tính là DMG Resonance Skill.</t>
         </is>
       </c>
     </row>
@@ -13048,8 +13048,8 @@
       <c r="M191" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Basic Attack]&lt;/color&gt;
-- Gây sát thương bằng Basic Attack sẽ triệu hồi Cảnh Mộng: Mây Mù gây Fusion DMG.
-- Khi thực hiện Heavy Attack: Cuồng Phong Mây hoặc Heavy Attack: Vỡ Cosmos, Encore chịu ít sát thương hơn và hút kẻ địch xung quanh, gây Fusion DMG.</t>
+- Gây DMG bằng Basic Attack sẽ triệu hồi Cảnh Mộng: Mây Mù gây DMG Fusion.
+- Khi thực hiện Heavy Attack: Cuồng Phong Mây hoặc Heavy Attack: Vỡ Vũ Trụ, Encore chịu ít DMG hơn và hút kẻ địch xung quanh, gây DMG Fusion.</t>
         </is>
       </c>
     </row>
@@ -13118,9 +13118,9 @@
       <c r="M192" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Basic Attack]&lt;/color&gt;
-- Encore nhận thêm {0} Fusion DMG Bonus.
-- Gây sát thương bằng Resonance Skill sẽ triệu hồi Cảnh Mộng: Mây Mù gây Fusion DMG bằng {1} Sát Thương Attack của Encore, được tính là sát thương Basic Attack. Hiệu ứng này chỉ kích hoạt một lần mỗi {2}s.
-- Cảnh Mộng: Mây Mù và Cảnh Mộng: Cosmos được tăng cường như sau: Phạm vi tấn công mở rộng và hệ số sát thương tăng thêm {3}.</t>
+- Encore nhận thêm {0} Tăng Sát Thương Fusion.
+- Gây DMG bằng Resonance Skill sẽ triệu hồi Cảnh Mộng: Mây Mù gây DMG Fusion bằng {1} Sát Thương ATK của Encore, được tính là DMG Basic Attack. Hiệu ứng này chỉ kích hoạt một lần mỗi {2}s.
+- Cảnh Mộng: Mây Mù và Cảnh Mộng: Vũ Trụ được tăng cường như sau: Phạm vi tấn công mở rộng và hệ số DMG tăng thêm {3}.</t>
         </is>
       </c>
     </row>
@@ -13189,9 +13189,9 @@
       <c r="M193" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Basic Attack]&lt;/color&gt;
-- Encore nhận thêm Fusion DMG Bonus.
-- Gây sát thương bằng Resonance Skill sẽ gây thêm Fusion DMG.
-- Cảnh Mộng: Mây Mù và Cảnh Mộng: Cosmos có phạm vi tấn công mở rộng và hệ số sát thương tăng thêm.</t>
+- Encore nhận thêm Tăng Sát Thương Fusion.
+- Gây DMG bằng Resonance Skill sẽ gây thêm DMG Fusion.
+- Cảnh Mộng: Cloudy and Dreamscape: Cosmos gain increased attack range and additional DMG Multiplier.</t>
         </is>
       </c>
     </row>
@@ -13259,8 +13259,8 @@
       <c r="M194" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Basic Attack]&lt;/color&gt;
-- Gây sát thương bằng Basic Attack sẽ hồi phục {0} Resonance Energy. Hiệu ứng này chỉ kích hoạt một lần mỗi giây.
-- Kích hoạt Resonance Liberation sẽ tung thêm một đòn Fusion DMG bằng {1} Sát Thương Attack của Encore, được tính là sát thương Basic Attack.</t>
+- Gây DMG bằng Basic Attack sẽ hồi phục {0} Resonance Energy. Hiệu ứng này chỉ kích hoạt một lần mỗi giây.
+- Kích hoạt Resonance Liberation sẽ tung thêm một đòn DMG Fusion bằng {1} Sát Thương ATK của Encore, được tính là DMG Basic Attack.</t>
         </is>
       </c>
     </row>
@@ -13329,7 +13329,7 @@
         <is>
           <t>&lt;color=#c49e55&gt;Basic Attack&lt;/color&gt;
 - Gây Sát Thương bằng Basic Attack sẽ hồi phục Resonance Energy.
-- Kích hoạt Resonance Liberation sẽ tung ra thêm một đòn Fusion DMG.</t>
+- Kích hoạt Resonance Liberation sẽ tung ra thêm một đòn Sát Thương Fusion.</t>
         </is>
       </c>
     </row>
@@ -13536,7 +13536,7 @@
         <is>
           <t>&lt;color=#c49e55&gt;[Resonance Liberation]&lt;/color&gt;
 - Kích hoạt Resonance Liberation sẽ ngay lập tức tung ra {0} đòn Sforzato.
-- Mục tiêu trúng Sforzato sẽ bị giảm Fusion RES DMG {1} trong {2} giây, có thể chồng chất lên đến {3} lần.</t>
+- Mục tiêu trúng Sforzato sẽ bị giảm Kháng Sát Thương Fusion {1} trong {2} giây, có thể chồng chất lên đến {3} lần.</t>
         </is>
       </c>
     </row>
@@ -13605,7 +13605,7 @@
         <is>
           <t>&lt;color=#c49e55&gt;[Resonance Liberation]&lt;/color&gt;
 - Kích hoạt Resonance Liberation sẽ ngay lập tức tung ra một loạt đòn Sforzato.
-- Mục tiêu trúng Sforzato sẽ bị giảm Fusion RES DMG.</t>
+- Mục tiêu trúng Sforzato sẽ bị giảm Kháng Sát Thương Fusion.</t>
         </is>
       </c>
     </row>
@@ -13673,7 +13673,7 @@
       <c r="M200" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Resonance Skill]&lt;/color&gt;
-- Tấn Công của Mortefi tăng thêm {0}.
+- ATK của Mortefi tăng thêm {0}.
 - Thi triển Resonance Skill Passionate Variation sẽ hồi phục toàn bộ Annoyance. Hiệu ứng này chỉ có thể kích hoạt mỗi {1} giây một lần.</t>
         </is>
       </c>
@@ -13742,7 +13742,7 @@
       <c r="M201" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Resonance Skill]&lt;/color&gt;
-- Tấn Công của Mortefi được tăng mạnh.
+- ATK của Mortefi được tăng mạnh.
 - Thi triển Resonance Skill Passionate Variation sẽ hồi phục toàn bộ Annoyance.</t>
         </is>
       </c>
@@ -13812,7 +13812,7 @@
         <is>
           <t>&lt;color=#c49e55&gt;[Resonance Skill]&lt;/color&gt;
 · Sức tấn công của Mortefi tăng thêm {0}.
-· Resonance Skill Khúc Phẫn Nộ được thay thế bằng Dodge Counter. Sử dụng Resonance Skill Khúc Phẫn Nộ hoặc Resonance Skill Giai Điệu Cuồng Nhiệt sẽ kích hoạt thêm {1} đòn Sforzato.</t>
+· Resonance Skill Khúc Phẫn Nộ được thay thế bằng Dodge Counter Tránh. Sử dụng Resonance Skill Khúc Phẫn Nộ hoặc Resonance Skill Giai Điệu Cuồng Nhiệt sẽ kích hoạt thêm {1} đòn Sforzato.</t>
         </is>
       </c>
     </row>
@@ -13880,8 +13880,8 @@
       <c r="M203" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Resonance Skill]&lt;/color&gt;
-- Tấn Công của Mortefi được tăng mạnh.
-- Phản Đòn Dodge trở thành Resonance Skill Fury Fugue. Thi triển Fury Fugue hoặc Resonance Skill Passionate Variation sẽ kích hoạt thêm đòn tấn công Sforzato.</t>
+- ATK của Mortefi được tăng mạnh.
+- Phản Đòn né trở thành Resonance Skill Fury Fugue. Thi triển Fury Fugue hoặc Resonance Skill Passionate Variation sẽ kích hoạt thêm đòn tấn công Sforzato.</t>
         </is>
       </c>
     </row>
@@ -13949,7 +13949,7 @@
       <c r="M204" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Resonance Liberation]&lt;/color&gt;
-- Mortefi nhận thêm {0} Fusion DMG Bonus.
+- Mortefi nhận thêm {0} Tăng Sát Thương Fusion.
 - Burning Rhapsody được tăng cường: Basic Attack giờ đây sẽ kích hoạt 2 đòn Marcato thay vì 1 khi trúng mục tiêu.</t>
         </is>
       </c>
@@ -14018,8 +14018,8 @@
       <c r="M205" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Resonance Liberation]&lt;/color&gt;
-- Mortefi nhận thêm Fusion DMG Bonus.
-- Burning Rhapsody được tăng cường: Basic Attack giờ đây sẽ kích hoạt thêm Marcato khi trúng mục tiêu.</t>
+- Mortefi nhận thêm Tăng Sát Thương Fusion.
+- Burning Rhapsody được tăng cường: Basic Attacks now trigger additional Marcato on hit.</t>
         </is>
       </c>
     </row>
@@ -14084,7 +14084,7 @@
       </c>
       <c r="M206" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Companion's Aid]&lt;/color&gt; Summon Mortefi để tung chiêu Resonance Liberation khi Năng Lượng Khúc Tụ đã đầy, kích hoạt Kỹ Năng Khởi Đầu.</t>
+          <t>&lt;color=#ffd12f&gt;[Hỗ Trợ Đồng Hành]&lt;/color&gt; Triệu hồi Mortefi để tung chiêu Resonance Liberation khi Năng Lượng Khúc Tụ đã đầy, kích hoạt Kỹ Năng Khởi Đầu.</t>
         </is>
       </c>
     </row>
@@ -14217,7 +14217,7 @@
       <c r="M208" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Resonance Liberation]&lt;/color&gt;
-Cooldown chiêu của Resonance Liberation - Vươn Tới Chân Trời giảm {0}.
+Thời gian hồi chiêu của Resonance Liberation - Vươn Tới Chân Trời giảm {0}.
 Kích hoạt Resonance Liberation - Vươn Tới Chân Trời sẽ hồi phục toàn bộ HP cho Bravo.</t>
         </is>
       </c>
@@ -14353,8 +14353,8 @@
       <c r="M210" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Forte Circuit]&lt;/color&gt;
-Forte Circuit - Trở Về Từ Tro Tàn giờ đây sẽ tung ra Giai Đoạn Mid-air Attack 1 về phía trước, sau đó triệu hồi Mỏ Neo từ trên cao đâm xuống mục tiêu, gây sát thương bằng {0} sát thương của Trở Về Từ Tro Tàn. Phạm vi tấn công được mở rộng.
-Kích hoạt Trở Về Từ Tro Tàn không còn kết thúc trạng thái Aflame nữa.</t>
+Forte Circuit - Trở Về Từ Tro Tàn giờ đây sẽ tung ra Giai Đoạn Mid-air Attack 1 về phía trước, sau đó triệu hồi Mỏ Neo từ trên cao đâm xuống mục tiêu, gây DMG bằng {0} DMG của Trở Về Từ Tro Tàn. Phạm vi tấn công được mở rộng.
+Kích hoạt Trở Về Từ Tro Tàn không còn kết thúc trạng thái Bốc Cháy nữa.</t>
         </is>
       </c>
     </row>
@@ -14492,11 +14492,11 @@
       <c r="M212" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Forte Circuit]&lt;/color&gt;
-Khi một trong các điều kiện sau được đáp ứng, triệu hồi Mắt Vực Sâu tại vị trí mục tiêu để hút các mục tiêu lân cận trong {0} giây, gây Fusion DMG bằng {2} Attack của Brant &lt;SapTag=1&gt;{1}&lt;/SapTag&gt; {Cus:Sap,S=lần P=lần SapTag=1}.
-- Khi Giai đoạn 4 hoặc 5 của Forte Circuit - Trở Về Từ Tro Tàn gây sát thương.
-- Khi Giai đoạn 2 của Resonance Skill - Neo Đã Buông! gây sát thương.
-- Khi Giai đoạn 1, 2 hoặc 3 của Đòn Mid-air Attack gây sát thương.
-- Khi Heavy Attack - Khúc Rhapsody trúng mục tiêu.</t>
+Khi một trong các điều kiện sau được đáp ứng, triệu hồi Mắt Vực Sâu tại vị trí mục tiêu để hút các mục tiêu lân cận trong {0} giây, gây Sát Thương Fusion bằng {2} ATK của Brant &lt;SapTag=1&gt;{1}&lt;/SapTag&gt; {Cus:Sap,S=lần P=lần SapTag=1}.
+- Khi Giai đoạn 4 hoặc 5 của Forte Circuit - Trở Về Từ Tro Tàn gây DMG.
+- Khi Giai đoạn 2 của Resonance Skill - Neo Đã Buông! gây DMG.
+- Khi Giai đoạn 1, 2 hoặc 3 của Đòn ATK Giữa Không gây DMG.
+- Khi Đòn Heavy Attack - Khúc Rhapsody trúng mục tiêu.</t>
         </is>
       </c>
     </row>
@@ -14563,7 +14563,7 @@
       <c r="M213" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Forte Circuit]&lt;/color&gt;
-Summon Mắt Vực Sâu để kéo các mục tiêu gần đó vào khi đáp ứng điều kiện nhất định.</t>
+Triệu hồi Mắt Vực Sâu để kéo các mục tiêu gần đó vào khi đáp ứng điều kiện nhất định.</t>
         </is>
       </c>
     </row>
@@ -14631,8 +14631,8 @@
       <c r="M214" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Basic Attack]&lt;/color&gt;
-Đánh trúng mục tiêu bằng Basic Attack trên không sẽ tạo ra &lt;SapTag=0&gt;{0}&lt;/SapTag&gt; Mỏ Neo Nổ {Cus:Sap,S=Mỏ P=Mỏ SapTag=0}, gây Fusion DMG bằng {9} Attack của Brant, kích hoạt mỗi {1} giây. Mỏ Neo Nổ tồn tại trên chiến trường trong {2} giây. Khi thời gian tồn tại của Mỏ Neo Nổ kết thúc hoặc sau khi kích hoạt Forte Circuit - Returned from Ashes, tất cả Mỏ Neo Nổ sẽ phát nổ, gây Fusion DMG bằng {4} Attack của Brant &lt;SapTag=3&gt;{3}&lt;/SapTag&gt; {Cus:Sap,S=lần P=lần SapTag=3}, được tính là Sát Thương Basic Attack.
-Tối đa {5} Mỏ Neo Nổ có thể tồn tại đồng thời. Mỗi lần tạo ra Mỏ Neo Nổ, Brant nhận thêm {6} Fusion DMG trong {7} giây, có thể cộng dồn tối đa {8} lần.</t>
+Đánh trúng mục tiêu bằng Đòn Basic Attack trên không sẽ tạo ra &lt;SapTag=0&gt;{0}&lt;/SapTag&gt; Mỏ Neo Nổ {Cus:Sap,S=Mỏ P=Mỏ SapTag=0}, gây Sát Thương Fusion bằng {9} ATK của Brant, kích hoạt mỗi {1} giây. Mỏ Neo Nổ tồn tại trên chiến trường trong {2} giây. Khi thời gian tồn tại của Mỏ Neo Nổ kết thúc hoặc sau khi kích hoạt Forte Circuit - Returned from Ashes, tất cả Mỏ Neo Nổ sẽ phát nổ, gây Sát Thương Fusion bằng {4} ATK của Brant &lt;SapTag=3&gt;{3}&lt;/SapTag&gt; {Cus:Sap,S=lần P=lần SapTag=3}, được tính là Sát Thương Basic Attack.
+Tối đa {5} Mỏ Neo Nổ có thể tồn tại đồng thời. Mỗi lần tạo ra Mỏ Neo Nổ, Brant nhận thêm {6} Sát Thương Fusion trong {7} giây, có thể cộng dồn tối đa {8} lần.</t>
         </is>
       </c>
     </row>
@@ -14699,7 +14699,7 @@
       <c r="M215" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Basic Attack]&lt;/color&gt;
-Basic Attack trên không tạo ra Mỏ Neo Nổ, mang lại hiệu ứng cộng thêm Fusion DMG và gây sát thương khi phát nổ.</t>
+Basic Attack trên không tạo ra Mỏ Neo Nổ, mang lại hiệu ứng cộng thêm Sát Thương Fusion và gây DMG khi phát nổ.</t>
         </is>
       </c>
     </row>
@@ -14766,7 +14766,7 @@
       <c r="M216" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Forte Circuit]&lt;/color&gt;
-Khi ở trên không, Brant miễn nhiễm với gián đoạn và nhận thêm {0} Fusion DMG. Hiệu ứng tăng Fusion DMG sẽ bị loại bỏ sau {1} giây khi Brant tiếp đất.</t>
+Khi ở trên không, Brant miễn nhiễm với gián đoạn và nhận thêm {0} Sát Thương Fusion. Hiệu ứng tăng Sát Thương Fusion sẽ bị loại bỏ sau {1} giây khi Brant tiếp đất.</t>
         </is>
       </c>
     </row>
@@ -14833,7 +14833,7 @@
       <c r="M217" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Forte Circuit]&lt;/color&gt;
-Khi ở trên không, Brant miễn nhiễm với gián đoạn và nhận thêm Fusion DMG Bonus.</t>
+Khi ở trên không, Brant miễn nhiễm với gián đoạn và nhận thêm Tăng Sát Thương Fusion.</t>
         </is>
       </c>
     </row>
@@ -14900,7 +14900,7 @@
       <c r="M218" t="inlineStr">
         <is>
           <t>&lt;color=Highlight&gt;[Forte Circuit]&lt;/color&gt;
-Resonance Skill - Khiêu Vũ Cùng Sói và Resonance Skill - Khiêu Vũ Cùng Sói: Cao Trào sẽ triệu hồi Bầy Sói để gây thêm sát thương.</t>
+Resonance Skill - Khiêu Vũ Cùng Sói và Resonance Skill - Khiêu Vũ Cùng Sói: Climax summon Wolfpack to deal extra DMG.</t>
         </is>
       </c>
     </row>
@@ -14967,7 +14967,7 @@
       <c r="M219" t="inlineStr">
         <is>
           <t>&lt;color=Highlight&gt;[Resonance Liberation]&lt;/color&gt;
-Glory Ngọn Lửa có Cooldown chiêu ngắn hơn và gây Sát Thương cao hơn.</t>
+Vinh Quang Ngọn Lửa có Thời gian hồi chiêu ngắn hơn và gây Sát Thương cao hơn.</t>
         </is>
       </c>
     </row>
@@ -15034,7 +15034,7 @@
       <c r="M220" t="inlineStr">
         <is>
           <t>&lt;color=Highlight&gt;[Forte Circuit]&lt;/color&gt;
-Resonance Skill - Khiêu Vũ Cùng Sói và Resonance Skill - Khiêu Vũ Cùng Sói: Cao Trào sẽ giảm Fusion RES của mục tiêu khi trúng đích.</t>
+Resonance Skill - Khiêu Vũ Cùng Sói và Resonance Skill - Khiêu Vũ Cùng Sói: Cao Trào sẽ giảm Kháng Fusion của mục tiêu khi trúng đích.</t>
         </is>
       </c>
     </row>
@@ -15102,8 +15102,8 @@
       <c r="M221" t="inlineStr">
         <is>
           <t>&lt;color=Highlight&gt;[Forte Circuit]&lt;/color&gt;
-- Kích hoạt Hellstride trong Threshold State sẽ gây thêm Fusion DMG bằng &lt;color=Highlight&gt;{0}&lt;/color&gt; Attack của Galbrena (được tính là sát thương Heavy Attack) và làm choáng kẻ địch xung quanh trong &lt;color=Highlight&gt;{1}s&lt;/color&gt;. Lần sử dụng Basic Attack tiếp theo sẽ kích hoạt Giai Đoạn 3 và 4 của Basic Attack và hồi &lt;color=Highlight&gt;{2}&lt;/color&gt; điểm Sinflame.
-- Mỗi lần kích hoạt Hellstride sẽ tăng &lt;color=Highlight&gt;{3}&lt;/color&gt; Fusion DMG trong &lt;color=Highlight&gt;{4}s&lt;/color&gt;, có thể cộng dồn tối đa &lt;color=Highlight&gt;{5}&lt;/color&gt; lần.</t>
+- Kích hoạt Hellstride trong Trạng Thái Ngưỡng sẽ gây thêm DMG Hợp Nhất bằng &lt;color=Highlight&gt;{0}&lt;/color&gt; ATK của Galbrena (được tính là DMG Đòn Heavy Attack) và làm choáng kẻ địch xung quanh trong &lt;color=Highlight&gt;{1} giây&lt;/color&gt;. Lần sử dụng Đòn Basic Attack tiếp theo sẽ kích hoạt Giai Đoạn 3 và 4 của Đòn Basic Attack và hồi &lt;color=Highlight&gt;{2}&lt;/color&gt; điểm Sinflame.
+- Mỗi lần kích hoạt Hellstride sẽ tăng &lt;color=Highlight&gt;{3}&lt;/color&gt; DMG Hợp Nhất trong &lt;color=Highlight&gt;{4} giây&lt;/color&gt;, có thể cộng dồn tối đa &lt;color=Highlight&gt;{5}&lt;/color&gt; lần.</t>
         </is>
       </c>
     </row>
@@ -15378,8 +15378,8 @@
       <c r="M225" t="inlineStr">
         <is>
           <t>&lt;color=Highlight&gt;[Resonance Liberation]&lt;/color&gt;
-- Cooldown chiêu của Resonance Liberation - Giải Tội Hỏa Ngục giảm &lt;color=Highlight&gt;{0}s&lt;/color&gt;.
-- Khi sử dụng kỹ năng, mỗi &lt;color=Highlight&gt;{1}&lt;/color&gt; điểm Ngọn Sinflame Lỗi hoặc Ngọn Purging Flame sẽ hồi phục thêm &lt;color=Highlight&gt;{2}&lt;/color&gt; điểm Ngọn Lửa Dư Dả. Mỗi điểm Ngọn Sinflame Lỗi hoặc Ngọn Purging Flame sẽ tăng &lt;color=Highlight&gt;{3}&lt;/color&gt; Hệ Số Sát Thương trong &lt;color=Highlight&gt;{4}s&lt;/color&gt;.</t>
+- Thời gian hồi chiêu của Resonance Liberation - Giải Tội Hỏa Ngục giảm &lt;color=Highlight&gt;{0} giây&lt;/color&gt;.
+- Khi sử dụng kỹ năng, mỗi &lt;color=Highlight&gt;{1}&lt;/color&gt; điểm Ngọn Lửa Tội Lỗi hoặc Ngọn Lửa Thanh Tẩy sẽ hồi phục thêm &lt;color=Highlight&gt;{2}&lt;/color&gt; điểm Ngọn Lửa Dư Dả. Mỗi điểm Ngọn Lửa Tội Lỗi hoặc Ngọn Lửa Thanh Tẩy sẽ tăng &lt;color=Highlight&gt;{3}&lt;/color&gt; Hệ Số Sát Thương trong &lt;color=Highlight&gt;{4} giây&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -15447,7 +15447,7 @@
       <c r="M226" t="inlineStr">
         <is>
           <t>&lt;color=Highlight&gt;[Resonance Liberation]&lt;/color&gt;
-- Cooldown chiêu của Resonance Liberation được giảm.
+- Thời gian hồi chiêu của Resonance Liberation được giảm.
 - Khi sử dụng Resonance Liberation, phục hồi thêm Lửa Dư và tăng Sát Thương gây ra.</t>
         </is>
       </c>
@@ -15515,7 +15515,7 @@
       <c r="M227" t="inlineStr">
         <is>
           <t>&lt;color=Highlight&gt;[Forte Circuit]&lt;/color&gt;
-Dạng Ác Quỷ tăng &lt;color=Highlight&gt;{0}&lt;/color&gt; Sát Thương Kỹ Năng Dư Âm, tăng tổng sát thương của Basic Attack và Đòn Heavy Attack thêm &lt;color=Highlight&gt;{1}&lt;/color&gt;, và tăng Attack Speed thêm &lt;color=Highlight&gt;{2}&lt;/color&gt;.</t>
+Dạng Ác Quỷ tăng &lt;color=Highlight&gt;{0}&lt;/color&gt; Sát Thương Kỹ Năng Dư Âm, tăng tổng DMG của Đòn Basic Attack và Đòn Heavy Attack thêm &lt;color=Highlight&gt;{1}&lt;/color&gt;, và tăng Tốc Độ Tấn Công thêm &lt;color=Highlight&gt;{2}&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -15649,7 +15649,7 @@
       <c r="M229" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Basic Attack]&lt;/color&gt;
-Trong thời gian ngắn sau khi thực hiện Heavy Attack: Lời Thương Xót, Heavy Attack: Messenger Tử Thần hoặc Dodge Counter, sử dụng Normal Attack sẽ kích hoạt Săn Lùng Hoang Dã, gây Electro DMG tương đương {0} Attack của Calcharo, được tính là sát thương Resonance Liberation.</t>
+Trong thời gian ngắn sau khi thực hiện Heavy Attack: Lời Thương Xót, Heavy Attack: Sứ Giả Tử Thần hoặc Dodge Counter Tránh, sử dụng Normal Attack sẽ kích hoạt Săn Lùng Hoang Dã, gây DMG Electro tương đương {0} ATK của Calcharo, được tính là DMG Resonance Liberation.</t>
         </is>
       </c>
     </row>
@@ -15716,7 +15716,7 @@
       <c r="M230" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Basic Attack]&lt;/color&gt;
-Trong thời gian ngắn sau khi thực hiện Heavy Attack: Lời Thương Xót, Heavy Attack: Messenger Tử Thần và Dodge Counter, sử dụng Normal Attack sẽ kích hoạt Săn Lùng Hoang Dã, gây Electro DMG, được tính là sát thương Resonance Liberation.</t>
+Trong thời gian ngắn sau khi thực hiện Heavy Attack: Lời Thương Xót, Heavy Attack: Sứ Giả Tử Thần và Dodge Counter Tránh, sử dụng Normal Attack sẽ kích hoạt Săn Lùng Hoang Dã, gây DMG Electro, được tính là DMG Resonance Liberation.</t>
         </is>
       </c>
     </row>
@@ -15784,8 +15784,8 @@
       <c r="M231" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Resonance Skill]&lt;/color&gt;
-- Khi sử dụng Resonance Skill, Calcharo sẽ triệu hồi thêm một bóng ma của chính mình, gây Electro DMG bằng {0} Attack của cậu ta. Sát Thương này được tính là Sát Thương Resonance Liberation, và cậu ta nhận được 3 tầng Tàn Nhẫn.
-- Heavy Attack: Lòng Thương Xót giờ có thể thực hiện thông qua Basic Attack. Mỗi lần Calcharo thực hiện Heavy Attack: Lòng Thương Xót hoặc Heavy Attack: Messenger Tử Thần, cậu ta sẽ nhận thêm {1} Electro DMG Bonus trong {2} giây, tối đa {3} lần cộng dồn.</t>
+- Khi sử dụng Resonance Skill, Calcharo sẽ triệu hồi thêm một bóng ma của chính mình, gây Sát Thương Electro bằng {0} ATK của cậu ta. Sát Thương này được tính là Sát Thương Resonance Liberation, và cậu ta nhận được 3 tầng Tàn Nhẫn.
+- Đòn Heavy Attack: Lòng Thương Xót giờ có thể thực hiện thông qua Đòn Basic Attack. Mỗi lần Calcharo thực hiện Đòn Heavy Attack: Lòng Thương Xót hoặc Đòn Heavy Attack: Sứ Giả Tử Thần, cậu ta sẽ nhận thêm {1} Tăng Sát Thương Electro trong {2} giây, tối đa {3} lần cộng dồn.</t>
         </is>
       </c>
     </row>
@@ -15853,8 +15853,8 @@
       <c r="M232" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Resonance Skill]&lt;/color&gt;
-- Khi sử dụng Resonance Skill, Calcharo gây thêm Electro DMG. Sát Thương này được tính là Sát Thương Resonance Liberation, và cậu ta nhận được 3 tầng Tàn Nhẫn.
-- Heavy Attack: Lòng Thương Xót giờ có thể thực hiện thông qua Basic Attack. Calcharo nhận Electro DMG Bonus mỗi khi thực hiện Heavy Attack: Lòng Thương Xót hoặc Heavy Attack: Messenger Tử Thần.</t>
+- Khi sử dụng Resonance Skill, Calcharo gây thêm Sát Thương Electro. Sát Thương này được tính là Sát Thương Resonance Liberation, và cậu ta nhận được 3 tầng Tàn Nhẫn.
+- Đòn Heavy Attack: Mercy can now be performed through Basic Attack. Calcharo gains Electro DMG Bonus with each Heavy Attack: Mercy or Heavy Attack: Death Messenger performed.</t>
         </is>
       </c>
     </row>
@@ -15925,8 +15925,8 @@
         <is>
           <t>&lt;color=#c49e55&gt;[Resonance Liberation]&lt;/color&gt;
 Khi ở trạng thái kích hoạt bởi Resonance Liberation, Calcharo nhận được các hiệu ứng sau:
-- Increase khả năng kháng làm gián đoạn.
-- Increase tốc độ Basic Attack thêm {0}.
+- Tăng khả năng kháng làm gián đoạn.
+- Tăng tốc độ Basic Attack thêm {0}.
 - Kích hoạt Resonance Skill sẽ kéo dài thời gian trạng thái thêm {1} giây.</t>
         </is>
       </c>
@@ -15998,8 +15998,8 @@
         <is>
           <t>&lt;color=#c49e55&gt;[Resonance Liberation]&lt;/color&gt;
 Khi ở trạng thái kích hoạt bởi Resonance Liberation, Calcharo nhận được các hiệu ứng sau:
-- Increase khả năng kháng làm gián đoạn.
-- Increase tốc độ Basic Attack.
+- Tăng khả năng kháng làm gián đoạn.
+- Tăng tốc độ Basic Attack.
 - Kích hoạt Resonance Skill sẽ kéo dài thời gian trạng thái.</t>
         </is>
       </c>
@@ -16068,8 +16068,8 @@
       <c r="M235" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Resonance Skill]&lt;/color&gt;
-- Thực hiện Heavy Attack: Mercy hoặc Heavy Attack: Death Messenger sẽ tạo ra 1 tầng Bloodlust.
-- Khi có 4 tầng Bloodlust, Resonance Skill sẽ được thay thế bằng Extreme Measures, gây Electro DMG bằng {0} Attack của Calcharo, được tính là Sát Thương Resonance Liberation.</t>
+- Thực hiện Đòn Heavy Attack: Mercy hoặc Đòn Heavy Attack: Death Messenger sẽ tạo ra 1 tầng Bloodlust.
+- Khi có 4 tầng Bloodlust, Resonance Skill sẽ được thay thế bằng Extreme Measures, gây Sát Thương Electro bằng {0} ATK của Calcharo, được tính là Sát Thương Resonance Liberation.</t>
         </is>
       </c>
     </row>
@@ -16137,8 +16137,8 @@
       <c r="M236" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Resonance Skill]&lt;/color&gt;
-- Thực hiện Heavy Attack: Mercy hoặc Heavy Attack: Death Messenger sẽ tạo ra 1 tầng Bloodlust.
-- Khi có 4 tầng Bloodlust, Resonance Skill sẽ được thay thế bằng Extreme Measures, gây Electro DMG, được tính là Sát Thương Resonance Liberation.</t>
+- Thực hiện Đòn Heavy Attack: Mercy hoặc Đòn Heavy Attack: Death Messenger sẽ tạo ra 1 tầng Bloodlust.
+- Khi có 4 tầng Bloodlust, Resonance Skill sẽ được thay thế bằng Extreme Measures, gây Sát Thương Electro, được tính là Sát Thương Resonance Liberation.</t>
         </is>
       </c>
     </row>
@@ -16205,7 +16205,7 @@
       <c r="M237" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Basic Attack]&lt;/color&gt;
-Thực hiện Heavy Attack: Mercy và Heavy Attack: Death Messenger sẽ giảm Cooldown chiêu của Resonance Skill và Resonance Liberation đi {0} giây và hồi {1} Resonance Energy.</t>
+Thực hiện Đòn Heavy Attack: Mercy và Đòn Heavy Attack: Death Messenger sẽ giảm Thời gian hồi chiêu của Resonance Skill và Resonance Liberation đi {0} giây và hồi {1} Resonance Energy.</t>
         </is>
       </c>
     </row>
@@ -16272,7 +16272,7 @@
       <c r="M238" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Basic Attack]&lt;/color&gt;
-Thực hiện Heavy Attack: Mercy và Heavy Attack: Death Messenger sẽ giảm Cooldown chiêu của Resonance Skill và Resonance Liberation, đồng thời hồi phục Resonance Energy.</t>
+Thực hiện Đòn Heavy Attack: Mercy and Heavy Attack: Death Messenger reduces Resonance Skill and Resonance Liberation Thời gian hồi and restores Resonance Energy.</t>
         </is>
       </c>
     </row>
@@ -16337,7 +16337,7 @@
       </c>
       <c r="M239" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Companion's Aid]&lt;/color&gt; Summon Yinlin để thi triển Resonance Liberation khi Năng Lượng Khúc Tấu đạt tối đa, kích hoạt Intro Skill.</t>
+          <t>&lt;color=#ffd12f&gt;[Hỗ Trợ Đồng Hành]&lt;/color&gt; Triệu hồi Yinlin để thi triển Resonance Liberation khi Năng Lượng Khúc Tấu đạt tối đa, kích hoạt Kỹ Năng Khởi Động.</t>
         </is>
       </c>
     </row>
@@ -16402,7 +16402,7 @@
       </c>
       <c r="M240" t="inlineStr">
         <is>
-          <t>Concerto: Yinlin</t>
+          <t>Khúc Concerto: Yinlin</t>
         </is>
       </c>
     </row>
@@ -16467,7 +16467,7 @@
       </c>
       <c r="M241" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Companion's Aid]&lt;/color&gt; Summon Yuanwu để thi triển Resonance Liberation khi Năng Lượng Khúc Tấu đạt tối đa, kích hoạt Intro Skill.</t>
+          <t>&lt;color=#ffd12f&gt;[Hỗ Trợ Đồng Hành]&lt;/color&gt; Triệu hồi Yuanwu để thi triển Resonance Liberation khi Năng Lượng Khúc Tấu đạt tối đa, kích hoạt Kỹ Năng Khởi Động.</t>
         </is>
       </c>
     </row>
@@ -16532,7 +16532,7 @@
       </c>
       <c r="M242" t="inlineStr">
         <is>
-          <t>Concerto: Yuanwu</t>
+          <t>Khúc Concerto: Yuanwu</t>
         </is>
       </c>
     </row>
@@ -16599,7 +16599,7 @@
       <c r="M243" t="inlineStr">
         <is>
           <t>&lt;color=Highlight&gt;[Basic Attack]&lt;/color&gt;
-- Basic Attack giờ bắt đầu từ Stage 3, tăng đáng kể Sát Thương và có những hiệu ứng đặc biệt.</t>
+- Basic Attack giờ bắt đầu từ Giai Đoạn 3, tăng đáng kể Sát Thương và có những hiệu ứng đặc biệt.</t>
         </is>
       </c>
     </row>
@@ -16666,7 +16666,7 @@
       <c r="M244" t="inlineStr">
         <is>
           <t>&lt;color=Highlight&gt;[Basic Attack]&lt;/color&gt;
-Trong &lt;color=Highlight&gt;Resonance Skill&lt;/color&gt; - Incarnation, Attack được tăng nhẹ, và sử dụng Basic Attack hoặc Resonance Skill sẽ hồi phục Forte Gauge.</t>
+Trong &lt;color=Highlight&gt;Resonance Skill&lt;/color&gt; - Hóa Thân, ATK được tăng nhẹ, và sử dụng Basic Attack hoặc Resonance Skill sẽ hồi phục Forte Gauge.</t>
         </is>
       </c>
     </row>
@@ -16731,7 +16731,7 @@
       </c>
       <c r="M245" t="inlineStr">
         <is>
-          <t>&lt;color=#c49e55&gt;[Dodge]&lt;/color&gt; Dodge thành công sẽ kích hoạt Loong's Reign, tạo ra vùng trì trệ. Tấn Công Bổ Sung Spectro tăng thêm {1} trong {2} giây. Hiệu ứng này chỉ có thể kích hoạt mỗi {3} giây một lần. Jinhsi phục hồi {0} Thanh Forte cho mỗi mục tiêu bị ảnh hưởng bởi hiệu ứng trì trệ.</t>
+          <t>&lt;color=#c49e55&gt;[Né Tránh]&lt;/color&gt; Né tránh thành công sẽ kích hoạt Loong's Reign, tạo ra vùng trì trệ. Tấn Công Bổ Sung Spectro tăng thêm {1} trong {2} giây. Hiệu ứng này chỉ có thể kích hoạt mỗi {3} giây một lần. Jinhsi phục hồi {0} Thanh Forte cho mỗi mục tiêu bị ảnh hưởng bởi hiệu ứng trì trệ.</t>
         </is>
       </c>
     </row>
@@ -16797,8 +16797,8 @@
       </c>
       <c r="M246" t="inlineStr">
         <is>
-          <t>&lt;color=Highlight&gt;[Dodge]&lt;/color&gt;
-Dodge thành công sẽ hồi phục Forte Gauge và kích hoạt Long Chúa Trị Vì, tăng đáng kể Spectro DMG.</t>
+          <t>&lt;color=Highlight&gt;[Né Tránh]&lt;/color&gt;
+Né tránh thành công sẽ hồi phục Forte Gauge và kích hoạt Long Chúa Trị Vì, tăng đáng kể Sát Thương Spectro.</t>
         </is>
       </c>
     </row>
@@ -16933,10 +16933,10 @@
       </c>
       <c r="M248" t="inlineStr">
         <is>
-          <t>&lt;color=Highlight&gt;[Heavy Attack]&lt;/color&gt;
-- Khi Prowess đạt &lt;color=Highlight&gt;{0}&lt;/color&gt; điểm, giữ Basic Attack hoặc {Cus:Ipt,Touch=tap PC=click Gamepad=press} Basic Attack khi đang ở trên không để tiêu hao &lt;color=Highlight&gt;{0}&lt;/color&gt; điểm Prowess và thi triển Heavy Attack - Thét Sấm: Thượng Đoạn.
-- Thi triển Heavy Attack - Thét Sấm: Thượng Đoạn sẽ hồi phục thêm &lt;color=Highlight&gt;{1}&lt;/color&gt; điểm Thăng Hoa và tăng &lt;color=Highlight&gt;{2}&lt;/color&gt; Sát Thương trong &lt;color=Highlight&gt;{4}s&lt;/color&gt;, có thể chồng chất lên đến &lt;color=Highlight&gt;{3}&lt;/color&gt; lần.
-- Khi Prowess đạt &lt;color=Highlight&gt;{0}&lt;/color&gt; điểm, giữ Basic Attack sau khi thi triển Stage 2 của Basic Attack để tiêu hao &lt;color=Highlight&gt;{0}&lt;/color&gt; điểm Prowess và thi triển Heavy Attack - Thét Sấm: Lùi Bước.</t>
+          <t>&lt;color=Highlight&gt;[Đòn Heavy Attack]&lt;/color&gt;
+- Khi Prowess đạt &lt;color=Highlight&gt;{0}&lt;/color&gt; điểm, giữ Basic Attack hoặc {Cus: Ipt,Touch=tap PC=click Gamepad=press} Basic Attack while in mid-air to consume &lt;color=Highlight&gt;{0}&lt;/color&gt; points of Prowess and cast Heavy Attack - Thunderoar: Uppercut.
+- Casting Heavy Attack - Thunderoar: Uppercut additionally restores &lt;color=Highlight&gt;{1}&lt;/color&gt; Ascendancy and grants &lt;color=Highlight&gt;{2}&lt;/color&gt; DMG Bonus for &lt;color=Highlight&gt;{4}s&lt;/color&gt;, stacking up to &lt;color=Highlight&gt;{3}&lt;/color&gt; times.
+- When Prowess reaches &lt;color=Highlight&gt;{0}&lt;/color&gt; points, hold Basic Attack after casting Basic Attack Stage 2 to consume &lt;color=Highlight&gt;{0}&lt;/color&gt; points of Prowess and cast Heavy Attack - Thunderoar: Backstep.</t>
         </is>
       </c>
     </row>
@@ -17003,9 +17003,9 @@
       </c>
       <c r="M249" t="inlineStr">
         <is>
-          <t>&lt;color=Highlight&gt;[Heavy Attack]&lt;/color&gt;
-- Giữ Basic Attack hoặc {Cus:Ipt,Touch=tap PC=click Gamepad=press} Basic Attack khi đang ở trên không để thi triển Heavy Attack - Thét Sấm: Thượng Đoạn, tiêu hao Prowess và nhận hiệu ứng tăng cường.
-- Giữ Basic Attack sau khi thi triển Stage 2 của Basic Attack để thi triển Heavy Attack - Thét Sấm: Lùi Bước, tiêu hao Prowess.</t>
+          <t>&lt;color=Highlight&gt;[Đòn Heavy Attack]&lt;/color&gt;
+- Giữ Basic Attack hoặc {Cus: Ipt,Touch=tap PC=click Gamepad=press} Basic Attack while in mid-air to cast Heavy Attack - Thunderoar: Uppercut at the cost of Prowess and gain enhancements.
+- Hold Basic Attack after casting Basic Attack Stage 2 to cast Heavy Attack - Thunderoar: Backstep at the cost of Prowess.</t>
         </is>
       </c>
     </row>
@@ -17076,11 +17076,11 @@
       <c r="M250" t="inlineStr">
         <is>
           <t>&lt;color=Highlight&gt;[Resonance Liberation]&lt;/color&gt;
-- Thi triển Heavy Attack - Thét Sấm: Thượng Đoạn hoặc Heavy Attack - Thét Sấm: Lùi Bước sẽ tạo ra &lt;color=Highlight&gt;&lt;SapTag=0&gt;{0}&lt;/SapTag&gt;&lt;/color&gt; {Cus:Sap,S=điểm P=điểm} Daystar, có thể chồng chất lên đến &lt;color=Highlight&gt;{1}&lt;/color&gt; lần.
+- Thi triển Đòn Heavy Attack - Thét Sấm: Thượng Đoạn hoặc Đòn Heavy Attack - Thét Sấm: Lùi Bước sẽ tạo ra &lt;color=Highlight&gt;&lt;SapTag=0&gt;{0}&lt;/SapTag&gt;&lt;/color&gt; {Cus:Sap,S=điểm P=điểm} Daystar, có thể chồng chất lên đến &lt;color=Highlight&gt;{1}&lt;/color&gt; lần.
 - Khi có ít nhất &lt;color=Highlight&gt;{2}&lt;/color&gt; điểm Daystar, sử dụng Resonance Liberation để tiêu hao &lt;color=Highlight&gt;{2}&lt;/color&gt; điểm Daystar và thi triển Kiếm Bùng Nổ.
-- Sau khi hoàn thành &lt;color=Highlight&gt;{3}&lt;/color&gt; giai đoạn của Kiếm Bùng Nổ với ít nhất &lt;color=Highlight&gt;{4}&lt;/color&gt; điểm Daystar còn lại, sử dụng Resonance Liberation lần nữa để tiêu hao &lt;color=Highlight&gt;{2}&lt;/color&gt; điểm Daystar và thi triển Eclipse.
-- Kiếm Bùng Nổ và Nhật Thực gây Electro DMG tương đương &lt;color=Highlight&gt;{5}&lt;/color&gt; và &lt;color=Highlight&gt;{6}&lt;/color&gt; Attack của Augusta, được tính là Sát Thương Heavy Attack.
-- Thi triển Heavy Attack - Thét Sấm: Thượng Đoạn, Heavy Attack - Thét Sấm: Lùi Bước, Kiếm Bùng Nổ và Nhật Thực sẽ hồi phục thêm &lt;color=Highlight&gt;{7}&lt;/color&gt; điểm Resonance Energy và tăng &lt;color=Highlight&gt;{8}&lt;/color&gt; Sát Thương trong &lt;color=Highlight&gt;{10}s&lt;/color&gt;, có thể chồng chất lên đến &lt;color=Highlight&gt;{9}&lt;/color&gt; lần.</t>
+- Sau khi hoàn thành &lt;color=Highlight&gt;{3}&lt;/color&gt; giai đoạn của Kiếm Bùng Nổ với ít nhất &lt;color=Highlight&gt;{4}&lt;/color&gt; điểm Daystar còn lại, sử dụng Resonance Liberation lần nữa để tiêu hao &lt;color=Highlight&gt;{2}&lt;/color&gt; điểm Daystar và thi triển Nhật Thực.
+- Kiếm Bùng Nổ và Nhật Thực gây Sát Thương Electro tương đương &lt;color=Highlight&gt;{5}&lt;/color&gt; và &lt;color=Highlight&gt;{6}&lt;/color&gt; ATK của Augusta, được tính là Sát Thương Đòn Heavy Attack.
+- Thi triển Đòn Heavy Attack - Thét Sấm: Thượng Đoạn, Đòn Heavy Attack - Thét Sấm: Lùi Bước, Kiếm Bùng Nổ và Nhật Thực sẽ hồi phục thêm &lt;color=Highlight&gt;{7}&lt;/color&gt; điểm Resonance Energy và tăng &lt;color=Highlight&gt;{8}&lt;/color&gt; Sát Thương trong &lt;color=Highlight&gt;{10} giây&lt;/color&gt;, có thể chồng chất lên đến &lt;color=Highlight&gt;{9}&lt;/color&gt; lần.</t>
         </is>
       </c>
     </row>
@@ -17149,9 +17149,9 @@
       <c r="M251" t="inlineStr">
         <is>
           <t>&lt;color=Highlight&gt;[Resonance Liberation]&lt;/color&gt;
-- Thi triển Heavy Attack - Thét Sấm: Thượng Đoạn hoặc Heavy Attack - Thét Sấm: Lùi Bước sẽ tạo ra Daystar.
+- Thi triển Đòn Heavy Attack - Thét Sấm: Thượng Đoạn hoặc Đòn Heavy Attack - Thét Sấm: Lùi Bước sẽ tạo ra Daystar.
 - Sử dụng Resonance Liberation để thi triển Kiếm Bùng Nổ hoặc Nhật Thực, tiêu hao Daystar.
-- Heavy Attack - Thét Sấm: Thượng Đoạn, Heavy Attack - Thét Sấm: Lùi Bước, Kiếm Bùng Nổ và Nhật Thực đều được tăng cường.</t>
+- Đòn Heavy Attack - Thét Sấm: Thượng Đoạn, Đòn Heavy Attack - Thét Sấm: Lùi Bước, Kiếm Bùng Nổ và Nhật Thực đều được tăng cường.</t>
         </is>
       </c>
     </row>
@@ -17220,7 +17220,7 @@
         <is>
           <t>&lt;color=Highlight&gt;[Resonance Liberation]&lt;/color&gt;
 - Tổng Sát Thương của Resonance Liberation - Kiếm Lời Thề Vĩnh Hằng, Resonance Liberation - Vinh Quang Như Mặt Trời, Vinh Quang Như Mặt Trời - Hạ Sinh Từ Ánh Dương và Vinh Quang Như Mặt Trời - Người Bảo Hộ Vĩnh Cửu tăng thêm &lt;color=Highlight&gt;{0}&lt;/color&gt;.
-- Cooldown chiêu của Resonance Liberation - Kiếm Lời Thề Vĩnh Hằng giảm &lt;color=Highlight&gt;{1}&lt;/color&gt; giây. Khi sử dụng kỹ năng này, phục hồi &lt;color=Highlight&gt;{2}&lt;/color&gt; Năng Lượng Thăng Hoa.</t>
+- Thời gian hồi chiêu của Resonance Liberation - Kiếm Lời Thề Vĩnh Hằng giảm &lt;color=Highlight&gt;{1}&lt;/color&gt; giây. Khi sử dụng kỹ năng này, phục hồi &lt;color=Highlight&gt;{2}&lt;/color&gt; Năng Lượng Thăng Hoa.</t>
         </is>
       </c>
     </row>
@@ -17289,7 +17289,7 @@
         <is>
           <t>&lt;color=Highlight&gt;[Resonance Liberation]&lt;/color&gt;
 - Tổng Sát Thương của Resonance Liberation được tăng lên.
-- Cooldown chiêu của Resonance Liberation - Kiếm Lời Thề Vĩnh Hằng được giảm. Khi sử dụng kỹ năng này, phục hồi toàn bộ Năng Lượng Thăng Hoa.</t>
+- Thời gian hồi chiêu của Resonance Liberation - Kiếm Lời Thề Vĩnh Hằng được giảm. Khi sử dụng kỹ năng này, phục hồi toàn bộ Năng Lượng Thăng Hoa.</t>
         </is>
       </c>
     </row>
@@ -17356,7 +17356,7 @@
       <c r="M254" t="inlineStr">
         <is>
           <t>&lt;color=Highlight&gt;[Forte Circuit]&lt;/color&gt;
-Mỗi lần nhận Shield sẽ tăng &lt;color=Highlight&gt;{0}&lt;/color&gt; Sát Thương Heavy Attack và tăng Giảm Sát Thương thêm &lt;color=Highlight&gt;{1}&lt;/color&gt; trong &lt;color=Highlight&gt;{3}s&lt;/color&gt;, tối đa &lt;color=Highlight&gt;{2}&lt;/color&gt; tầng.</t>
+Mỗi lần nhận Khiên sẽ tăng &lt;color=Highlight&gt;{0}&lt;/color&gt; Sát Thương Heavy Attack và tăng Giảm Sát Thương thêm &lt;color=Highlight&gt;{1}&lt;/color&gt; trong &lt;color=Highlight&gt;{3} giây&lt;/color&gt;, tối đa &lt;color=Highlight&gt;{2}&lt;/color&gt; tầng.</t>
         </is>
       </c>
     </row>
@@ -17423,7 +17423,7 @@
       <c r="M255" t="inlineStr">
         <is>
           <t>&lt;color=Highlight&gt;[Forte Circuit]&lt;/color&gt;
-Mỗi lần nhận Shield sẽ tăng Sát Thương Heavy Attack và tăng Giảm Sát Thương.</t>
+Mỗi lần nhận Khiên sẽ tăng Sát Thương Heavy Attack và tăng Giảm Sát Thương.</t>
         </is>
       </c>
     </row>
@@ -17553,7 +17553,7 @@
       </c>
       <c r="M257" t="inlineStr">
         <is>
-          <t>&lt;color=#c49e55&gt;[Special Enhancement]&lt;/color&gt; Hệ số sát thương của Tổ Gió tăng thêm {0} và hiệu ứng kéo tăng thêm {1}.</t>
+          <t>&lt;color=#c49e55&gt;[Tăng Cường Đặc Biệt]&lt;/color&gt; Hệ số DMG của Tổ Gió tăng thêm {0} và hiệu ứng kéo tăng thêm {1}.</t>
         </is>
       </c>
     </row>
@@ -17683,7 +17683,7 @@
       </c>
       <c r="M259" t="inlineStr">
         <is>
-          <t>&lt;color=#c49e55&gt;[Heavy Attack]&lt;/color&gt; Heavy Attack - Song Gió tạo ra Trường Gió thẳng đứng, gây {0} Sát Thương và kéo kẻ địch vào.</t>
+          <t>&lt;color=#c49e55&gt;[Heavy Attack]&lt;/color&gt; Heavy Attack - Khúc Ca Gió tạo ra Trường Gió thẳng đứng, gây {0} Sát Thương và kéo kẻ địch vào.</t>
         </is>
       </c>
     </row>
@@ -17749,8 +17749,8 @@
       </c>
       <c r="M260" t="inlineStr">
         <is>
-          <t>&lt;color=#c49e55&gt;[Forte Circuit]&lt;/color&gt; &lt;color=#c49e55&gt;[Effect Replacecement]&lt;/color&gt; Mỗi khi tạo ra "Trường Gió", tích lũy 1 điểm "Năng Lượng Gió", tối đa 4 điểm.
-"Mid-air Attack: Giải Phóng Feather" sẽ tiêu thụ toàn bộ điểm "Năng Lượng Gió", mỗi điểm tăng phạm vi và sát thương của giai đoạn cuối lần lượt là {0} và {1}.</t>
+          <t>&lt;color=#c49e55&gt;[Forte Circuit]&lt;/color&gt; &lt;color=#c49e55&gt;[Thay Thế Hiệu Ứng]&lt;/color&gt; Mỗi khi tạo ra "Trường Gió", tích lũy 1 điểm "Năng Lượng Gió", tối đa 4 điểm.
+"Tấn Công Giữa Không: Giải Phóng Lông Vũ" sẽ tiêu thụ toàn bộ điểm "Năng Lượng Gió", mỗi điểm tăng phạm vi và DMG của giai đoạn cuối lần lượt là {0} và {1}.</t>
         </is>
       </c>
     </row>
@@ -17815,7 +17815,7 @@
       </c>
       <c r="M261" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Forte Circuit]&lt;/color&gt; Đặt lại Cooldown chiêu của Skill Cộng hưởng sau khi sử dụng "Attack giữa không: Giải phóng Lông vũ".</t>
+          <t>&lt;color=#ffd12f&gt;[Forte Circuit]&lt;/color&gt; Reset Thời gian hồi chiêu của Kỹ năng Cộng hưởng sau khi sử dụng "Tấn công giữa không: Giải phóng Lông vũ".</t>
         </is>
       </c>
     </row>
@@ -17885,10 +17885,10 @@
       <c r="M262" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Basic Attack]&lt;/color&gt;
-Đòn Attack trên không không tiêu hao STA.
+Đòn ATK trên không không tiêu hao STA.
 Đánh trúng mục tiêu bằng Basic Attack sẽ mang lại các hiệu ứng sau:
 - Hồi {0} Resonance Energy.
-- Attack tăng thêm {1} trong {2} giây, có thể cộng dồn tối đa {3} lần.</t>
+- ATK tăng thêm {1} trong {2} giây, có thể cộng dồn tối đa {3} lần.</t>
         </is>
       </c>
     </row>
@@ -17955,7 +17955,7 @@
       <c r="M263" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Basic Attack]&lt;/color&gt;
-Đòn Attack trên không không tiêu hao STA, và Basic Attack hồi phục Resonance Energy cũng như tăng Attack.</t>
+Đòn ATK trên không không tiêu hao STA, và Basic Attack hồi phục Resonance Energy cũng như tăng ATK.</t>
         </is>
       </c>
     </row>
@@ -18022,7 +18022,7 @@
       <c r="M264" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Basic Attack]&lt;/color&gt;
-Khi Mistcloak Dash được kích hoạt, Aero DMG tăng thêm {0} trong {1} giây, tối đa {2} tầng, và đòn Basic Attack tiếp theo sẽ gây thêm sát thương và tạo Sương Mù phía trước.</t>
+Khi Mistcloak Dash được kích hoạt, Sát Thương Aero tăng thêm {0} trong {1} giây, tối đa {2} tầng, và đòn Basic Attack tiếp theo sẽ gây thêm DMG và tạo Sương Mù phía trước.</t>
         </is>
       </c>
     </row>
@@ -18156,7 +18156,7 @@
       <c r="M266" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Basic Attack]&lt;/color&gt;
-Khi Giai Đoạn {0} Basic Attack và Dodge Counter gây sát thương, sẽ tạo thêm Gate of Quandary - Interval ở phía trước trong {1} giây và &lt;SapTag=2&gt;{2}&lt;/SapTag&gt; viên {Cus:Sap,S=Sương P=Sương SapTag=2} Sương Mù.</t>
+Khi Giai Đoạn {0} Basic Attack và Dodge Counter Tránh gây sát thương, sẽ tạo thêm Gate of Quandary - Interval ở phía trước trong {1} giây và &lt;SapTag=2&gt;{2}&lt;/SapTag&gt; viên {Cus:Sap,S=Sương P=Sương SapTag=2} Sương Mù.</t>
         </is>
       </c>
     </row>
@@ -18223,7 +18223,7 @@
       <c r="M267" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Basic Attack]&lt;/color&gt;
-Basic Attack và Dodge Counter nhận được những cải tiến đặc biệt.</t>
+Basic Attack và Dodge Counter Tránh nhận được những cải tiến đặc biệt.</t>
         </is>
       </c>
     </row>
@@ -18290,7 +18290,7 @@
       <c r="M268" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Forte Circuit]&lt;/color&gt;
-Khi đạn xuyên qua Cánh Gate of Quandary và Đạn Sương Mù trúng mục tiêu, Aalto nhận được {0} tầng Xoáy Nước trong {1} giây. Xoáy Nước giảm &lt;SapTag=3&gt;{3}&lt;/SapTag&gt; {Cus:Sap,S=tầng P=tầng SapTag=3} mỗi {2} giây. Khi đạt {4} tầng Xoáy Nước, tất cả tầng sẽ bị xóa để gây Aero DMG bằng {6} Tấn Công của Aalto &lt;SapTag=5&gt;{5}&lt;/SapTag&gt; {Cus:Sap,S=lần P=lần SapTag=5}.</t>
+Khi đạn xuyên qua Cánh Cổng Băn Khoăn và Đạn Sương Mù trúng mục tiêu, Aalto nhận được {0} tầng Xoáy Nước trong {1} giây. Xoáy Nước giảm &lt;SapTag=3&gt;{3}&lt;/SapTag&gt; {Cus:Sap,S=tầng P=tầng SapTag=3} mỗi {2} giây. Khi đạt {4} tầng Xoáy Nước, tất cả tầng sẽ bị xóa để gây Sát Thương Aero bằng {6} ATK của Aalto &lt;SapTag=5&gt;{5}&lt;/SapTag&gt; {Cus:Sap,S=lần P=lần SapTag=5}.</t>
         </is>
       </c>
     </row>
@@ -18357,7 +18357,7 @@
       <c r="M269" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Forte Circuit]&lt;/color&gt;
-Khi đạn xuyên qua Cánh Gate of Quandary và Đạn Sương Mù trúng mục tiêu, Aalto nhận được tăng cường đặc biệt.</t>
+Khi đạn xuyên qua Cánh Cổng Băn Khoăn và Đạn Sương Mù trúng mục tiêu, Aalto nhận được tăng cường đặc biệt.</t>
         </is>
       </c>
     </row>
@@ -18556,7 +18556,7 @@
       </c>
       <c r="M272" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Companion's Aid]&lt;/color&gt; Summon Aalto để tung chiêu Resonance Liberation khi Năng Lượng Khúc Tụ đã đầy, kích hoạt Kỹ Năng Khởi Đầu.</t>
+          <t>&lt;color=#ffd12f&gt;[Hỗ Trợ Đồng Hành]&lt;/color&gt; Triệu hồi Aalto để tung chiêu Resonance Liberation khi Năng Lượng Khúc Tụ đã đầy, kích hoạt Kỹ Năng Khởi Đầu.</t>
         </is>
       </c>
     </row>
@@ -18686,7 +18686,7 @@
       </c>
       <c r="M274" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Resonance Liberation]&lt;/color&gt; &lt;color=#ffd12f&gt;[Effect Replacement]&lt;/color&gt; Emerald Storm: Đoạn Kết không còn yêu cầu Độ Quyết Tâm; gây thêm 100% Sát Thương và giảm 50% Resonance Energy cần thiết. Sau khi kích hoạt Resonance Liberation, Jiyan sẽ không còn vào chế độ Qingloong mà thay vào đó kích nổ những "Ngọn Giáo Bão" gần đó. Mỗi "Ngọn Giáo Bão" kích nổ sẽ tăng thêm 50% Sát Thương gây ra.</t>
+          <t>&lt;color=#ffd12f&gt;[Resonance Liberation]&lt;/color&gt; &lt;color=#ffd12f&gt;[Thay Thế Hiệu Ứng]&lt;/color&gt; Bão Ngọc Lục Bảo: Đoạn Kết không còn yêu cầu Độ Quyết Tâm; gây thêm 100% Sát Thương và giảm 50% Resonance Energy cần thiết. Sau khi kích hoạt Resonance Liberation, Jiyan sẽ không còn vào chế độ Thanh Long mà thay vào đó kích nổ những "Ngọn Giáo Bão" gần đó. Mỗi "Ngọn Giáo Bão" kích nổ sẽ tăng thêm 50% Sát Thương gây ra.</t>
         </is>
       </c>
     </row>
@@ -18751,7 +18751,7 @@
       </c>
       <c r="M275" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Resonance Liberation]&lt;/color&gt; &lt;color=#ffd12f&gt;[Effect Replacement]&lt;/color&gt; Tăng cường hiệu ứng phóng giáo. Sát Thương gây ra tăng theo số lượng "Ngọn Giáo Bão" hiện có. Jiyan sẽ không còn vào chế độ Qingloong.</t>
+          <t>&lt;color=#ffd12f&gt;[Resonance Liberation]&lt;/color&gt; &lt;color=#ffd12f&gt;[Thay Thế Hiệu Ứng]&lt;/color&gt; Tăng cường hiệu ứng phóng giáo. Sát Thương gây ra tăng theo số lượng "Ngọn Giáo Bão" hiện có. Jiyan sẽ không còn vào chế độ Thanh Long.</t>
         </is>
       </c>
     </row>
@@ -18816,7 +18816,7 @@
       </c>
       <c r="M276" t="inlineStr">
         <is>
-          <t>&lt;color=#c49e55&gt;[Resonance Liberation]&lt;/color&gt; &lt;color=#c49e55&gt;[Effect Enhancement]&lt;/color&gt; Resonance Energy cần cho Resonance Liberation giảm {0}, hiệu ứng kéo được tăng cường. "Thương Qingloong" gây thêm {1} Sát Thương.</t>
+          <t>&lt;color=#c49e55&gt;[Resonance Liberation]&lt;/color&gt; &lt;color=#c49e55&gt;[Tăng Cường Hiệu Ứng]&lt;/color&gt; Resonance Energy cần cho Resonance Liberation giảm {0}, hiệu ứng kéo được tăng cường. "Thương Thanh Long" gây thêm {1} Sát Thương.</t>
         </is>
       </c>
     </row>
@@ -18881,7 +18881,7 @@
       </c>
       <c r="M277" t="inlineStr">
         <is>
-          <t>&lt;color=#c49e55&gt;[Resonance Liberation]&lt;/color&gt; &lt;color=#c49e55&gt;[Effect Enhancement]&lt;/color&gt; Resonance Liberation cần ít Resonance Energy hơn. Chế độ Qingloong còn tạo thêm hiệu ứng kéo mạnh và gây Sát Thương cao hơn đáng kể.</t>
+          <t>&lt;color=#c49e55&gt;[Resonance Liberation]&lt;/color&gt; &lt;color=#c49e55&gt;[Tăng Cường Hiệu Ứng]&lt;/color&gt; Resonance Liberation cần ít Resonance Energy hơn. Chế độ Thanh Long còn tạo thêm hiệu ứng kéo mạnh và gây Sát Thương cao hơn đáng kể.</t>
         </is>
       </c>
     </row>
@@ -18946,7 +18946,7 @@
       </c>
       <c r="M278" t="inlineStr">
         <is>
-          <t>&lt;color=#c49e55&gt;[Resonance Skill]&lt;/color&gt; Resonance Skill của Jiyan triệu hồi {0} "Giáo Tempest" gần kẻ địch, mỗi "Giáo Tempest" gây {1} điểm Sát Thương. "Giáo Tempest" tồn tại trong {2} giây. Có thể kích nổ "Giáo Tempest" trên chiến trường bằng Kỹ Năng Thăng Hoa của Jiyan (nếu đã mở khóa). Những "Giáo Tempest" không bị kích nổ sẽ tự động phát nổ sau {3} giây, mỗi cái gây {4} điểm Sát Thương.</t>
+          <t>&lt;color=#c49e55&gt;[Resonance Skill]&lt;/color&gt; Resonance Skill của Jiyan triệu hồi {0} "Giáo Bão Tố" gần kẻ địch, mỗi "Giáo Bão Tố" gây {1} điểm Sát Thương. "Giáo Bão Tố" tồn tại trong {2} giây. Có thể kích nổ "Giáo Bão Tố" trên chiến trường bằng Kỹ Năng Thăng Hoa của Jiyan (nếu đã mở khóa). Những "Giáo Bão Tố" không bị kích nổ sẽ tự động phát nổ sau {3} giây, mỗi cái gây {4} điểm Sát Thương.</t>
         </is>
       </c>
     </row>
@@ -19011,7 +19011,7 @@
       </c>
       <c r="M279" t="inlineStr">
         <is>
-          <t>&lt;color=#c49e55&gt;[Resonance Skill]&lt;/color&gt; Resonance Skill triệu hồi "Giáo Tempest" tấn công kẻ địch.</t>
+          <t>&lt;color=#c49e55&gt;[Resonance Skill]&lt;/color&gt; Resonance Skill triệu hồi "Giáo Bão Tố" tấn công kẻ địch.</t>
         </is>
       </c>
     </row>
@@ -19076,7 +19076,7 @@
       </c>
       <c r="M280" t="inlineStr">
         <is>
-          <t>&lt;color=#c49e55&gt;[Basic Attack]&lt;/color&gt; Basic Attack 5 triệu hồi {0} "Tempest Spear" rơi ngẫu nhiên quanh kẻ địch, gây {1} sát thương. "Tempest Spear" tồn tại trong {2} giây. Có thể kích hoạt bằng kỹ năng đặc biệt của Jiyan (nếu đã mở khóa) để gây sát thương nổ. Sau {3} giây, "Tempest Spear" chưa kích hoạt sẽ tự động phát nổ, mỗi cái gây {4} sát thương.</t>
+          <t>&lt;color=#c49e55&gt;[Basic Attack]&lt;/color&gt; Basic Attack 5 triệu hồi {0} "Ngọn Giáo Bão Tố" rơi ngẫu nhiên quanh kẻ địch, gây {1} DMG. "Ngọn Giáo Bão Tố" tồn tại trong {2} giây. Có thể kích hoạt bằng kỹ năng đặc biệt của Jiyan (nếu đã mở khóa) để gây DMG nổ. Sau {3} giây, "Ngọn Giáo Bão Tố" chưa kích hoạt sẽ tự động phát nổ, mỗi cái gây {4} DMG.</t>
         </is>
       </c>
     </row>
@@ -19141,7 +19141,7 @@
       </c>
       <c r="M281" t="inlineStr">
         <is>
-          <t>&lt;color=#c49e55&gt;[Basic Attack]&lt;/color&gt; Basic Attack 5 triệu hồi "Tempest Spear" tấn công kẻ địch.</t>
+          <t>&lt;color=#c49e55&gt;[Basic Attack]&lt;/color&gt; Basic Attack 5 triệu hồi "Ngọn Giáo Bão Tố" tấn công kẻ địch.</t>
         </is>
       </c>
     </row>
@@ -19206,7 +19206,7 @@
       </c>
       <c r="M282" t="inlineStr">
         <is>
-          <t>&lt;color=#c49e55&gt;[Resonance Liberation]&lt;/color&gt; Jiyan có thể kích nổ "Giáo Tempest" bằng cách vào Qingloong Mode hoặc kích hoạt Resonance Liberation được tăng cường. Mỗi "Giáo Tempest" kích nổ sẽ giảm Cooldown chiêu Resonance Skill {0} giây và gây ra một vụ nổ nhỏ, gây {1} điểm sát thương.</t>
+          <t>&lt;color=#c49e55&gt;[Resonance Liberation]&lt;/color&gt; Jiyan có thể kích nổ "Giáo Bão Tố" bằng cách vào Chế Độ Thanh Long hoặc kích hoạt Resonance Liberation được tăng cường. Mỗi "Giáo Bão Tố" kích nổ sẽ giảm Thời gian hồi chiêu Resonance Skill {0} giây và gây ra một vụ nổ nhỏ, gây {1} điểm DMG.</t>
         </is>
       </c>
     </row>
@@ -19271,7 +19271,7 @@
       </c>
       <c r="M283" t="inlineStr">
         <is>
-          <t>&lt;color=#c49e55&gt;[Resonance Liberation]&lt;/color&gt; Resonance Liberation kích nổ "Giáo Bão", những "Giáo Bão" đã kích nổ sẽ giảm Cooldown chiêu Resonance Skill.</t>
+          <t>&lt;color=#c49e55&gt;[Resonance Liberation]&lt;/color&gt; Resonance Liberation kích nổ "Giáo Bão", những "Giáo Bão" đã kích nổ sẽ giảm Thời gian hồi chiêu Resonance Skill.</t>
         </is>
       </c>
     </row>
@@ -19336,7 +19336,7 @@
       </c>
       <c r="M284" t="inlineStr">
         <is>
-          <t>&lt;color=#c49e55&gt;[Resonance Skill]&lt;/color&gt; Sau khi Jiyan sử dụng Resonance Skill, Aero DMG của cậu tăng {0} trong {1} giây. Nếu Jiyan đang ở Qingloong Mode, thời gian duy trì sẽ kéo dài thêm {2} giây; nếu không, đòn tấn công tiếp theo trong {3} giây sẽ được thay thế bằng "Thương Qingloong".</t>
+          <t>&lt;color=#c49e55&gt;[Resonance Skill]&lt;/color&gt; Sau khi Jiyan sử dụng Resonance Skill, DMG Aero của cậu tăng {0} trong {1} giây. Nếu Jiyan đang ở Chế Độ Thanh Long, thời gian duy trì sẽ kéo dài thêm {2} giây; nếu không, đòn tấn công tiếp theo trong {3} giây sẽ được thay thế bằng "Thương Thanh Long".</t>
         </is>
       </c>
     </row>
@@ -19401,7 +19401,7 @@
       </c>
       <c r="M285" t="inlineStr">
         <is>
-          <t>&lt;color=#c49e55&gt;[Resonance Skill]&lt;/color&gt; Aero DMG tăng lên sau khi sử dụng Resonance Skill, và đòn tấn công tiếp theo sẽ được thay thế bằng "Thương Qingloong"; nếu Jiyan đang ở Qingloong Mode, thời gian duy trì sẽ được kéo dài.</t>
+          <t>&lt;color=#c49e55&gt;[Resonance Skill]&lt;/color&gt; DMG Aero tăng lên sau khi sử dụng Resonance Skill, và đòn tấn công tiếp theo sẽ được thay thế bằng "Thương Thanh Long"; nếu Jiyan đang ở Chế Độ Thanh Long, thời gian duy trì sẽ được kéo dài.</t>
         </is>
       </c>
     </row>
@@ -19466,7 +19466,7 @@
       </c>
       <c r="M286" t="inlineStr">
         <is>
-          <t>&lt;color=#c49e55&gt;[Resonance Skill]&lt;/color&gt; Nếu Phản Đòn Chí được kích hoạt thành công, trong vòng Hồi Lộ Forte tiếp theo: Luân Hồi Chí Nguyên, Tấn Công của Resonator tăng {0}, tối đa {1} tầng trong {2} giây.</t>
+          <t>&lt;color=#c49e55&gt;[Resonance Skill]&lt;/color&gt; Nếu Phản Đòn Chí được kích hoạt thành công, trong vòng Hồi Lộ Forte tiếp theo: Luân Hồi Chí Nguyên, ATK của Resonator tăng {0}, tối đa {1} tầng trong {2} giây.</t>
         </is>
       </c>
     </row>
@@ -19531,7 +19531,7 @@
       </c>
       <c r="M287" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Companion's Aid]&lt;/color&gt; Summon Jianxin để tung chiêu Resonance Liberation khi Năng Lượng Khúc Tụ đã đầy, kích hoạt Kỹ Năng Khởi Đầu.</t>
+          <t>&lt;color=#ffd12f&gt;[Hỗ Trợ Đồng Hành]&lt;/color&gt; Triệu hồi Jianxin để tung chiêu Resonance Liberation khi Năng Lượng Khúc Tụ đã đầy, kích hoạt Kỹ Năng Khởi Đầu.</t>
         </is>
       </c>
     </row>
@@ -19666,10 +19666,10 @@
       <c r="M289" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Resonance Skill]&lt;/color&gt;
-Cooldown chiêu của Resonance Skill - Cơn Gió Thức Tỉnh giảm {0}, và Rover: Aero miễn nhiễm với gián đoạn khi sử dụng kỹ năng.
-Sử dụng Đòn Mid-air Attack - Dance Mây Mưa và Basic Attack Giữa Không tăng sát thương Resonance Skill lên {1} trong {2} giây, có thể chồng chất tối đa {3} lần.
-Phạm vi tấn công của Dance Mây Mưa và Basic Attack Giữa Không được mở rộng, và chúng gây &lt;SapTag=4&gt;{4}&lt;/SapTag&gt; {Cus:Sap,S=lớp P=lớp} Erosion Aero lên mục tiêu khi trúng đòn.
-Khi Rover: Aero tấn công mục tiêu và gây Erosion Aero, mỗi lớp Erosion sẽ gây thêm Aero DMG bằng {5} Attack của Rover: Aero, được tính là sát thương Resonance Skill.</t>
+Thời gian hồi chiêu của Resonance Skill - Cơn Gió Thức Tỉnh giảm {0}, và Rover: Aero miễn nhiễm với gián đoạn khi sử dụng kỹ năng.
+Sử dụng Đòn ATK Giữa Không - Vũ Điệu Mây Mưa và Đòn Cơ Bản Giữa Không tăng DMG Resonance Skill lên {1} trong {2} giây, có thể chồng chất tối đa {3} lần.
+Phạm vi tấn công của Vũ Điệu Mây Mưa và Đòn Cơ Bản Giữa Không được mở rộng, và chúng gây &lt;SapTag=4&gt;{4}&lt;/SapTag&gt; {Cus:Sap,S=lớp P=lớp} Xói Mòn Aero lên mục tiêu khi trúng đòn.
+Khi Rover: Aero tấn công mục tiêu và gây Xói Mòn Aero, mỗi lớp Xói Mòn sẽ gây thêm DMG Aero bằng {5} ATK của Rover: Aero, được tính là DMG Resonance Skill.</t>
         </is>
       </c>
     </row>
@@ -19736,7 +19736,7 @@
       <c r="M290" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Resonance Skill]&lt;/color&gt;
-Cooldown chiêu của Resonance Skill được rút ngắn, và thi triển kỹ năng sẽ miễn nhiễm với gián đoạn. Mid-air Attack được tăng cường đặc biệt. Gây Erosion Aero sẽ gây thêm sát thương.</t>
+Thời gian hồi chiêu của Resonance Skill được rút ngắn, và thi triển kỹ năng sẽ miễn nhiễm với gián đoạn. Tấn Công Giữa Không được tăng cường đặc biệt. Gây Erosion Aero sẽ gây thêm sát thương.</t>
         </is>
       </c>
     </row>
@@ -19806,10 +19806,10 @@
       <c r="M291" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Resonance Skill]&lt;/color&gt;
-Sử dụng Resonance Skill - Thức Tỉnh Phong, Resonance Skill - Đoạn Trời Rơi và Heavy Attack - Phong Kiếm sẽ nhận được &lt;SapTag=0&gt;{0}&lt;/SapTag&gt; {Cus:Sap,S=luồng P=luồng SapTag=0} String Gió Lam, tối đa &lt;SapTag=1&gt;{1}&lt;/SapTag&gt; {Cus:Sap,S=luồng P=luồng SapTag=1}.
-Nếu String Gió chưa đầy, {Cus:Ipt,Touch=tap PC=press Gamepad=press} Normal Attack ngay sau khi dùng Basic Attack trên không để tiêu hao &lt;SapTag=2&gt;{2}&lt;/SapTag&gt; {Cus:Sap,S=luồng P=luồng SapTag=2} String Gió Lam và thi triển Resonance Skill - Lưu Chuyển Tự Do: Bản Chất.
-Lưu Chuyển - Bản Chất: Skill này không tiêu hao String Gió, và sát thương gây ra bằng {3} sát thương của Resonance Skill - Lưu Chuyển Tự Do.
-Sử dụng Lưu Chuyển khi có String Gió sẽ tiêu hao toàn bộ luồng String Gió Lam, mỗi luồng tăng sát thương gây ra thêm {4}.</t>
+Sử dụng Resonance Skill - Thức Tỉnh Phong, Resonance Skill - Đoạn Trời Rơi và Đòn Nặng - Phong Kiếm sẽ nhận được &lt;SapTag=0&gt;{0}&lt;/SapTag&gt; {Cus:Ipt,Touch=tap PC=press Gamepad=press} Chuỗi Gió Lam, tối đa &lt;SapTag=1&gt;{1}&lt;/SapTag&gt; {Cus:Sap,S=luồng P=luồng SapTag=1}.
+Nếu Chuỗi Gió chưa đầy, {Cus:Ipt,Touch=nhấn PC=nhấn Gamepad=nhấn} Đòn Normal Attack ngay sau khi dùng Đòn Tấn Công Cơ Bản trên không để tiêu hao &lt;SapTag=2&gt;{2}&lt;/SapTag&gt; {Cus:Sap,S=luồng P=luồng SapTag=2} Chuỗi Gió Lam và thi triển Resonance Skill - Lưu Chuyển Tự Do: Bản Chất.
+Lưu Chuyển - Bản Chất: Kỹ năng này không tiêu hao Chuỗi Gió, và DMG gây ra bằng {3} DMG của Resonance Skill - Lưu Chuyển Tự Do.
+Sử dụng Lưu Chuyển khi có Chuỗi Gió sẽ tiêu hao toàn bộ luồng Chuỗi Gió Lam, mỗi luồng tăng DMG gây ra thêm {4}.</t>
         </is>
       </c>
     </row>
@@ -19876,7 +19876,7 @@
       <c r="M292" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Resonance Skill]&lt;/color&gt;
-Sử dụng Resonance Skill - Thức Tỉnh Phong, Resonance Skill - Đoạn Trời Rơi và Heavy Attack - Phong Kiếm sẽ tích lũy năng lượng đặc biệt. Năng lượng này có thể thay thế Chuỗi Gió để thi triển Resonance Skill - Lưu Chuyển Tự Do hoặc tăng sát thương của Lưu Chuyển.</t>
+Sử dụng Resonance Skill - Thức Tỉnh Phong, Resonance Skill - Đoạn Trời Rơi và Đòn Nặng - Phong Kiếm sẽ tích lũy năng lượng đặc biệt. Năng lượng này có thể thay thế Chuỗi Gió để thi triển Resonance Skill - Lưu Chuyển Tự Do hoặc tăng sát thương của Lưu Chuyển.</t>
         </is>
       </c>
     </row>
@@ -19943,7 +19943,7 @@
       <c r="M293" t="inlineStr">
         <is>
           <t>&lt;color=Highlight&gt;[Resonance Skill]&lt;/color&gt;
-Sử dụng Resonance Skill - Cơn Gió Thức Tỉnh, Resonance Skill - Đoạn Kiếm Từ Trời Rơi và Heavy Attack - Lưỡi Gió Sắc sẽ nhận được một hiệu ứng đặc biệt, có thể thay thế Windstring để sử dụng Resonance Skill - Flow Tự Do: Bản Chất sau khi thực hiện Đòn Mid-air Attack, hoặc tiêu hao để tăng Sát Thương gây ra bởi Resonance Skill - Flow Tự Do.</t>
+Sử dụng Resonance Skill - Cơn Gió Thức Tỉnh, Resonance Skill - Đoạn Kiếm Từ Trời Rơi và Đòn Heavy Attack - Lưỡi Gió Sắc sẽ nhận được một hiệu ứng đặc biệt, có thể thay thế Dây Gió để sử dụng Resonance Skill - Dòng Chảy Tự Do: Bản Chất sau khi thực hiện Đòn Tấn Công Giữa Không Trung, hoặc tiêu hao để tăng Sát Thương gây ra bởi Resonance Skill - Dòng Chảy Tự Do.</t>
         </is>
       </c>
     </row>
@@ -20016,7 +20016,7 @@
 Crit. Rate tăng thêm {0}. Resonance Skill - Lưu Chuyển Tự Do trở thành Resonance Skill - Lưu Chuyển Tự Do: Siêu Cấp.
 Lưu Chuyển - Siêu Cấp:
 - Giai đoạn {1} hút mục tiêu xung quanh và tung thêm 2 đòn tấn công.
-- Khi thi triển kỹ năng, Rover: Aero miễn nhiễm với gián đoạn, phạm vi tấn công được mở rộng. Đánh trúng mục tiêu sẽ gây hiệu ứng &lt;SapTag=2&gt;{2}&lt;/SapTag&gt; {Cus:Sap,S=lớp P=lớp SapTag=2} Erosion Gió.</t>
+- Khi thi triển kỹ năng, Rover: Aero miễn nhiễm với gián đoạn, phạm vi tấn công được mở rộng. Đánh trúng mục tiêu sẽ gây hiệu ứng &lt;SapTag=2&gt;{2}&lt;/SapTag&gt; {Cus:Sap,S=lớp P=lớp SapTag=2} Aero Erosion.</t>
         </is>
       </c>
     </row>
@@ -20083,7 +20083,7 @@
       <c r="M295" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Resonance Skill]&lt;/color&gt;
-Resonance Skill - Flow Tự Do được tăng cường đặc biệt.</t>
+Resonance Skill - Dòng Chảy Tự Do được tăng cường đặc biệt.</t>
         </is>
       </c>
     </row>
@@ -20150,7 +20150,7 @@
       <c r="M296" t="inlineStr">
         <is>
           <t>&lt;color=Highlight&gt;[Resonance Skill]&lt;/color&gt;
-Resonance Skill - Flow Tự Do được tăng cường.</t>
+Resonance Skill - Dòng Chảy Tự Do được tăng cường.</t>
         </is>
       </c>
     </row>
@@ -20218,8 +20218,8 @@
       <c r="M297" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Resonance Skill]&lt;/color&gt;
-Resonance Skill - Cooldown chiêu của Đoạn Kết Từ Trời giảm {0} và nhận được &lt;SapTag=1&gt;{1}&lt;/SapTag&gt; {Cus:Sap,S=điểm P=điểm SapTag=1} Tần Số. Khi bị tấn công, Rover: Aero có thể tiêu hao {2} HP hiện tại để thi triển Đoạn Kết Từ Trời.
-Thi triển Resonance Skill - Đoạn Kết Từ Trời sẽ tạo một Lá Chắn không thể chồng chất, tương đương {3} HP tối đa của Rover: Aero trong {4} giây. Skill này có thể tiếp nối bằng Mid-air Attack - Dance Mây Động.</t>
+Resonance Skill - Thời gian hồi chiêu của Đoạn Kết Từ Trời giảm {0} và nhận được &lt;SapTag=1&gt;{1}&lt;/SapTag&gt; {Cus:Sap,S=điểm P=điểm SapTag=1} Tần Số. Khi bị tấn công, Rover: Aero có thể tiêu hao {2} HP hiện tại để thi triển Đoạn Kết Từ Trời.
+Thi triển Resonance Skill - Đoạn Kết Từ Trời sẽ tạo một Lá Chắn không thể chồng chất, tương đương {3} HP tối đa của Rover: Aero trong {4} giây. Kỹ năng này có thể tiếp nối bằng Tấn Công Giữa Không - Vũ Điệu Mây Động.</t>
         </is>
       </c>
     </row>
@@ -20354,8 +20354,8 @@
       <c r="M299" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Resonance Liberation]&lt;/color&gt;
-Resonance Liberation - Bão Omega gây thêm Aero DMG bằng {1} Tấn Công của Rover: Aero &lt;SapTag=0&gt;{0}&lt;/SapTag&gt; {Cus:Sap,S=lần P=lần SapTag=0} và giảm Aero RES của mục tiêu {2} trong {3} giây khi trúng đích. Hiệu ứng này không thể chồng chất.
-Sau khi thi triển Bão Omega, Outro Skill của Rover: Aero được tăng cường: Đánh trúng mục tiêu sẽ tăng số tầng Aero Erosion tối đa mục tiêu có thể nhận thêm {4} trong {5} giây.</t>
+Resonance Liberation - Bão Omega gây thêm DMG Aero bằng {1} ATK của Rover: Aero &lt;SapTag=0&gt;{0}&lt;/SapTag&gt; {Cus:Sap,S=lần P=lần SapTag=0} và giảm Kháng Aero của mục tiêu {2} trong {3} giây khi trúng đích. Hiệu ứng này không thể chồng chất.
+Sau khi thi triển Bão Omega, Kỹ Năng Outro của Rover: Aero được tăng cường: Đánh trúng mục tiêu sẽ tăng số tầng Aero Erosion tối đa mục tiêu có thể nhận thêm {4} trong {5} giây.</t>
         </is>
       </c>
     </row>
@@ -20556,7 +20556,7 @@
       <c r="M302" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Resonance Liberation]&lt;/color&gt;
-Ciaccona nhận thêm {0} Tăng Sát Thương Resonance Liberation. Resonance Liberation còn giảm Aero RES của mục tiêu {1} trong {2} giây.</t>
+Ciaccona nhận thêm {0} Tăng Sát Thương Resonance Liberation. Resonance Liberation còn giảm Kháng Aero của mục tiêu {1} trong {2} giây.</t>
         </is>
       </c>
     </row>
@@ -20623,7 +20623,7 @@
       <c r="M303" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Resonance Liberation]&lt;/color&gt;
-Tăng thưởng sát thương Resonance Liberation. Resonance Liberation giảm Aero RES của mục tiêu khi trúng đích.</t>
+Tăng thưởng DMG Resonance Liberation. Resonance Liberation giảm Kháng Aero của mục tiêu khi trúng đích.</t>
         </is>
       </c>
     </row>
@@ -20691,8 +20691,8 @@
       <c r="M304" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Forte Circuit]&lt;/color&gt;
-Khi Ciaccona tiếp đất sau khi tung Basic Attack Stage 4, tạo ra Trường Gió Zephyr gây {0} Aero DMG lên các mục tiêu gần đó.
-Khi Ciaccona tung Basic Attack Stage 2 hoặc Resonance Skill trên mặt đất, Basic Attack tiếp theo của cô sẽ trở thành Basic Attack Stage 4. Khi thi triển Resonance Liberation, Ciaccona có thể di chuyển tự do. Hệ Số Sát Thương của Bản Giao Hưởng: Tonic được tăng lên, và kỹ năng này gây cả Aero Erosion lẫn Spectro Frazzle lên mục tiêu.</t>
+Khi Ciaccona tiếp đất sau khi tung Đòn Basic Attack Giai Đoạn 4, tạo ra Trường Gió Zephyr gây {0} Sát Thương Aero lên các mục tiêu gần đó.
+Khi Ciaccona tung Đòn Basic Attack Giai Đoạn 2 hoặc Resonance Skill trên mặt đất, Đòn Basic Attack tiếp theo của cô sẽ trở thành Đòn Basic Attack Giai Đoạn 4. Khi thi triển Resonance Liberation, Ciaccona có thể di chuyển tự do. Hệ Số Sát Thương của Bản Giao Hưởng: Tonic được tăng lên, và kỹ năng này gây cả Aero Erosion lẫn Spectro Frazzle lên mục tiêu.</t>
         </is>
       </c>
     </row>
@@ -20760,8 +20760,8 @@
       <c r="M305" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Forte Circuit]&lt;/color&gt;
-Khi Ciaccona tiếp đất sau khi tung Basic Attack 4, tạo ra Trường Gió Zephyr gây sát thương diện rộng.
-Khi Ciaccona tung Basic Attack Stage 2 hoặc Resonance Skill trên mặt đất, Basic Attack tiếp theo của cô sẽ trở thành Basic Attack 4. Cô có thể di chuyển tự do khi thi triển Resonance Liberation.</t>
+Khi Ciaccona tiếp đất sau khi tung Đòn Basic Attack 4, tạo ra Trường Gió Zephyr gây sát thương diện rộng.
+Khi Ciaccona tung Đòn Basic Attack Giai Đoạn 2 hoặc Resonance Skill trên mặt đất, Đòn Basic Attack tiếp theo của cô sẽ trở thành Đòn Basic Attack 4. Cô có thể di chuyển tự do khi thi triển Resonance Liberation.</t>
         </is>
       </c>
     </row>
@@ -20831,8 +20831,8 @@
         <is>
           <t>&lt;color=#c49e55&gt;[Heavy Attack]&lt;/color&gt;
 Khi Ciaccona sử dụng Heavy Attack - Quadruple Downbeat:
-Summon Ensemble Sylph để thực hiện một đòn tấn công bổ sung, gây tổng Aero DMG bằng {0} Attack của Ciaccona.
-Ciaccona nhận thêm {1} bonus Aero DMG trong {2} giây, có thể cộng dồn tối đa {3} lần.</t>
+Triệu hồi Ensemble Sylph để thực hiện một đòn tấn công bổ sung, gây tổng DMG Aero bằng {0} ATK của Ciaccona.
+Ciaccona nhận thêm {1} bonus DMG Aero trong {2} giây, có thể cộng dồn tối đa {3} lần.</t>
         </is>
       </c>
     </row>
@@ -20971,10 +20971,10 @@
         <is>
           <t>&lt;color=#c49e55&gt;[Forte Circuit]&lt;/color&gt;
 Ciaccona có thể di chuyển tự do khi kích hoạt Resonance Liberation. Hệ số Sát Thương của Giao Hưởng Thi Ca: Chủ Âm được tăng cường, và kỹ năng gây ra cả Aero Erosion lẫn Spectro Frazzle lên mục tiêu.
-Ciaccona nhận hiệu ứng Giao Hưởng Vàng, tăng Attack của cô thêm {0} và mang lại nhiều hiệu ứng khác nhau khi cô hoặc Ensemble Sylph biểu diễn Solo Concert với các nhạc cụ khác nhau:
-- Giọng nói Thánh: Đặt lại Cooldown chiêu Resonance Skill.
-- Dây Đàn Rung: Mid-air Attack Stage 2 và Resonance Skill kế tiếp gây thêm {1} Sát Thương.
-- Nhịp Vũ Trời: Heavy Attack - Tứ Trùng Âm có phạm vi tấn công mở rộng. Trong {2} giây, Basic Attack kế tiếp sẽ trở thành Nhịp Mạnh, gây {3} Aero DMG.</t>
+Ciaccona nhận hiệu ứng Giao Hưởng Vàng, tăng ATK của cô thêm {0} và mang lại nhiều hiệu ứng khác nhau khi cô hoặc Ensemble Sylph biểu diễn Solo Concert với các nhạc cụ khác nhau:
+- Giọng Thánh: Đặt lại Thời gian hồi chiêu Resonance Skill.
+- Dây Đàn Rung: ATK Giữa Không Giai Đoạn 2 và Resonance Skill kế tiếp gây thêm {1} Sát Thương.
+- Nhịp Vũ Trời: Heavy Attack - Tứ Trùng Âm có phạm vi tấn công mở rộng. Trong {2} giây, Basic Attack kế tiếp sẽ trở thành Nhịp Mạnh, gây {3} Sát Thương Aero.</t>
         </is>
       </c>
     </row>
@@ -21043,7 +21043,7 @@
         <is>
           <t>&lt;color=#c49e55&gt;[Forte Circuit]&lt;/color&gt;
 Ciaccona có thể di chuyển tự do khi kích hoạt Resonance Liberation.
-Tấn Công của Ciaccona được tăng cường và nhận hiệu ứng đặc biệt khi biểu diễn Solo Concert dựa trên các nhạc cụ khác nhau.</t>
+ATK của Ciaccona được tăng cường và nhận hiệu ứng đặc biệt khi biểu diễn Solo Concert dựa trên các nhạc cụ khác nhau.</t>
         </is>
       </c>
     </row>
@@ -21111,8 +21111,8 @@
       <c r="M310" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Basic Attack]&lt;/color&gt;
-Buổi độc tấu Solo Concert của Ciaccona và Ensemble Sylph liên tục gây {0} Aero DMG lên các mục tiêu xung quanh và áp đặt một tầng Aero Erosion cùng một tầng String Warble lên chúng.
-String Warble: Sau một khoảng thời gian nhất định, gây Aero DMG bằng {1} Attack của Ciaccona lên các đơn vị đồng minh gần đó và bản thân, sau đó loại bỏ hiệu ứng.</t>
+Buổi độc tấu Solo Concert của Ciaccona và Ensemble Sylph liên tục gây {0} Sát Thương Aero lên các mục tiêu xung quanh và áp đặt một tầng Aero Erosion cùng một tầng String Warble lên chúng.
+String Warble: Sau một khoảng thời gian nhất định, gây Sát Thương Aero bằng {1} ATK của Ciaccona lên các đơn vị đồng minh gần đó và bản thân, sau đó loại bỏ hiệu ứng.</t>
         </is>
       </c>
     </row>
@@ -21247,7 +21247,7 @@
       <c r="M312" t="inlineStr">
         <is>
           <t>&lt;color=Highlight&gt;[Resonance Skill]&lt;/color&gt;
-- Resonance Skill - "Kiếm Đáp Lời Sóng" và Resonance Skill - "Tempest Phá Tan Triều Dâng" gây nhiều sát thương hơn và gây hiệu ứng Erosion Aero.
+- Resonance Skill - "Kiếm Đáp Lời Sóng" và Resonance Skill - "Bão Tố Phá Tan Triều Dâng" gây nhiều DMG hơn và gây hiệu ứng Xói Mòn Aero.
 - Cartethyia và Fleurdelys nhận được Lãnh Địa Gió.</t>
         </is>
       </c>
@@ -21318,8 +21318,8 @@
         <is>
           <t>&lt;color=Highlight&gt;[Resonance Liberation]&lt;/color&gt;
 - Fleurdelys có thể sử dụng Resonance Skill - Thẩm Phán Tà Ác trong một số điều kiện nhất định.
-- Resonance Liberation - Lưỡi Kiếm Bão Gào hoặc Đòn Mid-air Attack - Cartethyia sẽ nhận được hiệu ứng đặc biệt.
-- Cartethyia gây thêm sát thương.</t>
+- Resonance Liberation - Lưỡi Kiếm Bão Gào hoặc Đòn Tấn Công Giữa Không - Cartethyia sẽ nhận được hiệu ứng đặc biệt.
+- Cartethyia gây thêm DMG.</t>
         </is>
       </c>
     </row>
@@ -21386,7 +21386,7 @@
       <c r="M314" t="inlineStr">
         <is>
           <t>&lt;color=Highlight&gt;[Forte Circuit]&lt;/color&gt;
-Kích hoạt Resonance Liberation - Lưỡi Kiếm Gào Thét và Resonance Skill - Kẻ Trừng Ác sẽ tăng HP tối đa cho Lưỡi Kiếm Phản Kháng và khiến mọi sát thương gây ra đều bỏ qua Aero RES của mục tiêu.</t>
+Kích hoạt Resonance Liberation - Lưỡi Kiếm Gào Thét và Resonance Skill - Kẻ Trừng Ác sẽ tăng HP tối đa cho Lưỡi Kiếm Phản Kháng và khiến mọi DMG gây ra đều bỏ qua Kháng Aero của mục tiêu.</t>
         </is>
       </c>
     </row>
@@ -21523,8 +21523,8 @@
       <c r="M316" t="inlineStr">
         <is>
           <t>&lt;color=Highlight&gt;[Resonance Skill]&lt;/color&gt;
-- Kỹ Năng "Beyond Biên Giới" được tăng cường.
-- "Closing Refrain" và "Điệp Khúc Bất Tận" hút mục tiêu xung quanh.</t>
+- Kỹ Năng "Vượt Qua Biên Giới" được tăng cường.
+- "Điệp Khúc Kết" và "Điệp Khúc Bất Tận" hút mục tiêu xung quanh.</t>
         </is>
       </c>
     </row>
@@ -21593,7 +21593,7 @@
         <is>
           <t>&lt;color=Highlight&gt;[Forte Circuit]&lt;/color&gt;
 - Iuno nhận được &lt;color=Highlight&gt;{1}&lt;/color&gt; tầng Blessing of the Wan Light mỗi &lt;color=Highlight&gt;{0}s&lt;/color&gt;.
-- Sử dụng Heavy Attack - Flux làm tăng Aero DMG thêm &lt;color=Highlight&gt;{2}&lt;/color&gt; trong &lt;color=Highlight&gt;{3}s&lt;/color&gt; và làm chậm kẻ địch xung quanh trong &lt;color=Highlight&gt;{4}s&lt;/color&gt;.</t>
+- Sử dụng Heavy Attack - Flux làm tăng Sát Thương Aero thêm &lt;color=Highlight&gt;{2}&lt;/color&gt; trong &lt;color=Highlight&gt;{3}s&lt;/color&gt; và làm chậm kẻ địch xung quanh trong &lt;color=Highlight&gt;{4}s&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -21729,7 +21729,7 @@
       <c r="M319" t="inlineStr">
         <is>
           <t>&lt;color=Highlight&gt;[Resonance Liberation]&lt;/color&gt;
-Resonance Liberation - Dưới Sóng Trăng có Cooldown chiêu giảm &lt;color=Highlight&gt;{0}s&lt;/color&gt; và giờ đây có thể bắn thêm &lt;color=Highlight&gt;{1}&lt;/color&gt; Mũi Tên Thanh Minh, mỗi mũi tên gây Aero DMG bằng &lt;color=Highlight&gt;{2}&lt;/color&gt; Tấn Công của Iuno, được tính là Sát Thương Resonance Liberation.</t>
+Resonance Liberation - Dưới Sóng Trăng có Thời gian hồi chiêu giảm &lt;color=Highlight&gt;{0} giây&lt;/color&gt; và giờ đây có thể bắn thêm &lt;color=Highlight&gt;{1}&lt;/color&gt; Mũi Tên Thanh Minh, mỗi mũi tên gây Sát Thương Aero bằng &lt;color=Highlight&gt;{2}&lt;/color&gt; ATK của Iuno, được tính là Sát Thương Resonance Liberation.</t>
         </is>
       </c>
     </row>
@@ -21796,7 +21796,7 @@
       <c r="M320" t="inlineStr">
         <is>
           <t>&lt;color=Highlight&gt;[Resonance Liberation]&lt;/color&gt;
-Resonance Liberation có Cooldown chiêu ngắn hơn và giờ đây có thể bắn thêm Mũi Tên Thanh Minh.</t>
+Resonance Liberation có Thời gian hồi chiêu ngắn hơn và giờ đây có thể bắn thêm Mũi Tên Thanh Minh.</t>
         </is>
       </c>
     </row>
@@ -21864,8 +21864,8 @@
       <c r="M321" t="inlineStr">
         <is>
           <t>&lt;color=Highlight&gt;[Forte Circuit]&lt;/color&gt;
-- Tỷ Lệ Critical Hit tăng thêm &lt;color=Highlight&gt;{0}&lt;/color&gt;. Mỗi &lt;color=Highlight&gt;{1}&lt;/color&gt; Tỷ Lệ Critical Hit vượt quá &lt;color=Highlight&gt;{2}&lt;/color&gt; sẽ được chuyển đổi thành &lt;color=Highlight&gt;{3}&lt;/color&gt; Attack.
-- Gây Critical Hit sẽ tạo ra &lt;color=Highlight&gt;&lt;SapTag=4&gt;{4}&lt;/SapTag&gt;&lt;/color&gt; Lưỡi Gió, gây Aero DMG bằng &lt;color=Highlight&gt;{5}&lt;/color&gt; Attack của Qiuyuan, được tính là sát thương Heavy Attack. Hiệu ứng này có thể kích hoạt &lt;color=Highlight&gt;&lt;SapTag=7&gt;{7}&lt;/SapTag&gt;&lt;/color&gt; lần mỗi &lt;color=Highlight&gt;{6}s&lt;/color&gt;.</t>
+- Crit. Rate tăng thêm &lt;color=Highlight&gt;{0}&lt;/color&gt;. Mỗi &lt;color=Highlight&gt;{1}&lt;/color&gt; Crit. Rate vượt quá &lt;color=Highlight&gt;{2}&lt;/color&gt; sẽ được chuyển đổi thành &lt;color=Highlight&gt;{3}&lt;/color&gt; ATK.
+- Gây Bạo Kích sẽ tạo ra &lt;color=Highlight&gt;&lt;SapTag=4&gt;{4}&lt;/SapTag&gt;&lt;/color&gt; Lưỡi Gió, gây DMG Aero bằng &lt;color=Highlight&gt;{5}&lt;/color&gt; ATK của Qiuyuan, được tính là DMG Đòn Heavy Attack. Hiệu ứng này có thể kích hoạt &lt;color=Highlight&gt;&lt;SapTag=7&gt;{7}&lt;/SapTag&gt;&lt;/color&gt; lần mỗi &lt;color=Highlight&gt;{6} giây&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -21933,8 +21933,8 @@
       <c r="M322" t="inlineStr">
         <is>
           <t>&lt;color=Highlight&gt;[Forte Circuit]&lt;/color&gt;
-- Tỷ Lệ Critical Hit được tăng lên. Phần Tỷ Lệ Critical Hit vượt quá giá trị nhất định sẽ được chuyển đổi thành Tấn Công.
-- Gây Critical Hit sẽ tạo ra Lưỡi Gió gây Aero DMG.</t>
+- Crit. Rate được tăng lên. Phần Crit. Rate vượt quá giá trị nhất định sẽ được chuyển đổi thành ATK.
+- Gây Bạo Kích sẽ tạo ra Lưỡi Gió gây DMG Aero.</t>
         </is>
       </c>
     </row>
@@ -22003,7 +22003,7 @@
         <is>
           <t>&lt;color=Highlight&gt;[Basic Attack]&lt;/color&gt;
 - Basic Attack được thay thế bằng Kiếm Khách Tự Thoại - Mực Tàu, và đòn tấn công Giai Đoạn &lt;color=Highlight&gt;{0}&lt;/color&gt; sẽ hồi phục thêm &lt;color=Highlight&gt;{1}&lt;/color&gt; điểm Tự Thoại Kiếm Khách.
-- Khi Heavy Attack hoặc Kiếm Khách Tự Thoại - Mực Tàu Giai Đoạn &lt;color=Highlight&gt;{2}&lt;/color&gt; trúng mục tiêu, tạo ra Hú Gió hút mục tiêu vào và Aero DMG Bonus thêm &lt;color=Highlight&gt;{3}&lt;/color&gt; trong &lt;color=Highlight&gt;{4}s&lt;/color&gt;. Hiệu ứng này có thể kích hoạt &lt;color=Highlight&gt;&lt;SapTag=6&gt;{6}&lt;/SapTag&gt;&lt;/color&gt; {Cus:Sap,S=lần P=lần SapTag=6} mỗi &lt;color=Highlight&gt;{5}s&lt;/color&gt;.</t>
+- Khi Heavy Attack hoặc Kiếm Khách Tự Thoại - Mực Tàu Giai Đoạn &lt;color=Highlight&gt;{2}&lt;/color&gt; trúng mục tiêu, tạo ra Hú Gió hút mục tiêu vào và Tăng Sát Thương Aero thêm &lt;color=Highlight&gt;{3}&lt;/color&gt; trong &lt;color=Highlight&gt;{4}s&lt;/color&gt;. Hiệu ứng này có thể kích hoạt &lt;color=Highlight&gt;&lt;SapTag=6&gt;{6}&lt;/SapTag&gt;&lt;/color&gt; {Cus:Sap,S=lần P=lần SapTag=6} mỗi &lt;color=Highlight&gt;{5}s&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -22140,8 +22140,8 @@
       <c r="M325" t="inlineStr">
         <is>
           <t>&lt;color=Highlight&gt;[Resonance Skill]&lt;/color&gt;
-- Resonance Skill - "Vượt Qua Rặng Cây" giảm Cooldown chiêu &lt;color=Highlight&gt;{0}s&lt;/color&gt; và tổng sát thương tăng &lt;color=Highlight&gt;{1}&lt;/color&gt;. Sử dụng kỹ năng này sẽ nhận &lt;color=Highlight&gt;{2}&lt;/color&gt; Aero DMG Bonus trong &lt;color=Highlight&gt;{3}s&lt;/color&gt;.
-- Resonance Skill - "Vượt Qua Rặng Cây" sẽ tự động thi triển khi Qiuyuan bị tấn công, làm chậm kẻ địch xung quanh trong &lt;color=Highlight&gt;{4}s&lt;/color&gt; và hồi phục &lt;color=Highlight&gt;{5}&lt;/color&gt; điểm Khúc Tự Kiếm Sĩ.</t>
+- Resonance Skill - "Vượt Qua Rặng Cây" giảm Thời gian hồi chiêu &lt;color=Highlight&gt;{0} giây&lt;/color&gt; và tổng DMG tăng &lt;color=Highlight&gt;{1}&lt;/color&gt;. Sử dụng kỹ năng này sẽ nhận &lt;color=Highlight&gt;{2}&lt;/color&gt; Tăng Sát Thương Aero trong &lt;color=Highlight&gt;{3} giây&lt;/color&gt;.
+- Resonance Skill - "Vượt Qua Rặng Cây" sẽ tự động thi triển khi Qiuyuan bị tấn công, làm chậm kẻ địch xung quanh trong &lt;color=Highlight&gt;{4} giây&lt;/color&gt; và hồi phục &lt;color=Highlight&gt;{5}&lt;/color&gt; điểm Khúc Tự Kiếm Sĩ.</t>
         </is>
       </c>
     </row>
@@ -22277,7 +22277,7 @@
       <c r="M327" t="inlineStr">
         <is>
           <t>&lt;color=Highlight&gt;[Forte Circuit]&lt;/color&gt;
-Khi ở trong trạng thái "Bút Tháp Tâm Linh", "Lời Kiếm Dạy Đạo", "Lời Kiếm Cứu Độ" và "Lời Kiếm Hy Sinh" sẽ tăng tổng Sát Thương lên &lt;color=Highlight&gt;{0}&lt;/color&gt;, giảm lượng tiêu hao của "Swordster's Soliloquy" xuống &lt;color=Highlight&gt;{1}&lt;/color&gt;, đồng thời hồi phục &lt;color=Highlight&gt;{2}&lt;/color&gt; điểm Resonance Energy.</t>
+Khi ở trong trạng thái "Bút Tháp Tâm Linh", "Lời Kiếm Dạy Đạo", "Lời Kiếm Cứu Độ" và "Lời Kiếm Hy Sinh" sẽ tăng tổng Sát Thương lên &lt;color=Highlight&gt;{0}&lt;/color&gt;, giảm lượng tiêu hao của "Độc Thoại Kiếm Khách" xuống &lt;color=Highlight&gt;{1}&lt;/color&gt;, đồng thời hồi phục &lt;color=Highlight&gt;{2}&lt;/color&gt; điểm Resonance Energy.</t>
         </is>
       </c>
     </row>
@@ -22411,7 +22411,7 @@
       <c r="M329" t="inlineStr">
         <is>
           <t>&lt;color=Highlight&gt;[Resonance Liberation]&lt;/color&gt;
-Resonance Liberation - Đòn Phá Hủy có tổng Sát Thương tăng thêm &lt;color=Highlight&gt;{0}&lt;/color&gt; và Cooldown chiêu giảm &lt;color=Highlight&gt;{1}s&lt;/color&gt;.</t>
+Resonance Liberation - Đòn Phá Hủy có tổng Sát Thương tăng thêm &lt;color=Highlight&gt;{0}&lt;/color&gt; và Thời gian hồi chiêu giảm &lt;color=Highlight&gt;{1} giây&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -22478,7 +22478,7 @@
       <c r="M330" t="inlineStr">
         <is>
           <t>&lt;color=Highlight&gt;[Resonance Liberation]&lt;/color&gt;
-Resonance Liberation - Đòn Phá Hủy có tổng Sát Thương cao hơn và Cooldown chiêu ngắn hơn.</t>
+Resonance Liberation - Đòn Phá Hủy có tổng Sát Thương cao hơn và Thời gian hồi chiêu ngắn hơn.</t>
         </is>
       </c>
     </row>
@@ -22543,7 +22543,7 @@
       </c>
       <c r="M331" t="inlineStr">
         <is>
-          <t>&lt;color=#c49e55&gt;[Special Enhancement]&lt;/color&gt; Tiêu hao Âm Thanh Nhỏ làm tăng Crit. Rate thêm {0} nhưng giảm lượng Tích Lũy Forte đi {1}. Hiệu ứng kéo dài {2} giây.</t>
+          <t>&lt;color=#c49e55&gt;[Tăng Cường Đặc Biệt]&lt;/color&gt; Tiêu hao Âm Thanh Nhỏ làm tăng Crit. Rate thêm {0} nhưng giảm lượng Tích Lũy Forte đi {1}. Hiệu ứng kéo dài {2} giây.</t>
         </is>
       </c>
     </row>
@@ -22608,7 +22608,7 @@
       </c>
       <c r="M332" t="inlineStr">
         <is>
-          <t>&lt;color=#c49e55&gt;[Special Enhancement]&lt;/color&gt; Tiêu hao Âm Thanh Nhỏ làm tăng Crit. Rate nhưng giảm lượng Tích Lũy Forte trong thời gian ngắn.</t>
+          <t>&lt;color=#c49e55&gt;[Tăng Cường Đặc Biệt]&lt;/color&gt; Tiêu hao Âm Thanh Nhỏ làm tăng Crit. Rate nhưng giảm lượng Tích Lũy Forte trong thời gian ngắn.</t>
         </is>
       </c>
     </row>
@@ -22673,7 +22673,7 @@
       </c>
       <c r="M333" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Resonance Skill]&lt;/color&gt; Resonance Skill Nâng Cao sẽ đặt lại Cooldown chiêu của Resonance Skill. Hiệu ứng này chỉ có thể kích hoạt mỗi 10 giây một lần.</t>
+          <t>&lt;color=#ffd12f&gt;[Resonance Skill]&lt;/color&gt; Resonance Skill Nâng Cao sẽ đặt lại Thời gian hồi chiêu của Resonance Skill. Hiệu ứng này chỉ có thể kích hoạt mỗi 10 giây một lần.</t>
         </is>
       </c>
     </row>
@@ -22738,7 +22738,7 @@
       </c>
       <c r="M334" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Resonance Skill]&lt;/color&gt; Resonance Skill Nâng Cao sẽ đặt lại Cooldown chiêu của Resonance Skill.</t>
+          <t>&lt;color=#ffd12f&gt;[Resonance Skill]&lt;/color&gt; Resonance Skill Nâng Cao sẽ đặt lại Thời gian hồi chiêu của Resonance Skill.</t>
         </is>
       </c>
     </row>
@@ -22803,7 +22803,7 @@
       </c>
       <c r="M335" t="inlineStr">
         <is>
-          <t>&lt;color=#c49e55&gt;[Basic Attack]&lt;/color&gt; &lt;color=#c49e55&gt;[Heavy Attack]&lt;/color&gt; Basic Attack {0} và Heavy Attack sẽ triệu hồi thêm {1} "kiếm bay", gây {2} sát thương.</t>
+          <t>&lt;color=#c49e55&gt;[Basic Attack]&lt;/color&gt; &lt;color=#c49e55&gt;[Heavy Attack]&lt;/color&gt; Basic Attack {0} và Heavy Attack sẽ triệu hồi thêm {1} "kiếm bay", gây {2} DMG.</t>
         </is>
       </c>
     </row>
@@ -22933,7 +22933,7 @@
       </c>
       <c r="M337" t="inlineStr">
         <is>
-          <t>&lt;color=#c49e55&gt;[Special Enhancement]&lt;/color&gt; Tiêu hao Tích Lũy Forte làm tăng Crit. Rate thêm {0} nhưng giảm tốc độ hồi phục Tích Lũy Forte đi {1}. Hiệu ứng kéo dài {2} giây.</t>
+          <t>&lt;color=#c49e55&gt;[Tăng Cường Đặc Biệt]&lt;/color&gt; Tiêu hao Tích Lũy Forte làm tăng Crit. Rate thêm {0} nhưng giảm tốc độ hồi phục Tích Lũy Forte đi {1}. Hiệu ứng kéo dài {2} giây.</t>
         </is>
       </c>
     </row>
@@ -22998,7 +22998,7 @@
       </c>
       <c r="M338" t="inlineStr">
         <is>
-          <t>&lt;color=#c49e55&gt;[Special Enhancement]&lt;/color&gt; Tiêu hao Tích Lũy Forte tạm thời tăng Crit. Rate nhưng giảm tốc độ hồi phục Tích Lũy Forte.</t>
+          <t>&lt;color=#c49e55&gt;[Tăng Cường Đặc Biệt]&lt;/color&gt; Tiêu hao Tích Lũy Forte tạm thời tăng Crit. Rate nhưng giảm tốc độ hồi phục Tích Lũy Forte.</t>
         </is>
       </c>
     </row>
@@ -23063,7 +23063,7 @@
       </c>
       <c r="M339" t="inlineStr">
         <is>
-          <t>&lt;color=#c49e55&gt;[Basic Attack ]&lt;/color&gt; &lt;color=#c49e55&gt;[Special Enhancement]&lt;/color&gt; Trong vòng {0} giây sau khi sử dụng Resonance Skill - Resonating Spin, mỗi đòn Basic Attack sẽ kích hoạt thêm {1} đòn "Flying Kiếm", gây {2} sát thương. Cooldown chiêu của Resonance Skill tăng thêm {3} giây.</t>
+          <t>&lt;color=#c49e55&gt;[Basic Attack]&lt;/color&gt; &lt;color=#c49e55&gt;[Tăng Cường Đặc Biệt]&lt;/color&gt; Trong vòng {0} giây sau khi sử dụng Resonance Skill - Resonating Spin, mỗi đòn Basic Attack sẽ kích hoạt thêm {1} đòn "Flying Kiếm đơn", gây {2} DMG. Thời gian hồi chiêu của Resonance Skill tăng thêm {3} giây.</t>
         </is>
       </c>
     </row>
@@ -23128,7 +23128,7 @@
       </c>
       <c r="M340" t="inlineStr">
         <is>
-          <t>&lt;color=#c49e55&gt;[Basic Attack ]&lt;/color&gt;&lt;color=#c49e55&gt;[Special Enhancement]&lt;/color&gt; Sau khi sử dụng Resonating Spin, mỗi đòn Basic Attack sẽ kích hoạt thêm đòn "Flying Kiếm". Cooldown chiêu của Resonance Skill tăng lên.</t>
+          <t>&lt;color=#c49e55&gt;[Basic Attack]&lt;/color&gt;&lt;color=#c49e55&gt;[Tăng Cường Đặc Biệt]&lt;/color&gt; Sau khi sử dụng Resonating Spin, mỗi đòn Basic Attack sẽ kích hoạt thêm đòn "Flying Kiếm đơn". Thời gian hồi chiêu của Resonance Skill tăng lên.</t>
         </is>
       </c>
     </row>
@@ -23193,7 +23193,7 @@
       </c>
       <c r="M341" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Heavy Attack]&lt;/color&gt; Heavy Attack: Aftertune sẽ gây thêm 2 vụ nổ, mỗi vụ gây 150% Spectro DMG.</t>
+          <t>&lt;color=#ffd12f&gt;[Đòn Heavy Attack]&lt;/color&gt; Đòn Heavy Attack: Aftertune sẽ gây thêm 2 vụ nổ, mỗi vụ gây 150% Sát Thương Spectro.</t>
         </is>
       </c>
     </row>
@@ -23258,7 +23258,7 @@
       </c>
       <c r="M342" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Heavy Attack]&lt;/color&gt; Increase số lượng vụ nổ sau Heavy Attack.</t>
+          <t>&lt;color=#ffd12f&gt;[Đòn Heavy Attack]&lt;/color&gt; Tăng số lượng vụ nổ sau Đòn Heavy Attack.</t>
         </is>
       </c>
     </row>
@@ -23323,7 +23323,7 @@
       </c>
       <c r="M343" t="inlineStr">
         <is>
-          <t>&lt;color=#c49e55&gt;[Resonance Skill]&lt;/color&gt; "Echo Resonance" sẽ tạo ra thêm {0} Bánh Xe Kiếm, mỗi chiếc gây sát thương {1}.</t>
+          <t>&lt;color=#c49e55&gt;[Resonance Skill]&lt;/color&gt; "Tiếng Vọng Cộng Hưởng" sẽ tạo ra thêm {0} Bánh Xe Kiếm, mỗi chiếc gây DMG {1}.</t>
         </is>
       </c>
     </row>
@@ -23388,7 +23388,7 @@
       </c>
       <c r="M344" t="inlineStr">
         <is>
-          <t>&lt;color=#c49e55&gt;[Resonance Skill]&lt;/color&gt; Basic Attack Chuỗi sau Resonance Skill tạo thêm Bánh Kiếm.</t>
+          <t>&lt;color=#c49e55&gt;[Resonance Skill]&lt;/color&gt; Đòn Basic Attack Chuỗi sau Resonance Skill tạo thêm Bánh Kiếm.</t>
         </is>
       </c>
     </row>
@@ -23583,7 +23583,7 @@
       </c>
       <c r="M347" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Resonance Skill]&lt;/color&gt; Resonance Skill Nâng Cao sẽ đặt lại Cooldown chiêu của Resonance Skill. Hiệu ứng này chỉ có thể kích hoạt mỗi 10 giây một lần.</t>
+          <t>&lt;color=#ffd12f&gt;[Resonance Skill]&lt;/color&gt; Resonance Skill Nâng Cao sẽ đặt lại Thời gian hồi chiêu của Resonance Skill. Hiệu ứng này chỉ có thể kích hoạt mỗi 10 giây một lần.</t>
         </is>
       </c>
     </row>
@@ -23648,7 +23648,7 @@
       </c>
       <c r="M348" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Resonance Skill]&lt;/color&gt; Resonance Skill Nâng Cao sẽ đặt lại Cooldown chiêu của Resonance Skill.</t>
+          <t>&lt;color=#ffd12f&gt;[Resonance Skill]&lt;/color&gt; Resonance Skill Nâng Cao sẽ đặt lại Thời gian hồi chiêu của Resonance Skill.</t>
         </is>
       </c>
     </row>
@@ -23717,7 +23717,7 @@
         <is>
           <t>&lt;color=#c49e55&gt;[Resonance Skill]&lt;/color&gt;
 - Khi HP của Verina ở mức đầy, Crit. Rate của cô tăng thêm {0}.
-- Khi HP của Verina ở mức đầy, sử dụng Resonance Skill sẽ tiêu hao {1} HP tối đa của cô và kích hoạt 1 Vùng Tăng Trưởng xung quanh, gây Spectro DMG bằng {2} Tấn Công của cô. Sát Thương này được tính là Sát Thương Resonance Skill và bỏ qua {3} Phòng Ngự của mục tiêu.</t>
+- Khi HP của Verina ở mức đầy, sử dụng Resonance Skill sẽ tiêu hao {1} HP tối đa của cô và kích hoạt 1 Vùng Tăng Trưởng xung quanh, gây Sát Thương Spectro bằng {2} ATK của cô. Sát Thương này được tính là Sát Thương Resonance Skill và bỏ qua {3} Phòng Ngự của mục tiêu.</t>
         </is>
       </c>
     </row>
@@ -23786,7 +23786,7 @@
         <is>
           <t>&lt;color=#c49e55&gt;[Resonance Skill]&lt;/color&gt;
 - Khi HP của Verina ở mức đầy, Crit. Rate của cô tăng lên.
-- Khi HP của Verina ở mức đầy, sử dụng Resonance Skill sẽ tiêu hao một lượng HP tối đa của cô và kích hoạt 1 Vùng Tăng Trưởng xung quanh, gây Spectro DMG bỏ qua một phần Phòng Ngự của mục tiêu.</t>
+- Khi HP của Verina ở mức đầy, sử dụng Resonance Skill sẽ tiêu hao một lượng HP tối đa của cô và kích hoạt 1 Vùng Tăng Trưởng xung quanh, gây Sát Thương Spectro bỏ qua một phần Phòng Ngự của mục tiêu.</t>
         </is>
       </c>
     </row>
@@ -23855,9 +23855,9 @@
       <c r="M351" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Basic Attack]&lt;/color&gt;
-- Chu kỳ Basic Attack giờ bắt đầu từ Stage 4, và hồi phục thêm 1 Photosynthesis Energy mỗi lần trúng đích.
-- Khi trúng mục tiêu bằng Heavy Attack, Verina sẽ triệu hồi 1 Bloombud phía trước, gây Spectro DMG bằng {0} Attack của cô, được tính là sát thương Resonance Skill. Hiệu ứng này có thể kích hoạt mỗi {1} giây một lần.
-- Verina nhận thêm {2} Spectro DMG Bonus.</t>
+- Chu kỳ Basic Attack giờ bắt đầu từ Giai Đoạn 4, và hồi phục thêm 1 Năng Lượng Quang Hợp mỗi lần trúng đích.
+- Khi trúng mục tiêu bằng Đòn Heavy Attack, Verina sẽ triệu hồi 1 Bloombud phía trước, gây DMG Spectro bằng {0} ATK của cô, được tính là DMG Resonance Skill. Hiệu ứng này có thể kích hoạt mỗi {1} giây một lần.
+- Verina nhận thêm {2} Tăng Sát Thương Spectro.</t>
         </is>
       </c>
     </row>
@@ -23926,9 +23926,9 @@
       <c r="M352" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Basic Attack]&lt;/color&gt;
-- Chu kỳ Basic Attack giờ bắt đầu từ Stage 4, và hồi phục thêm Photosynthesis Energy mỗi lần trúng đích.
-- Khi trúng mục tiêu bằng Heavy Attack, Verina sẽ triệu hồi Bloombud phía trước, gây Spectro DMG.
-- Verina nhận thêm Spectro DMG Bonus.</t>
+- Chu kỳ Basic Attack giờ bắt đầu từ Giai Đoạn 4, và hồi phục thêm Năng Lượng Quang Hợp mỗi lần trúng đích.
+- Khi trúng mục tiêu bằng Đòn Heavy Attack, Verina sẽ triệu hồi Bloombud phía trước, gây DMG Spectro.
+- Verina nhận thêm Tăng Sát Thương Spectro.</t>
         </is>
       </c>
     </row>
@@ -23997,9 +23997,9 @@
       <c r="M353" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Forte Circuit]&lt;/color&gt;
-- Cooldown chiêu Resonance Skill của Verina giảm {0} giây mỗi khi cô tiêu thụ Photosynthesis Energy.
-- Thi triển Resonance Skill cũng gây thêm Spectro DMG bằng {1} Tấn Công của Verina, tấn công một khu vực lớn 4 lần, được tính là Sát Thương Resonance Skill, và hồi phục {2} Photosynthesis Energy.
-- Verina nhận thêm {3} Spectro DMG Bonus.</t>
+- Thời gian hồi chiêu Resonance Skill của Verina giảm {0} giây mỗi khi cô tiêu thụ Năng Lượng Quang Hợp.
+- Thi triển Resonance Skill cũng gây thêm Sát Thương Spectro bằng {1} ATK của Verina, tấn công một khu vực lớn 4 lần, được tính là Sát Thương Resonance Skill, và hồi phục {2} Năng Lượng Quang Hợp.
+- Verina nhận thêm {3} Tăng Sát Thương Spectro.</t>
         </is>
       </c>
     </row>
@@ -24068,9 +24068,9 @@
       <c r="M354" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Forte Circuit]&lt;/color&gt;
-- Cooldown chiêu Resonance Skill của Verina giảm mỗi khi cô tiêu thụ Photosynthesis Energy.
-- Thi triển Resonance Skill cũng gây thêm Sát Thương trên một khu vực rộng và hồi phục Photosynthesis Energy.
-- Verina nhận Spectro DMG Bonus.</t>
+- Thời gian hồi chiêu Resonance Skill của Verina giảm mỗi khi cô tiêu thụ Năng Lượng Quang Hợp.
+- Thi triển Resonance Skill cũng gây thêm Sát Thương trên một khu vực rộng và hồi phục Năng Lượng Quang Hợp.
+- Verina nhận Tăng Sát Thương Spectro.</t>
         </is>
       </c>
     </row>
@@ -24138,8 +24138,8 @@
       <c r="M355" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Forte Circuit]&lt;/color&gt;
-- Basic Attack và Resonance Skill khi trúng mục tiêu sẽ áp dụng Dấu Hiệu Quang Hợp trong {0} giây.
-- Verina nhận thêm {1} Attack Bổ Sung Spectro.</t>
+- Đòn Basic Attack và Resonance Skill khi trúng mục tiêu sẽ áp dụng Dấu Hiệu Quang Hợp trong {0} giây.
+- Verina nhận thêm {1} Tấn Công Bổ Sung Spectro.</t>
         </is>
       </c>
     </row>
@@ -24207,8 +24207,8 @@
       <c r="M356" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Forte Circuit]&lt;/color&gt;
-- Basic Attack và Resonance Skill khi trúng mục tiêu sẽ áp dụng Dấu Hiệu Quang Hợp.
-- Verina nhận Attack Bổ Sung Spectro.</t>
+- Đòn Basic Attack và Resonance Skill khi trúng mục tiêu sẽ áp dụng Dấu Hiệu Quang Hợp.
+- Verina nhận Tấn Công Bổ Sung Spectro.</t>
         </is>
       </c>
     </row>
@@ -24276,7 +24276,7 @@
       <c r="M357" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Basic Attack]&lt;/color&gt;
-- Thực hiện Mid-air Attack và Heavy Attack Giữa Không sẽ hồi phục thêm {0} STA.
+- Thực hiện Tấn Công Giữa Không và Heavy Attack Giữa Không sẽ hồi phục thêm {0} STA.
 - Thực hiện Heavy Attack Giữa Không khi STA đầy sẽ tăng Crit. DMG của Verina thêm {1} trong {2} giây.</t>
         </is>
       </c>
@@ -24345,7 +24345,7 @@
       <c r="M358" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Basic Attack]&lt;/color&gt;
-- Thực hiện Mid-air Attack và Heavy Attack Giữa Không sẽ hồi phục thêm STA.
+- Thực hiện Tấn Công Giữa Không và Heavy Attack Giữa Không sẽ hồi phục thêm STA.
 - Thực hiện Heavy Attack Giữa Không khi STA đầy sẽ tăng Crit. DMG của Verina.</t>
         </is>
       </c>
@@ -24411,7 +24411,7 @@
       </c>
       <c r="M359" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Companion's Aid]&lt;/color&gt; Summon Verina để thi triển Resonance Liberation khi Năng Lượng Khúc Tấu đạt tối đa, kích hoạt Intro Skill.</t>
+          <t>&lt;color=#ffd12f&gt;[Hỗ Trợ Đồng Hành]&lt;/color&gt; Triệu hồi Verina để thi triển Resonance Liberation khi Năng Lượng Khúc Tấu đạt tối đa, kích hoạt Kỹ Năng Khởi Động.</t>
         </is>
       </c>
     </row>
@@ -24476,7 +24476,7 @@
       </c>
       <c r="M360" t="inlineStr">
         <is>
-          <t>Concerto: Verina</t>
+          <t>Khúc Concerto: Verina</t>
         </is>
       </c>
     </row>
@@ -24543,7 +24543,7 @@
       <c r="M361" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Heavy Attack]&lt;/color&gt;
-Red Light: Heavy Attack có phạm vi rộng hơn và không còn tiêu hao STA. Lumi nhận thêm {0} bonus Electro DMG.</t>
+Red Light: Heavy Attack có phạm vi rộng hơn và không còn tiêu hao STA. Lumi nhận thêm {0} bonus DMG Electro.</t>
         </is>
       </c>
     </row>
@@ -24610,7 +24610,7 @@
       <c r="M362" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Heavy Attack]&lt;/color&gt;
-Red Light: Heavy Attack có phạm vi rộng hơn và không còn tiêu hao STA. Lumi nhận thêm bonus Electro DMG.</t>
+Red Light: Heavy Attack has a larger range and no longer consumes STA. Lumi gains Electro DMG Bonus.</t>
         </is>
       </c>
     </row>
@@ -24677,7 +24677,7 @@
       <c r="M363" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Basic Attack]&lt;/color&gt;
-Sau khi vào trạng thái Zoom, số lượng đạn Glitter sẽ tăng gấp đôi. Glitter nhận được theo cách này gây {0} sát thương, được tính là sát thương Basic Attack và không tạo ra Yellow Light Spark.</t>
+Sau khi vào trạng thái Zoom, số lượng đạn Glitter sẽ tăng gấp đôi. Glitter nhận được theo cách này gây {0} DMG, được tính là DMG Basic Attack và không tạo ra Yellow Light Spark.</t>
         </is>
       </c>
     </row>
@@ -24811,7 +24811,7 @@
       <c r="M365" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Resonance Skill]&lt;/color&gt;
-Sau khi Đòn Nhảy Tích Điện trúng mục tiêu, thực hiện Basic Attack trong vòng {0} giây để Lumi bật lùi và triệu hồi 5 Tia Sáng, mỗi tia gây {1} Sát Thương, được tính là Sát Thương Basic Attack.</t>
+Sau khi Đòn Nhảy Tích Điện trúng mục tiêu, thực hiện Đòn Basic Attack trong vòng {0} giây để Lumi bật lùi và triệu hồi 5 Tia Sáng, mỗi tia gây {1} Sát Thương, được tính là Sát Thương Đòn Basic Attack.</t>
         </is>
       </c>
     </row>
@@ -24878,7 +24878,7 @@
       <c r="M366" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Resonance Skill]&lt;/color&gt;
-Sau khi Đòn Nhảy Tích Điện trúng mục tiêu, thực hiện Basic Attack để Lumi bật lùi và triệu hồi 5 Tia Sáng, mỗi tia gây Electro DMG.</t>
+Sau khi Đòn Nhảy Tích Điện trúng mục tiêu, thực hiện Đòn Basic Attack để Lumi bật lùi và triệu hồi 5 Tia Sáng, mỗi tia gây Sát Thương Electro.</t>
         </is>
       </c>
     </row>
@@ -24945,7 +24945,7 @@
       <c r="M367" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Forte Circuit]&lt;/color&gt;
-Lumi nhận được 1 Tia Light mỗi khi thực hiện Đèn Đỏ: Heavy Attack, có thể tích lũy tối đa {0}. Khi sử dụng Resonance Skill Nảy Lại Tăng Năng, tất cả Tia Light sẽ bắn ra dưới dạng tia laser vào mục tiêu, gây {1} Electro DMG, được tính là Sát Thương từ Basic Attack.</t>
+Lumi nhận được 1 Tia Sáng mỗi khi thực hiện Đèn Đỏ: Đòn Tấn Công Mạnh, có thể tích lũy tối đa {0}. Khi sử dụng Resonance Skill Nảy Lại Tăng Năng, tất cả Tia Sáng sẽ bắn ra dưới dạng tia laser vào mục tiêu, gây {1} Sát Thương Electro, được tính là Sát Thương từ Đòn Basic Attack.</t>
         </is>
       </c>
     </row>
@@ -25012,7 +25012,7 @@
       <c r="M368" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Forte Circuit]&lt;/color&gt;
-Lumi nhận được 1 Tia Light mỗi khi thực hiện Đèn Đỏ: Heavy Attack. Khi sử dụng Resonance Skill Nảy Lại Tăng Năng, tất cả Tia Light sẽ bắn ra dưới dạng tia laser vào mục tiêu, gây Electro DMG.</t>
+Lumi nhận được 1 Tia Sáng mỗi khi thực hiện Đèn Đỏ: Đòn Tấn Công Mạnh. Khi sử dụng Resonance Skill Nảy Lại Tăng Năng, tất cả Tia Sáng sẽ bắn ra dưới dạng tia laser vào mục tiêu, gây Sát Thương Electro.</t>
         </is>
       </c>
     </row>
@@ -25080,8 +25080,8 @@
       <c r="M369" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Basic Attack]&lt;/color&gt;
-- Khi ở trạng thái Zoom hoặc thực hiện Heavy Attack: Red Light, khả năng chống gián đoạn của Lumi được tăng cường và Attack của cô tăng thêm {0}.
-- Mỗi Heavy Attack: Red Light cô thực hiện sẽ tạo một lá chắn dựa trên {1} HP tối đa của cô trong {2} giây.</t>
+- Khi ở trạng thái Zoom hoặc thực hiện Đòn Heavy Attack: Red Light, khả năng chống gián đoạn của Lumi được tăng cường và ATK của cô tăng thêm {0}.
+- Mỗi Đòn Heavy Attack: Red Light cô thực hiện sẽ tạo một lá chắn dựa trên {1} HP tối đa của cô trong {2} giây.</t>
         </is>
       </c>
     </row>
@@ -25149,8 +25149,8 @@
       <c r="M370" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Basic Attack]&lt;/color&gt;
-- Khi ở trạng thái Zoom hoặc thực hiện Heavy Attack: Red Light, khả năng chống gián đoạn của Lumi được tăng cường và Attack của cô tăng lên.
-- Mỗi Heavy Attack: Red Light cô thực hiện sẽ tạo một lá chắn.</t>
+- Khi ở trạng thái Zoom hoặc thực hiện Đòn Heavy Attack: Red Light, khả năng chống gián đoạn của Lumi được tăng cường và ATK của cô tăng lên.
+- Mỗi Đòn Heavy Attack: Red Light cô thực hiện sẽ tạo một lá chắn.</t>
         </is>
       </c>
     </row>
@@ -25221,11 +25221,11 @@
       <c r="M371" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Forte Circuit]&lt;/color&gt;
-- Mỗi khi Shorekeeper gây sát thương bằng bướm (Roam Star Butterfly, Ferry Star Butterfly, Altered Dim Star Butterfly, Altered Flare Star Butterfly), cô hồi phục {0} Resonance Energy.
-- Khi ở trạng thái Unbound Form (giữ nút Normal Attack để kích hoạt), Shorekeeper miễn nhiễm với mọi sát thương.
+- Mỗi khi Shorekeeper gây DMG bằng bướm (Roam Star Butterfly, Ferry Star Butterfly, Altered Dim Star Butterfly, Altered Flare Star Butterfly), cô hồi phục {0} Resonance Energy.
+- Khi ở trạng thái Unbound Form (giữ nút Normal Attack để kích hoạt), Shorekeeper miễn nhiễm với mọi DMG.
 - Khi kết thúc Unbound Form:
-Kích hoạt vụ nổ gây Spectro DMG bằng {1} Attack của Shorekeeper. Mỗi đoạn Data Suy Diễn tích lũy làm tăng Hệ Số Sát Thương của vụ nổ thêm {2} và mở rộng phạm vi nổ.
-Tạo ra 5 Roam Star Butterfly tự động đuổi theo kẻ địch, gây Spectro DMG bằng {3} Attack của Shorekeeper. Khi trúng mục tiêu, hồi phục {4} HP của Shorekeeper và giảm Spectro RES DMG của mục tiêu đi {5} trong {6} giây.</t>
+Kích hoạt vụ nổ gây Sát Thương Spectro bằng {1} ATK của Shorekeeper. Mỗi đoạn Dữ Liệu Suy Diễn tích lũy làm tăng Hệ Số Sát Thương của vụ nổ thêm {2} và mở rộng phạm vi nổ.
+Tạo ra 5 Roam Star Butterfly tự động đuổi theo kẻ địch, gây Sát Thương Spectro bằng {3} ATK của Shorekeeper. Khi trúng mục tiêu, hồi phục {4} HP của Shorekeeper và giảm Kháng Sát Thương Spectro của mục tiêu đi {5} trong {6} giây.</t>
         </is>
       </c>
     </row>
@@ -25296,11 +25296,11 @@
       <c r="M372" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Forte Circuit]&lt;/color&gt;
-- Mỗi khi Shorekeeper gây sát thương bằng bướm, cô hồi phục Resonance Energy.
-- Khi ở trạng thái Unbound Form, Shorekeeper miễn nhiễm với mọi sát thương.
+- Mỗi khi Shorekeeper gây DMG bằng bướm, cô hồi phục Resonance Energy.
+- Khi ở trạng thái Unbound Form, Shorekeeper miễn nhiễm với mọi DMG.
 - Khi kết thúc Unbound Form:
-Kích hoạt vụ nổ gây Spectro DMG. Mỗi đoạn Data Suy Diễn tích lũy làm tăng Hệ Số Sát Thương của vụ nổ và mở rộng phạm vi nổ.
-Tạo ra 5 Roam Star Butterfly tự động đuổi theo kẻ địch, gây Spectro DMG. Khi trúng mục tiêu, hồi phục HP cho Shorekeeper và giảm Spectro RES DMG của mục tiêu.</t>
+Kích hoạt vụ nổ gây Sát Thương Spectro. Mỗi đoạn Dữ Liệu Suy Diễn tích lũy làm tăng Hệ Số Sát Thương của vụ nổ và mở rộng phạm vi nổ.
+Tạo ra 5 Roam Star Butterfly tự động đuổi theo kẻ địch, gây Sát Thương Spectro. Khi trúng mục tiêu, hồi phục HP cho Shorekeeper và giảm Kháng Sát Thương Spectro của mục tiêu.</t>
         </is>
       </c>
     </row>
@@ -25371,11 +25371,11 @@
       <c r="M373" t="inlineStr">
         <is>
           <t>&lt;color=Highlight&gt;[Forte Circuit]&lt;/color&gt;
-- Mỗi khi Shorekeeper gây sát thương bằng bướm, cô hồi phục Resonance Energy.
-- Khi ở trạng thái Unbound Form, Shorekeeper miễn nhiễm với mọi sát thương.
+- Mỗi khi Shorekeeper gây DMG bằng bướm, cô hồi phục Resonance Energy.
+- Khi ở trạng thái Unbound Form, Shorekeeper miễn nhiễm với mọi DMG.
 - Khi kết thúc Unbound Form:
-Kích hoạt vụ nổ gây Spectro DMG. Mỗi đoạn Data Suy Diễn tích lũy làm tăng Hệ Số Sát Thương của vụ nổ và mở rộng phạm vi nổ.
-Tạo ra 5 Roam Star Butterfly tự động truy đuổi kẻ địch, gây Spectro DMG. Hồi phục HP của Shorekeeper và giảm Spectro RES DMG của mục tiêu khi trúng đích.</t>
+Kích hoạt vụ nổ gây Sát Thương Spectro. Mỗi đoạn Dữ Liệu Suy Diễn tích lũy làm tăng Hệ Số Sát Thương của vụ nổ và mở rộng phạm vi nổ.
+Tạo ra 5 Roam Star Butterfly tự động truy đuổi kẻ địch, gây Sát Thương Spectro. Hồi phục HP của Shorekeeper và giảm Kháng Sát Thương Spectro của mục tiêu khi trúng đích.</t>
         </is>
       </c>
     </row>
@@ -25445,10 +25445,10 @@
       <c r="M374" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Resonance Liberation]&lt;/color&gt;
-- End vòng Resonance Liberation sẽ trực tiếp tạo ra Nội Giới Tinh Vân.
-- Thực hiện Mid-air Attack sẽ tạo ra 5 Bươm Butterfly Sao Phà tự động truy đuổi kẻ địch, gây Spectro DMG bằng {0} Attack của Shorekeeper.
-- Khi trúng mục tiêu bằng Bươm Butterfly Sao Phà, Shorekeeper nhận hiệu ứng sau trong {1} giây:
-Mỗi lần Shorekeeper gây sát thương bằng bướm (Bươm Butterfly Sao Lang Thang, Bươm Butterfly Sao Phà, Bươm Butterfly Sao Mờ Biến Đổi, Bươm Butterfly Sao Lóe Biến Đổi), chúng sẽ gây thêm Spectro DMG bằng {2} Attack của cô.</t>
+- Kết thúc vòng Resonance Liberation sẽ trực tiếp tạo ra Nội Giới Tinh Vân.
+- Thực hiện ATK Giữa Không sẽ tạo ra 5 Bươm Bướm Sao Phà tự động truy đuổi kẻ địch, gây Sát Thương Spectro bằng {0} ATK của Shorekeeper.
+- Khi trúng mục tiêu bằng Bươm Bướm Sao Phà, Shorekeeper nhận hiệu ứng sau trong {1} giây:
+Mỗi lần Shorekeeper gây DMG bằng bướm (Bươm Bướm Sao Lang Thang, Bươm Bướm Sao Phà, Bươm Bướm Sao Mờ Biến Đổi, Bươm Bướm Sao Lóe Biến Đổi), chúng sẽ gây thêm Sát Thương Spectro bằng {2} ATK của cô.</t>
         </is>
       </c>
     </row>
@@ -25518,10 +25518,10 @@
       <c r="M375" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Resonance Liberation]&lt;/color&gt;
-- End vòng Resonance Liberation sẽ trực tiếp tạo ra Nội Giới Tinh Vân.
-- Thực hiện Mid-air Attack sẽ tạo ra 5 Bươm Butterfly Sao Phà tự động truy đuổi kẻ địch, gây Spectro DMG.
-- Khi trúng mục tiêu bằng Bươm Butterfly Sao Phà, Shorekeeper nhận hiệu ứng sau:
-Mỗi lần Shorekeeper gây sát thương bằng bướm, chúng sẽ gây thêm Spectro DMG.</t>
+- Kết thúc vòng Resonance Liberation sẽ trực tiếp tạo ra Nội Giới Tinh Vân.
+- Thực hiện Tấn Công Giữa Không sẽ tạo ra 5 Bươm Bướm Sao Phà tự động truy đuổi kẻ địch, gây Sát Thương Spectro.
+- Khi trúng mục tiêu bằng Bươm Bướm Sao Phà, Shorekeeper nhận hiệu ứng sau:
+Mỗi lần Shorekeeper gây DMG bằng bướm, chúng sẽ gây thêm Sát Thương Spectro.</t>
         </is>
       </c>
     </row>
@@ -25592,11 +25592,11 @@
       <c r="M376" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Resonance Liberation]&lt;/color&gt;
-- Kích hoạt Resonance Liberation Vòng Lặp End giờ đây sẽ trực tiếp tạo ra Nội Giới Tinh Vân.
-- Gây Sát Thương Basic Attack sẽ giảm Cooldown chiêu của Resonance Skill đi {0} giây. Hiệu ứng này chỉ có thể kích hoạt mỗi {1} giây một lần.
-- Khi ở trong phạm vi hiệu quả của Tinh Vân, Resonance Skill sẽ triệu hồi Bướm Sao Bóng Tối Biến Đổi gây Spectro DMG bằng {2} Attack của Shorekeeper.
-- Khi Resonance Liberation Vòng Lặp End đang hoạt động, Bướm Sao Bóng Tối Biến Đổi do Resonance Skill triệu hồi khi trúng mục tiêu sẽ tạo ra Collapsed Core Biến Đổi (được tính là Collapsed Core, có giới hạn chung).
-- Collapsed Core Biến Đổi có thể chuyển hóa thành Bướm Sao Lửa Biến Đổi tự động đuổi theo kẻ địch, gây Spectro DMG bằng {3} Attack của Shorekeeper và kéo mục tiêu gần lại, gây thêm Spectro DMG bằng {4} Attack của Shorekeeper.</t>
+- Kích hoạt Resonance Liberation Vòng Lặp Kết Thúc giờ đây sẽ trực tiếp tạo ra Nội Giới Tinh Vân.
+- Gây Sát Thương Đòn Basic Attack sẽ giảm Thời gian hồi chiêu của Resonance Skill đi {0} giây. Hiệu ứng này chỉ có thể kích hoạt mỗi {1} giây một lần.
+- Khi ở trong phạm vi hiệu quả của Tinh Vân, Resonance Skill sẽ triệu hồi Bướm Sao Bóng Tối Biến Đổi gây Sát Thương Spectro bằng {2} ATK của Shorekeeper.
+- Khi Resonance Liberation Vòng Lặp Kết Thúc đang hoạt động, Bướm Sao Bóng Tối Biến Đổi do Resonance Skill triệu hồi khi trúng mục tiêu sẽ tạo ra Lõi Sụp Đổ Biến Đổi (được tính là Lõi Sụp Đổ, có giới hạn chung).
+- Lõi Sụp Đổ Biến Đổi có thể chuyển hóa thành Bướm Sao Lửa Biến Đổi tự động đuổi theo kẻ địch, gây Sát Thương Spectro bằng {3} ATK của Shorekeeper và kéo mục tiêu gần lại, gây thêm Sát Thương Spectro bằng {4} ATK của Shorekeeper.</t>
         </is>
       </c>
     </row>
@@ -25667,11 +25667,11 @@
       <c r="M377" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Resonance Liberation]&lt;/color&gt;
-- Kích hoạt Resonance Liberation Vòng Lặp End giờ đây sẽ trực tiếp tạo ra Nội Giới Tinh Vân.
-- Gây Sát Thương Basic Attack sẽ giảm Cooldown chiêu của Resonance Skill.
-- Khi ở trong phạm vi hiệu quả của Tinh Vân, Resonance Skill sẽ triệu hồi Bướm Sao Bóng Tối Biến Đổi gây Spectro DMG.
-- Khi Resonance Liberation Vòng Lặp End đang hoạt động, Bướm Sao Bóng Tối Biến Đổi do Resonance Skill triệu hồi khi trúng mục tiêu sẽ tạo ra Collapsed Core Biến Đổi.
-- Collapsed Core Biến Đổi có thể chuyển hóa thành Bướm Sao Lửa Biến Đổi tự động đuổi theo kẻ địch, gây Spectro DMG và kéo mục tiêu gần lại, gây thêm Spectro DMG.</t>
+- Kích hoạt Resonance Liberation Vòng Lặp Kết Thúc giờ đây sẽ trực tiếp tạo ra Nội Giới Tinh Vân.
+- Gây Sát Thương Đòn Basic Attack sẽ giảm Thời gian hồi chiêu của Resonance Skill.
+- Khi ở trong phạm vi hiệu quả của Tinh Vân, Resonance Skill sẽ triệu hồi Bướm Sao Bóng Tối Biến Đổi gây Sát Thương Spectro.
+- Khi Resonance Liberation Vòng Lặp Kết Thúc đang hoạt động, Bướm Sao Bóng Tối Biến Đổi do Resonance Skill triệu hồi khi trúng mục tiêu sẽ tạo ra Lõi Sụp Đổ Biến Đổi.
+- Lõi Sụp Đổ Biến Đổi có thể chuyển hóa thành Bướm Sao Lửa Biến Đổi tự động đuổi theo kẻ địch, gây Sát Thương Spectro và kéo mục tiêu gần lại, gây thêm Sát Thương Spectro.</t>
         </is>
       </c>
     </row>
@@ -25740,7 +25740,7 @@
         <is>
           <t>&lt;color=#c49e55&gt;[Forte Circuit]&lt;/color&gt;
 - Khi kích hoạt Illation hoặc Transmutation của Forte Circuit, Crit. Rate của Shorekeeper tăng {0} và Crit. DMG tăng {1} trong {2} giây.
-- Khi trúng mục tiêu, Illation hoặc Transmutation gây sát thương bằng {3} sát thương của Kỹ Năng Nhập Môn: Discernment. Hiệu ứng này có thể kích hoạt mỗi {4} giây một lần.</t>
+- Khi trúng mục tiêu, Illation hoặc Transmutation gây DMG bằng {3} DMG của Kỹ Năng Nhập Môn: Discernment. Hiệu ứng này có thể kích hoạt mỗi {4} giây một lần.</t>
         </is>
       </c>
     </row>
@@ -25874,7 +25874,7 @@
       <c r="M380" t="inlineStr">
         <is>
           <t>&lt;color=Highlight&gt;[Forte Circuit]&lt;/color&gt;
-- Kích hoạt Suy Luận hoặc Biến Hóa của Forte Circuit sẽ tăng Crit. Rate và Crit. DMG của Shorekeeper, đồng thời gây thêm sát thương khi trúng mục tiêu.</t>
+- Kích hoạt Suy Luận hoặc Biến Hóa của Forte Circuit sẽ tăng Crit. Rate và Crit. DMG của Shorekeeper, đồng thời gây thêm DMG khi trúng mục tiêu.</t>
         </is>
       </c>
     </row>
@@ -25944,8 +25944,8 @@
         <is>
           <t>&lt;color=#c49e55&gt;[Forte Circuit]&lt;/color&gt;
 Mỗi 30 giây, nhận các hiệu ứng sau:
-- Sử dụng Dodge sẽ giúp các Resonator trong đội gần đó thoát khỏi trạng thái gián đoạn khi bị đánh trúng hoặc tung lên không, được tính là Dodge thành công. Nếu họ đang ở trên không, họ sẽ hạ cánh xuống mặt đất. Hiệu ứng này có thể kích hoạt tối đa 5 lần.
-- Khi kích hoạt Dodge thành công bằng hiệu ứng trên, Shorekeeper sẽ phục hồi {0} HP mỗi giây cho đến khi cô chịu sát thương. Khi hiệu ứng trên chưa được kích hoạt, Shorekeeper nhận thêm {1} Spectro DMG Bonus.</t>
+- Sử dụng Né Tránh sẽ giúp các Cộng Hưởng Giả trong đội gần đó thoát khỏi trạng thái gián đoạn khi bị đánh trúng hoặc tung lên không, được tính là Né Tránh thành công. Nếu họ đang ở trên không, họ sẽ hạ cánh xuống mặt đất. Hiệu ứng này có thể kích hoạt tối đa 5 lần.
+- Khi kích hoạt Né Tránh thành công bằng hiệu ứng trên, Shorekeeper sẽ phục hồi {0} HP mỗi giây cho đến khi cô chịu DMG. Khi hiệu ứng trên chưa được kích hoạt, Shorekeeper nhận thêm {1} Tăng Sát Thương Spectro.</t>
         </is>
       </c>
     </row>
@@ -26015,8 +26015,8 @@
         <is>
           <t>&lt;color=#c49e55&gt;[Forte Circuit]&lt;/color&gt;
 Mỗi 30 giây, nhận các hiệu ứng sau:
-- Sử dụng Dodge sẽ giúp các Resonator trong đội gần đó thoát khỏi trạng thái gián đoạn khi bị đánh trúng hoặc tung lên không, được tính là Dodge thành công.
-- Khi kích hoạt Dodge thành công bằng hiệu ứng trên, Shorekeeper sẽ phục hồi HP mỗi giây cho đến khi cô chịu sát thương. Khi hiệu ứng trên chưa được kích hoạt, Shorekeeper nhận thêm Spectro DMG Bonus.</t>
+- Sử dụng Né Tránh sẽ giúp các Cộng Hưởng Giả trong đội gần đó thoát khỏi trạng thái gián đoạn khi bị đánh trúng hoặc tung lên không, được tính là Né Tránh thành công.
+- Khi kích hoạt Né Tránh thành công bằng hiệu ứng trên, Shorekeeper sẽ phục hồi HP mỗi giây cho đến khi cô chịu DMG. Khi hiệu ứng trên chưa được kích hoạt, Shorekeeper nhận thêm Tăng Sát Thương Spectro.</t>
         </is>
       </c>
     </row>
@@ -26086,8 +26086,8 @@
         <is>
           <t>&lt;color=Highlight&gt;[Forte Circuit]&lt;/color&gt;
 Mỗi 30 giây sẽ nhận các hiệu ứng sau:
-- Sử dụng Dodge sẽ giúp Resonators đang hoạt động gần đó trong đội hồi phục khỏi trạng thái gián đoạn khi bị tấn công hoặc tung lên, được tính là Dodge thành công.
-- Khi kích hoạt Dodge thành công bằng hiệu ứng trên, Shorekeeper sẽ phục hồi HP mỗi giây cho đến khi cô chịu sát thương. Nếu hiệu ứng trên không được kích hoạt, Shorekeeper sẽ nhận thêm Spectro DMG.</t>
+- Sử dụng Né Tránh sẽ giúp Resonator đang hoạt động gần đó trong đội hồi phục khỏi trạng thái gián đoạn khi bị tấn công hoặc tung lên, được tính là Né Tránh thành công.
+- Khi kích hoạt Né Tránh thành công bằng hiệu ứng trên, Shorekeeper sẽ phục hồi HP mỗi giây cho đến khi cô chịu DMG. Nếu hiệu ứng trên không được kích hoạt, Shorekeeper sẽ nhận thêm Sát Thương Spectro.</t>
         </is>
       </c>
     </row>
@@ -26155,8 +26155,8 @@
       <c r="M384" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Resonance Skill]&lt;/color&gt;
-Khi Thanh Cầu Nguyện đầy, Phoebe chỉ có thể sử dụng Heavy Attack - Thánh Ca Giải Oan.
-Hệ số sát thương của Vòng Gương được triệu hồi bởi Resonance Skill tăng thêm {0}, phạm vi tấn công cũng được mở rộng thêm {1}. Khi Vòng Gương còn tồn tại, nó sẽ hút mục tiêu xung quanh mỗi {2} giây và tung ra Đòn Sóng Xung Kích &lt;SapTag=3&gt;{3}&lt;/SapTag&gt; {Cus:Sap,S=lần P=lần SapTag=3}, gây sát thương bằng {4} sức tấn công của Vòng Gương và áp dụng &lt;SapTag=5&gt;{5}&lt;/SapTag&gt; {Cus:Sap,S=lớp P=lớp SapTag=5} trạng thái Spectro Frazzle khi trúng đích. Khi Đòn Sóng Xung Kích trúng mục tiêu, Phoebe sẽ hồi phục thêm {6} điểm Cầu Nguyện.</t>
+Khi Thanh Cầu Nguyện đầy, Phoebe chỉ có thể sử dụng Đòn Heavy Attack - Thánh Ca Giải Oan.
+Hệ số DMG của Vòng Gương được triệu hồi bởi Resonance Skill tăng thêm {0}, phạm vi tấn công cũng được mở rộng thêm {1}. Khi Vòng Gương còn tồn tại, nó sẽ hút mục tiêu xung quanh mỗi {2} giây và tung ra Đòn Sóng Xung Kích &lt;SapTag=3&gt;{3}&lt;/SapTag&gt; {Cus:Sap,S=lần P=lần SapTag=3}, gây DMG bằng {4} sức tấn công của Vòng Gương và áp dụng &lt;SapTag=5&gt;{5}&lt;/SapTag&gt; {Cus:Sap,S=lớp P=lớp SapTag=5} trạng thái Rối Loạn Spectro khi trúng đích. Khi Đòn Sóng Xung Kích trúng mục tiêu, Phoebe sẽ hồi phục thêm {6} điểm Cầu Nguyện.</t>
         </is>
       </c>
     </row>
@@ -26223,7 +26223,7 @@
       <c r="M385" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Resonance Skill]&lt;/color&gt;
-Khi Thanh Cầu Nguyện đầy, Phoebe chỉ có thể sử dụng Heavy Attack - Thánh Ca Giải Oan. Vòng Gương được triệu hồi bởi Resonance Skill sẽ nhận được những nâng cấp đặc biệt.</t>
+Khi Thanh Cầu Nguyện đầy, Phoebe chỉ có thể sử dụng Đòn Heavy Attack - Thánh Ca Giải Oan. Vòng Gương được triệu hồi bởi Resonance Skill sẽ nhận được những nâng cấp đặc biệt.</t>
         </is>
       </c>
     </row>
@@ -26291,7 +26291,7 @@
       <c r="M386" t="inlineStr">
         <is>
           <t>&lt;color=Highlight&gt;[Resonance Skill]&lt;/color&gt;
-- Khi Thanh Cầu Nguyện đầy, Phoebe chỉ có thể sử dụng Heavy Attack - Khúc Thánh Ca Giải Oan.
+- Khi Thanh Cầu Nguyện đầy, Phoebe chỉ có thể sử dụng Đòn Heavy Attack - Khúc Thánh Ca Giải Oan.
 - Vòng Gương được triệu hồi bởi Resonance Skill được tăng cường.</t>
         </is>
       </c>
@@ -26361,9 +26361,9 @@
       <c r="M387" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Basic Attack]&lt;/color&gt;
-Các mục tiêu trong Ring of Mirrors chịu thêm {0} Spectro DMG.
+Các mục tiêu trong Ring of Mirrors chịu thêm {0} Sát Thương Spectro.
 Đánh trúng mục tiêu bằng Basic Attack sẽ tạo &lt;SapTag=1&gt;{1}&lt;/SapTag&gt; {Cus:Sap,S=tầng P=tầng SapTag=1} Hymn, tối đa &lt;SapTag=2&gt;{2}&lt;/SapTag&gt; {Cus:Sap,S=tầng P=tầng SapTag=2}. Hiệu ứng này có thể kích hoạt &lt;SapTag=3&gt;{3}&lt;/SapTag&gt; {Cus:Sap,S=lần P=lần SapTag=3} mỗi giây.
-Khi đạt tối đa tầng Hymn, tất cả các tầng sẽ bị loại bỏ để kích nổ một lần, gây tổng Spectro DMG bằng {4} Attack của Phoebe, được tính là Sát Thương Basic Attack.</t>
+Khi đạt tối đa tầng Hymn, tất cả các tầng sẽ bị loại bỏ để kích nổ một lần, gây tổng Sát Thương Spectro bằng {4} ATK của Phoebe, được tính là Sát Thương Basic Attack.</t>
         </is>
       </c>
     </row>
@@ -26431,8 +26431,8 @@
       <c r="M388" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Basic Attack]&lt;/color&gt;
-Các mục tiêu trong Ring of Mirrors chịu nhiều Spectro DMG hơn.
-Basic Attack tạo Hymn và gây sát thương khi kích nổ.</t>
+Các mục tiêu trong Ring of Mirrors chịu nhiều Sát Thương Spectro hơn.
+Basic Attack tạo Hymn và gây DMG khi kích nổ.</t>
         </is>
       </c>
     </row>
@@ -26500,7 +26500,7 @@
       <c r="M389" t="inlineStr">
         <is>
           <t>&lt;color=Highlight&gt;[Basic Attack]&lt;/color&gt;
-- Mục tiêu trong Vòng Gương nhận thêm Spectro DMG.
+- Mục tiêu trong Vòng Gương nhận thêm Sát Thương Spectro.
 - Basic Attack của Phoebe tạo ra Hymn, có thể kích nổ để gây Sát Thương.</t>
         </is>
       </c>
@@ -26571,9 +26571,9 @@
       <c r="M390" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Forte Circuit]&lt;/color&gt;
-Khi Thanh Cầu Nguyện đầy, Phoebe chỉ có thể tung Heavy Attack - Khúc Thánh Ca Giải Oan.
-Thi triển Khúc Thánh Ca Giải Oan sẽ nhận &lt;SapTag=0&gt;{0}&lt;/SapTag&gt; {Cus:Sap,S=lớp P=lớp SapTag=0} Gương Light. Khi không có Giọng nói Thần, Đòn Mid-air Attack sẽ tiêu hao &lt;SapTag=1&gt;{1}&lt;/SapTag&gt; {Cus:Sap,S=lớp P=lớp SapTag=1} Gương Light để hồi phục &lt;SapTag=2&gt;{2}&lt;/SapTag&gt; {Cus:Sap,S=điểm P=điểm SapTag=2} Giọng nói Thần khi trúng đích.
-Khi Phoebe đang giữ Giọng nói Thần, chi phí STA của Heavy Attack Trên Không sẽ giảm. Thi triển Heavy Attack Trên Không sẽ triệu hồi Prism Light gây Spectro DMG bằng {3} Attack của Phoebe (được tính là Sát Thương Basic Attack) lên mục tiêu và tung Heavy Attack - Sao Lóe.
+Khi Thanh Cầu Nguyện đầy, Phoebe chỉ có thể tung Đòn Heavy Attack - Khúc Thánh Ca Giải Oan.
+Thi triển Khúc Thánh Ca Giải Oan sẽ nhận &lt;SapTag=0&gt;{0}&lt;/SapTag&gt; {Cus:Sap,S=lớp P=lớp SapTag=0} Gương Ánh Sáng. Khi không có Giọng Thần, Đòn Mid-air Attack sẽ tiêu hao &lt;SapTag=1&gt;{1}&lt;/SapTag&gt; {Cus:Sap,S=lớp P=lớp SapTag=1} Gương Ánh Sáng để hồi phục &lt;SapTag=2&gt;{2}&lt;/SapTag&gt; {Cus:Sap,S=điểm P=điểm SapTag=2} Giọng Thần khi trúng đích.
+Khi Phoebe đang giữ Giọng Thần, chi phí STA của Đòn Heavy Attack Trên Không sẽ giảm. Thi triển Đòn Heavy Attack Trên Không sẽ triệu hồi Lăng Kính Ánh Sáng gây Sát Thương Spectro bằng {3} ATK của Phoebe (được tính là Sát Thương Đòn Basic Attack) lên mục tiêu và tung Đòn Heavy Attack - Sao Lóe.
 Trúng đích bằng Sao Lóe sẽ gây &lt;SapTag=4&gt;{4}&lt;/SapTag&gt; {Cus:Sap,S=lớp P=lớp SapTag=4} Spectro Frazzle.</t>
         </is>
       </c>
@@ -26641,7 +26641,7 @@
       <c r="M391" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Forte Circuit]&lt;/color&gt;
-Khi Thanh Cầu Nguyện đầy, Phoebe chỉ có thể tung Heavy Attack - Khúc Thánh Ca Giải Oan. Heavy Attack - Khúc Thánh Ca Giải Oan và Heavy Attack Trên Không sẽ được tăng cường đặc biệt.</t>
+Khi Thanh Cầu Nguyện đầy, Phoebe chỉ có thể tung Đòn Heavy Attack - Khúc Thánh Ca Giải Oan. Đòn Heavy Attack - Khúc Thánh Ca Giải Oan và Đòn Heavy Attack Trên Không sẽ được tăng cường đặc biệt.</t>
         </is>
       </c>
     </row>
@@ -26709,8 +26709,8 @@
       <c r="M392" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Forte Circuit]&lt;/color&gt;
-Số lượng Gương Light Phoebe nhận được tăng lên {0}.
-Với mỗi lớp Spectro Frazzle mục tiêu chịu, Phoebe gây thêm {1} Spectro DMG, tối đa {2}.</t>
+Số lượng Gương Ánh Sáng Phoebe nhận được tăng lên {0}.
+Với mỗi lớp Spectro Frazzle mục tiêu chịu, Phoebe gây thêm {1} Sát Thương Spectro, tối đa {2}.</t>
         </is>
       </c>
     </row>
@@ -26777,7 +26777,7 @@
       <c r="M393" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Forte Circuit]&lt;/color&gt;
-Số lượng Gương Light Phoebe nhận được tăng lên. Phoebe gây thêm Spectro DMG lên mục tiêu bị Spectro Frazzle.</t>
+Số lượng Gương Ánh Sáng Phoebe nhận được tăng lên. Phoebe gây thêm Sát Thương Spectro lên mục tiêu bị Spectro Frazzle.</t>
         </is>
       </c>
     </row>
@@ -26846,9 +26846,9 @@
       <c r="M394" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Resonance Liberation]&lt;/color&gt;
-Spectro DMG Bonus thêm {0}.
-Khi thi triển Resonance Liberation - Dawn Khải Tâm, kích hoạt một vụ nổ nhỏ &lt;SapTag=1&gt;{1}&lt;/SapTag&gt; {Cus:Sap,S=lần P=lần SapTag=1}, mỗi lần gây Spectro DMG bằng {2} Attack của Phoebe (được tính là sát thương Kỹ Năng Basic).
-Đánh trúng mục tiêu bằng Resonance Liberation sẽ giảm Spectro RES của chúng {3} trong {4} giây.</t>
+Tăng DMG Spectro thêm {0}.
+Khi thi triển Resonance Liberation - Bình Minh Khải Tâm, kích hoạt một vụ nổ nhỏ &lt;SapTag=1&gt;{1}&lt;/SapTag&gt; {Cus:Sap,S=lần P=lần SapTag=1}, mỗi lần gây DMG Spectro bằng {2} ATK của Phoebe (được tính là DMG Kỹ Năng Cơ Bản).
+Đánh trúng mục tiêu bằng Resonance Liberation sẽ giảm Kháng Spectro của chúng {3} trong {4} giây.</t>
         </is>
       </c>
     </row>
@@ -26915,7 +26915,7 @@
       <c r="M395" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Resonance Liberation]&lt;/color&gt;
-Spectro DMG Bonus và Resonance Liberation nhận được những tăng cường đặc biệt.</t>
+Tăng DMG Spectro và Resonance Liberation nhận được những tăng cường đặc biệt.</t>
         </is>
       </c>
     </row>
@@ -26982,7 +26982,7 @@
       <c r="M396" t="inlineStr">
         <is>
           <t>&lt;color=Highlight&gt;Resonance Liberation&lt;/color&gt;
-Spectro DMG Bonus và nâng cấp Resonance Liberation.</t>
+Tăng Sát Thương Spectro và nâng cấp Resonance Liberation.</t>
         </is>
       </c>
     </row>
@@ -27054,11 +27054,11 @@
       <c r="M397" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Forte Circuit]&lt;/color&gt;
-Đòn Chém Nặng - Hoàng Hôn và đòn đánh cuối của Giai Đoạn Basic Attack {0} sẽ tạo ra &lt;SapTag=1&gt;{1}&lt;/SapTag&gt; {Cus:Sap,S=Ngọn Lửa P=Ngọn Lửa SapTag=1} và {2} Resonance Energy.
+Đòn Chém Nặng - Hoàng Hôn và đòn đánh cuối của Giai Đoạn Basic Attack {0} sẽ tạo ra &lt;SapTag=1&gt;{1}&lt;/SapTag&gt; {Cus:Ipt,Touch=tapping PC=pressing Gamepad=pressing} và {2} Resonance Energy.
 Khi ở Tư Thế Sẵn Sàng, phục hồi &lt;SapTag=3&gt;{3}&lt;/SapTag&gt; {Cus:Sap,S=Ngọn Lửa P=Ngọn Lửa SapTag=3} mỗi giây, và ngay lập tức phục hồi &lt;SapTag=4&gt;{4}&lt;/SapTag&gt; {Cus:Sap,S=Ngọn Lửa P=Ngọn Lửa SapTag=4} khi bị tấn công, đồng thời nhận một lá chắn bằng {5} HP tối đa. Hiệu ứng này kéo dài trong {6} giây.
-Khi Ngọn Lửa đạt tối đa trong Inferno Mode:
-Khi {Cus:Ipt,Touch=tap PC=press Gamepad=press} hoặc thả nút Resonance Skill trong Tư Thế Sẵn Sàng, khi Tư Thế Sẵn Sàng kết thúc, hoặc khi bị tấn công trong Tư Thế Sẵn Sàng, tiêu hao toàn bộ Ngọn Lửa để tung ra Đòn Chém Nặng - Hoàng Hôn: Không Ai Sống Sót.
-Đòn Chém Nặng - Hoàng Hôn: Không Ai Sống Sót gây Spectro DMG bằng {7} Attack của Resonator đang kích hoạt, được tính là sát thương của Heavy Attack và Spectro DMG Frazzle.
+Khi Ngọn Lửa đạt tối đa trong Chế Độ Hỏa Ngục:
+Khi {Cus:Ipt,Touch=chạm PC=nhấn Gamepad=nhấn} hoặc thả nút Resonance Skill trong Tư Thế Sẵn Sàng, khi Tư Thế Sẵn Sàng kết thúc, hoặc khi bị tấn công trong Tư Thế Sẵn Sàng, tiêu hao toàn bộ Ngọn Lửa để tung ra Đòn Chém Nặng - Hoàng Hôn: Không Ai Sống Sót.
+Đòn Chém Nặng - Hoàng Hôn: Không Ai Sống Sót gây DMG Spectro bằng {7} ATK của Resonator đang kích hoạt, được tính là DMG của Đòn Heavy Attack và DMG Spectro Frazzle.
 Khi Zani tham gia với tư cách Đồng Hành Concerto, Forte Circuit - Than Hồng Sáng Thế sẽ không có hiệu lực.</t>
         </is>
       </c>
@@ -27128,7 +27128,7 @@
         <is>
           <t>&lt;color=#c49e55&gt;[Forte Circuit]&lt;/color&gt;
 Đòn Chém Nặng - Hoàng Hôn và Giai Đoạn Basic Attack 4 sẽ tạo thêm Ngọn Lửa và Resonance Energy.
-Tư Thế Sẵn Sàng trong Inferno Mode được tăng cường đặc biệt. Khi Ngọn Lửa đạt tối đa, Resonance Skill sẽ được tăng cường đặc biệt.</t>
+Tư Thế Sẵn Sàng trong Chế Độ Hỏa Ngục được tăng cường đặc biệt. Khi Ngọn Lửa đạt tối đa, Resonance Skill sẽ được tăng cường đặc biệt.</t>
         </is>
       </c>
     </row>
@@ -27203,13 +27203,13 @@
         <is>
           <t>&lt;color=#c49e55&gt;[Resonance Liberation]&lt;/color&gt;
 Loại bỏ giới hạn {0} Ngọn Lửa của Lá Chắn Cuối Cùng, nhưng chỉ có thể sử dụng &lt;SapTag=2&gt;{2}&lt;/SapTag&gt; {Cus:Sap,S=lần P=lần SapTag=2} trong {1} giây.
-Khi Zani sử dụng Resonance Liberation - Giữa Dawn Và Hoàng Hôn cùng Lá Chắn Cuối Cùng, cô sẽ nhận được một tầng Đếm Đến Ngày Tận Thế, có thể chồng chất lên đến {3} tầng.
+Khi Zani sử dụng Resonance Liberation - Giữa Bình Minh Và Hoàng Hôn cùng Lá Chắn Cuối Cùng, cô sẽ nhận được một tầng Đếm Đến Ngày Tận Thế, có thể chồng chất lên đến {3} tầng.
 Lá Chắn Cuối Cùng nhận được các nâng cấp có thể chồng chất dựa trên số tầng Đếm Đến Ngày Tận Thế:
-- Tầng 1: Sử dụng Lá Chắn Cuối Cùng sẽ làm mới thời gian duy trì Inferno Mode và nhận thêm &lt;SapTag=4&gt;{4}&lt;/SapTag&gt; {Cus:Sap,S=Ngọn Lửa P=Ngọn Lửa SapTag=4}.
+- Tầng 1: Sử dụng Lá Chắn Cuối Cùng sẽ làm mới thời gian duy trì Chế Độ Hỏa Ngục và nhận thêm &lt;SapTag=4&gt;{4}&lt;/SapTag&gt; {Cus:Sap,S=Ngọn Lửa P=Ngọn Lửa SapTag=4}.
 - Tầng 2: Phạm vi của Lá Chắn Cuối Cùng được mở rộng.
-- Tầng 3: Hệ Số Sát Thương của Lá Chắn Cuối Cùng tăng thêm {5} mỗi giây trong Inferno Mode.
-Sau khi sử dụng Lá Chắn Cuối Cùng {6} lần trong Inferno Mode, Inferno Mode sẽ kết thúc và xóa tất cả tầng Đếm Đến Ngày Tận Thế.
-Khi Zani tham gia với tư cách Đồng Hành Concerto, Forte Circuit - Than Hồng Dawn sẽ không có hiệu lực.</t>
+- Tầng 3: Hệ Số Sát Thương của Lá Chắn Cuối Cùng tăng thêm {5} mỗi giây trong Chế Độ Hỏa Ngục.
+Sau khi sử dụng Lá Chắn Cuối Cùng {6} lần trong Chế Độ Hỏa Ngục, Chế Độ Hỏa Ngục sẽ kết thúc và xóa tất cả tầng Đếm Đến Ngày Tận Thế.
+Khi Zani tham gia với tư cách Đồng Hành Concerto, Forte Circuit - Than Hồng Bình Minh sẽ không có hiệu lực.</t>
         </is>
       </c>
     </row>
@@ -27276,7 +27276,7 @@
       <c r="M400" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Resonance Liberation]&lt;/color&gt;
-Lá Chắn Cuối Cùng nhận thêm số lần sử dụng và nâng cấp dựa trên thời gian duy trì Inferno Mode.</t>
+Lá Chắn Cuối Cùng nhận thêm số lần sử dụng và nâng cấp dựa trên thời gian duy trì Chế Độ Hỏa Ngục.</t>
         </is>
       </c>
     </row>
@@ -27346,7 +27346,7 @@
         <is>
           <t>&lt;color=#c49e55&gt;[Forte Circuit]&lt;/color&gt;
 Zani nhận một tầng Đếm Ngược Tàn Khốc khi sử dụng Heavy Slash - Nightfall.
-Mỗi tầng Đếm Ngược Tàn Khốc tăng Spectro DMG của Zani lên {0}.
+Mỗi tầng Đếm Ngược Tàn Khốc tăng Sát Thương Spectro của Zani lên {0}.
 Kết thúc chế độ Inferno sẽ xóa tất cả tầng Đếm Ngược Tàn Khốc.</t>
         </is>
       </c>
@@ -27414,7 +27414,7 @@
       <c r="M402" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Forte Circuit]&lt;/color&gt;
-Sử dụng Heavy Slash - Night Fall sẽ nhận được Imminent Reckoning làm tăng Spectro DMG.</t>
+Sử dụng Heavy Slash - Night Fall sẽ nhận được Imminent Reckoning làm tăng Sát Thương Spectro.</t>
         </is>
       </c>
     </row>
@@ -27481,7 +27481,7 @@
       <c r="M403" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Forte Circuit]&lt;/color&gt;
-Khi Zani sử dụng Kỹ Năng Nặng - Hoàng Hôn, có {0}% cơ hội thay thế Basic Attack tiếp theo bằng Kỹ Năng Nặng - Hoàng Hôn.</t>
+Khi Zani sử dụng Kỹ Năng Nặng - Hoàng Hôn, có {0}% cơ hội thay thế Đòn Cơ Bản tiếp theo bằng Kỹ Năng Nặng - Hoàng Hôn.</t>
         </is>
       </c>
     </row>
@@ -27546,7 +27546,7 @@
       </c>
       <c r="M404" t="inlineStr">
         <is>
-          <t>&lt;color=#c49e55&gt;[Forte Circuit]&lt;/color&gt; Khi sử dụng Kỹ Năng Đòn Trọng - Hoàng Hôn, có khả năng thay thế Basic Attack tiếp theo bằng Kỹ Năng Đòn Trọng - Hoàng Hôn.</t>
+          <t>&lt;color=#c49e55&gt;[Forte Circuit]&lt;/color&gt; Khi sử dụng Kỹ Năng Đòn Trọng - Hoàng Hôn, có khả năng thay thế Đòn Cơ Bản tiếp theo bằng Kỹ Năng Đòn Trọng - Hoàng Hôn.</t>
         </is>
       </c>
     </row>
@@ -27613,7 +27613,7 @@
       <c r="M405" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Forte Circuit]&lt;/color&gt;
-Bước Nhảy Cuối Cùng và đòn cuối của Đòn Tấn Công Mạnh - Hoàng Hôn khi trúng mục tiêu sẽ giảm Spectro RES DMG của mục tiêu đi {0} trong {1} giây.</t>
+Bước Nhảy Cuối Cùng và đòn cuối của Đòn Tấn Công Mạnh - Hoàng Hôn khi trúng mục tiêu sẽ giảm Kháng Sát Thương Spectro của mục tiêu đi {0} trong {1} giây.</t>
         </is>
       </c>
     </row>
@@ -27680,7 +27680,7 @@
       <c r="M406" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Forte Circuit]&lt;/color&gt;
-Bước Nhảy Cuối Cùng và đòn cuối của Đòn Tấn Công Mạnh - Hoàng Hôn khi trúng mục tiêu sẽ giảm Spectro RES của mục tiêu.</t>
+Bước Nhảy Cuối Cùng và đòn cuối của Đòn Tấn Công Mạnh - Hoàng Hôn khi trúng mục tiêu sẽ giảm Kháng Spectro của mục tiêu.</t>
         </is>
       </c>
     </row>
@@ -27747,7 +27747,7 @@
       <c r="M407" t="inlineStr">
         <is>
           <t>&lt;color=Highlight&gt;[Forte Circuit]&lt;/color&gt;
-Mỗi khi Chisa gây sát thương &lt;color=Highlight&gt;{0}&lt;/color&gt; lần, Số Mệnh Xé Nát sẽ được kích hoạt, gây Havoc DMG bằng &lt;color=Highlight&gt;{1}&lt;/color&gt; Tấn Công của Chisa (được tính là Sát Thương Resonance Liberation) và áp đặt Havoc Bane. Hiệu ứng này có thể kích hoạt &lt;color=Highlight&gt;&lt;SapTag=2&gt;{2}&lt;/SapTag&gt;&lt;/color&gt; {Cus:Sap,S=lần P=lần SapTag=2} mỗi giây.</t>
+Mỗi khi Chisa gây DMG &lt;color=Highlight&gt;{0}&lt;/color&gt; lần, Số Mệnh Xé Nát sẽ được kích hoạt, gây Sát Thương Havoc bằng &lt;color=Highlight&gt;{1}&lt;/color&gt; ATK của Chisa (được tính là Sát Thương Resonance Liberation) và áp đặt Hiểm Họa Havoc. Hiệu ứng này có thể kích hoạt &lt;color=Highlight&gt;&lt;SapTag=2&gt;{2}&lt;/SapTag&gt;&lt;/color&gt; {Cus:Sap,S=lần P=lần SapTag=2} mỗi giây.</t>
         </is>
       </c>
     </row>
@@ -27814,7 +27814,7 @@
       <c r="M408" t="inlineStr">
         <is>
           <t>&lt;color=Highlight&gt;[Forte Circuit]&lt;/color&gt;
-Mỗi khi Chisa gây sát thương &lt;color=Highlight&gt;{0}&lt;/color&gt; lần, Số Mệnh Xé Nát sẽ được kích hoạt, gây Havoc DMG và áp đặt Havoc Bane.</t>
+Mỗi khi Chisa gây DMG &lt;color=Highlight&gt;{0}&lt;/color&gt; lần, Số Mệnh Xé Nát sẽ được kích hoạt, gây Sát Thương Havoc và áp đặt Hiểm Họa Havoc.</t>
         </is>
       </c>
     </row>
@@ -27881,7 +27881,7 @@
       <c r="M409" t="inlineStr">
         <is>
           <t>&lt;color=Highlight&gt;[Forte Circuit]&lt;/color&gt;
-Khi ở Chế Độ Chainsaw và sau khi sử dụng Chainsaw - Tiêu Diệt, dùng Kỹ Năng Basic để thi triển Chainsaw - Trừng Phạt, gây Havoc DMG bằng &lt;color=Highlight&gt;{0}&lt;/color&gt; Attack của Chisa (được tính là Sát Thương Resonance Liberation) và phục hồi &lt;color=Highlight&gt;{1}&lt;/color&gt; điểm Resonance Energy.</t>
+Khi ở Chế Độ Cưa Xích và sau khi sử dụng Cưa Xích - Tiêu Diệt, dùng Kỹ Năng Cơ Bản để thi triển Cưa Xích - Trừng Phạt, gây Sát Thương Havoc bằng &lt;color=Highlight&gt;{0}&lt;/color&gt; ATK của Chisa (được tính là Sát Thương Resonance Liberation) và phục hồi &lt;color=Highlight&gt;{1}&lt;/color&gt; điểm Resonance Energy.</t>
         </is>
       </c>
     </row>
@@ -27948,7 +27948,7 @@
       <c r="M410" t="inlineStr">
         <is>
           <t>&lt;color=Highlight&gt;[Forte Circuit]&lt;/color&gt;
-Khi ở Chế Độ Chainsaw và sau khi sử dụng Chainsaw - Tiêu Diệt, dùng Kỹ Năng Basic để thi triển Chainsaw - Trừng Phạt.</t>
+Khi ở Chế Độ Cưa Xích và sau khi sử dụng Cưa Xích - Tiêu Diệt, dùng Kỹ Năng Cơ Bản để thi triển Cưa Xích - Trừng Phạt.</t>
         </is>
       </c>
     </row>
@@ -28017,9 +28017,9 @@
       <c r="M411" t="inlineStr">
         <is>
           <t>&lt;color=Highlight&gt;[Forte Circuit]&lt;/color&gt;
-- Cooldown chiêu của Resonance Skill - Mắt Giải Mê giảm &lt;color=Highlight&gt;{0} giây&lt;/color&gt;.
-- Kích hoạt Resonance Skill - Mắt Giải Mê sẽ hồi &lt;color=Highlight&gt;{1}&lt;/color&gt; điểm Resonance Energy và tạo ra &lt;color=Highlight&gt;&lt;SapTag=4&gt;{4}&lt;/SapTag&gt;&lt;/color&gt; điểm Vòng Chainsaw.
-- Kích hoạt Resonance Skill - Vòng Lặp Răng Cưa sẽ tăng &lt;color=Highlight&gt;{2}&lt;/color&gt; Havoc DMG trong &lt;color=Highlight&gt;{3}s&lt;/color&gt;.</t>
+- Thời gian hồi chiêu của Resonance Skill - Mắt Giải Mê giảm &lt;color=Highlight&gt;{0} giây&lt;/color&gt;.
+- Kích hoạt Resonance Skill - Mắt Giải Mê sẽ hồi &lt;color=Highlight&gt;{1}&lt;/color&gt; điểm Resonance Energy và tạo ra &lt;color=Highlight&gt;&lt;SapTag=4&gt;{4}&lt;/SapTag&gt;&lt;/color&gt; điểm Vòng Cưa Xích.
+- Kích hoạt Resonance Skill - Vòng Lặp Răng Cưa sẽ tăng &lt;color=Highlight&gt;{2}&lt;/color&gt; DMG Havoc trong &lt;color=Highlight&gt;{3} giây&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -28088,9 +28088,9 @@
       <c r="M412" t="inlineStr">
         <is>
           <t>&lt;color=Highlight&gt;[Forte Circuit]&lt;/color&gt;
-- Cooldown chiêu của Resonance Skill - Mắt Giải Mê được rút ngắn.
-- Kích hoạt Resonance Skill - Mắt Giải Mê sẽ hồi Resonance Energy và tạo ra Vòng Chainsaw.
-- Kích hoạt Resonance Skill - Vòng Lặp Răng Cưa sẽ tăng Havoc DMG.</t>
+- Thời gian hồi chiêu của Resonance Skill - Mắt Giải Mê được rút ngắn.
+- Kích hoạt Resonance Skill - Mắt Giải Mê sẽ hồi Resonance Energy và tạo ra Vòng Cưa Xích.
+- Kích hoạt Resonance Skill - Vòng Lặp Răng Cưa sẽ tăng DMG Havoc.</t>
         </is>
       </c>
     </row>
@@ -28157,7 +28157,7 @@
       <c r="M413" t="inlineStr">
         <is>
           <t>&lt;color=Highlight&gt;[Resonance Liberation]&lt;/color&gt;
-Resonance Liberation - Khoảnh Khắc Hư Vô có tổng Sát Thương tăng thêm &lt;color=Highlight&gt;{0}&lt;/color&gt; và Cooldown chiêu giảm &lt;color=Highlight&gt;{1}s&lt;/color&gt;.</t>
+Resonance Liberation - Khoảnh Khắc Hư Vô có tổng Sát Thương tăng thêm &lt;color=Highlight&gt;{0}&lt;/color&gt; và Thời gian hồi chiêu giảm &lt;color=Highlight&gt;{1} giây&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -28224,7 +28224,7 @@
       <c r="M414" t="inlineStr">
         <is>
           <t>&lt;color=Highlight&gt;[Resonance Liberation]&lt;/color&gt;
-Resonance Liberation - Khoảnh Khắc Hư Vô có tổng Sát Thương cao hơn và Cooldown chiêu ngắn hơn.</t>
+Resonance Liberation - Khoảnh Khắc Hư Vô có tổng Sát Thương cao hơn và Thời gian hồi chiêu ngắn hơn.</t>
         </is>
       </c>
     </row>
@@ -28289,7 +28289,7 @@
       </c>
       <c r="M415" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Companion's Aid]&lt;/color&gt; Summon Danjin để tung chiêu Resonance Liberation khi Năng Lượng Khúc Tụ đã đầy, kích hoạt Kỹ Năng Khởi Đầu.</t>
+          <t>&lt;color=#ffd12f&gt;[Hỗ Trợ Đồng Hành]&lt;/color&gt; Triệu hồi Danjin để tung chiêu Resonance Liberation khi Năng Lượng Khúc Tụ đã đầy, kích hoạt Kỹ Năng Khởi Đầu.</t>
         </is>
       </c>
     </row>
@@ -28425,11 +28425,11 @@
       <c r="M417" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Basic Attack]&lt;/color&gt;
-Khi Camellya trúng mục tiêu bằng các đòn Basic Attack hoặc kỹ năng sau đây, cô sẽ triệu hồi thêm dây leo gây Havoc DMG bằng {0} Attack của mình:
-- Stage 4 Basic Attack
-- Stage 3 Vining Waltz và Blazing Waltz của Basic Attack
+Khi Camellya trúng mục tiêu bằng các đòn Basic Attack hoặc kỹ năng sau đây, cô sẽ triệu hồi thêm dây leo gây Sát Thương Havoc bằng {0} ATK của mình:
+- Giai Đoạn 4 Basic Attack
+- Giai Đoạn 3 Vining Waltz và Blazing Waltz của Basic Attack
 - Resonance Skill Crimson Blossom hoặc Floral Ravage
-Sát thương gây ra được tính là Sát Thương Basic Attack, kích hoạt mỗi 1 giây một lần.</t>
+DMG gây ra được tính là Sát Thương Basic Attack, kích hoạt mỗi 1 giây một lần.</t>
         </is>
       </c>
     </row>
@@ -28499,9 +28499,9 @@
       <c r="M418" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Basic Attack]&lt;/color&gt;
-Khi Camellya trúng mục tiêu bằng các đòn Basic Attack hoặc kỹ năng sau đây, cô sẽ triệu hồi thêm dây leo gây Havoc DMG:
-- Stage 4 Basic Attack
-- Stage 3 Vining Waltz và Blazing Waltz của Basic Attack
+Khi Camellya trúng mục tiêu bằng các đòn Basic Attack hoặc kỹ năng sau đây, cô sẽ triệu hồi thêm dây leo gây Sát Thương Havoc:
+- Giai Đoạn 4 Basic Attack
+- Giai Đoạn 3 Vining Waltz và Blazing Waltz của Basic Attack
 - Resonance Skill Crimson Blossom hoặc Floral Ravage</t>
         </is>
       </c>
@@ -28572,10 +28572,10 @@
       <c r="M419" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Basic Attack]&lt;/color&gt;
-- Nhận hiệu ứng Glean: Restore {0} Crimson Pistil mỗi giây (không cộng dồn).
+- Nhận hiệu ứng Glean: Hồi phục {0} Crimson Pistil mỗi giây (không cộng dồn).
 - Blazing Walt không còn tiêu hao STA.
-- Basic Attack Stage 4, Vining Waltz Stage 3 và Blazing Waltz giờ đây giảm Vibration Strength của kẻ địch mạnh hơn. Giữ nút Normal Attack để kéo dài thời gian.
-- Basic Attack Stage 4, Vining Waltz Stage 3 và Blazing Waltz giảm Havoc RES của kẻ địch {1} trong {2} giây khi gây sát thương, tối đa {3} lần.</t>
+- Basic Attack Giai Đoạn 4, Vining Waltz Giai Đoạn 3 và Blazing Waltz giờ đây giảm Vibration Strength của kẻ địch mạnh hơn. Giữ nút Normal Attack để kéo dài thời gian.
+- Basic Attack Giai Đoạn 4, Vining Waltz Giai Đoạn 3 và Blazing Waltz giảm Kháng Havoc của kẻ địch {1} trong {2} giây khi gây sát thương, tối đa {3} lần.</t>
         </is>
       </c>
     </row>
@@ -28644,9 +28644,9 @@
       <c r="M420" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Basic Attack]&lt;/color&gt;
-- Nhận hiệu ứng Glean: Restore Crimson Pistil mỗi giây.
+- Nhận hiệu ứng Glean: Hồi phục Crimson Pistil mỗi giây.
 - Blazing Waltz không còn tiêu hao STA.
-- Basic Attack Stage 4, Vining Waltz Stage 3 và Blazing Waltz giờ đây giảm Vibration Strength của kẻ địch mạnh hơn. Giữ nút Normal Attack để kéo dài thời gian. Chúng cũng giảm Havoc RES của kẻ địch khi gây sát thương.</t>
+- Basic Attack Giai Đoạn 4, Vining Waltz Giai Đoạn 3 và Blazing Waltz giờ đây giảm Vibration Strength của kẻ địch mạnh hơn. Giữ nút Normal Attack để kéo dài thời gian. Chúng cũng giảm Kháng Havoc của kẻ địch khi gây sát thương.</t>
         </is>
       </c>
     </row>
@@ -28714,7 +28714,7 @@
       <c r="M421" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Resonance Skill]&lt;/color&gt;
-- Cấp hiệu ứng Glean: Restore {0} Crimson Pistil mỗi giây (không cộng dồn).
+- Cấp hiệu ứng Glean: Hồi phục {0} Crimson Pistil mỗi giây (không cộng dồn).
 - Camellya bước vào chế độ Budding sau khi thi triển Resonance Skill Crimson Blossom hoặc Floral Ravage.</t>
         </is>
       </c>
@@ -28783,7 +28783,7 @@
       <c r="M422" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Resonance Skill]&lt;/color&gt;
-- Cấp hiệu ứng Glean: Restore Crimson Pistil mỗi giây.
+- Cấp hiệu ứng Glean: Hồi phục Crimson Pistil mỗi giây.
 - Camellya bước vào chế độ Budding sau khi thi triển Resonance Skill.</t>
         </is>
       </c>
@@ -28854,8 +28854,8 @@
       <c r="M423" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Basic Attack]&lt;/color&gt;
-Khả năng chống gián đoạn của Camellya được tăng cường khi thực hiện Basic Attack Stage 4, Basic Attack Vining Waltz Stage 3 hoặc Blazing Waltz.
-Khi gây sát thương bằng Basic Attack:
+Khả năng chống gián đoạn của Camellya được tăng cường khi thực hiện Basic Attack Giai Đoạn 4, Basic Attack Vining Waltz Giai Đoạn 3 hoặc Blazing Waltz.
+Khi gây DMG bằng Basic Attack:
 - Camellya hồi {0} HP tối đa, kích hoạt mỗi 1 giây.
 - Camellya sẽ hồi thêm {1} điểm Resonance Energy nếu Forte Gauge chưa đạt tối đa, kích hoạt mỗi {2} giây.</t>
         </is>
@@ -28927,8 +28927,8 @@
       <c r="M424" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Basic Attack]&lt;/color&gt;
-Khả năng chống gián đoạn của Camellya được tăng cường khi thực hiện Basic Attack Stage 4, Basic Attack Vining Waltz Stage 3 hoặc Blazing Waltz.
-Khi gây sát thương bằng Basic Attack:
+Khả năng chống gián đoạn của Camellya được tăng cường khi thực hiện Basic Attack Giai Đoạn 4, Basic Attack Vining Waltz Giai Đoạn 3 hoặc Blazing Waltz.
+Khi gây DMG bằng Basic Attack:
 - Camellya hồi một lượng nhỏ HP.
 - Camellya sẽ hồi thêm Resonance Energy nếu Forte Gauge chưa đạt tối đa.</t>
         </is>
@@ -28999,9 +28999,9 @@
       <c r="M425" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Forte Circuit]&lt;/color&gt;
-- Các đòn tấn công liên tiếp sẽ thay đổi bộ kỹ năng của Camellya, giúp cô có thể sử dụng Basic Attack 4 và Basic Attack Vining Waltz 3 thường xuyên hơn.
-- Camellya sẽ không chịu sát thương trong thời gian ngắn sau khi sử dụng Resonance Skill Crimson Blossom hoặc Floral Ravage. Nếu bị tấn công, Thorny Wellspring sẽ được kích hoạt.
-- Thorny Wellspring: Gây Havoc DMG bằng {0} Attack của Camellya và tạo ra trường trì trệ trong {1} giây.</t>
+- Các đòn tấn công liên tiếp sẽ thay đổi bộ kỹ năng của Camellya, giúp cô có thể sử dụng Đòn Basic Attack 4 và Đòn Basic Attack Vining Waltz 3 thường xuyên hơn.
+- Camellya sẽ không chịu DMG trong thời gian ngắn sau khi sử dụng Resonance Skill Crimson Blossom hoặc Floral Ravage. Nếu bị tấn công, Thorny Wellspring sẽ được kích hoạt.
+- Thorny Wellspring: Gây Sát Thương Havoc bằng {0} ATK của Camellya và tạo ra trường trì trệ trong {1} giây.</t>
         </is>
       </c>
     </row>
@@ -29070,9 +29070,9 @@
       <c r="M426" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Forte Circuit]&lt;/color&gt;
-- Các đòn tấn công liên tiếp sẽ thay đổi bộ kỹ năng của Camellya, giúp cô có thể sử dụng Basic Attack 4 và Basic Attack Vining Waltz 3 thường xuyên hơn.
-- Camellya sẽ không chịu sát thương trong thời gian ngắn sau khi sử dụng Resonance Skill Crimson Blossom hoặc Floral Ravage. Nếu bị tấn công, Thorny Wellspring sẽ được kích hoạt.
-- Thorny Wellspring: Gây Havoc DMG và tạo ra trường trì trệ.</t>
+- Các đòn tấn công liên tiếp sẽ thay đổi bộ kỹ năng của Camellya, giúp cô có thể sử dụng Đòn Basic Attack 4 và Đòn Basic Attack Vining Waltz 3 thường xuyên hơn.
+- Camellya sẽ không chịu DMG trong thời gian ngắn sau khi sử dụng Resonance Skill Crimson Blossom hoặc Floral Ravage. Nếu bị tấn công, Thorny Wellspring sẽ được kích hoạt.
+- Thorny Wellspring: Deals Havoc DMG and generates a stagnation field.</t>
         </is>
       </c>
     </row>
@@ -29139,7 +29139,7 @@
       <c r="M427" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Resonance Skill]&lt;/color&gt;
-Khi Resonance Skill - Lưỡi Kiếm Bay và Resonance Skill - Kẻ Đoạt Mạng trúng mục tiêu, Basic Attack và Basic Attack được tăng cường sẽ bắt đầu từ Giai Đoạn {0}. Trong {1} giây tiếp theo, mỗi khi Basic Attack trúng mục tiêu, sẽ hồi phục {2} Umbra và {3} Resonance Energy. Hiệu ứng này chỉ có thể kích hoạt một lần mỗi giây.</t>
+Khi Resonance Skill - Lưỡi Kiếm Bay và Resonance Skill - Kẻ Đoạt Mạng trúng mục tiêu, Đòn Basic Attack và Đòn Basic Attack được tăng cường sẽ bắt đầu từ Giai Đoạn {0}. Trong {1} giây tiếp theo, mỗi khi Đòn Basic Attack trúng mục tiêu, sẽ hồi phục {2} Umbra và {3} Resonance Energy. Hiệu ứng này chỉ có thể kích hoạt một lần mỗi giây.</t>
         </is>
       </c>
     </row>
@@ -29273,7 +29273,7 @@
       <c r="M429" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Resonance Skill]&lt;/color&gt;
-Phản Đòn Dodge trở thành Resonance Skill - Kẻ Đoạt Mạng. Kẻ Đoạt Mạng tăng gấp đôi số lần tấn công.</t>
+Phản Đòn né trở thành Resonance Skill - Kẻ Đoạt Mạng. Kẻ Đoạt Mạng tăng gấp đôi số lần tấn công.</t>
         </is>
       </c>
     </row>
@@ -29340,7 +29340,7 @@
       <c r="M430" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Resonance Skill]&lt;/color&gt;
-Phản Đòn Dodge trở thành Resonance Skill - Kẻ Đoạt Mạng. Kẻ Đoạt Mạng tăng số lần tấn công.</t>
+Phản Đòn né trở thành Resonance Skill - Kẻ Đoạt Mạng. Kẻ Đoạt Mạng tăng số lần tấn công.</t>
         </is>
       </c>
     </row>
@@ -29407,7 +29407,7 @@
       <c r="M431" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Resonance Liberation]&lt;/color&gt;
-Resonance Liberation - Vực Thẳm Tử Thần sẽ bổ sung thêm &lt;SapTag=0&gt;{0}&lt;/SapTag&gt; {Cus:Sap,S=lần P=lần SapTag=0} vụ nổ. Kích hoạt Resonance Liberation sẽ hồi {1} Umbra. Nếu Rover không ở trong trạng thái Dâng Dark Surge, kích hoạt Resonance Liberation sẽ kích hoạt Dâng Dark Surge, trong đó Havoc DMG được tăng thêm {2}.</t>
+Resonance Liberation - Vực Thẳm Tử Thần sẽ bổ sung thêm &lt;SapTag=0&gt;{0}&lt;/SapTag&gt; {Cus:Sap,S=lần P=lần SapTag=0} vụ nổ. Kích hoạt Resonance Liberation sẽ hồi {1} Umbra. Nếu Rover không ở trong trạng thái Dâng Sóng Bóng Tối, kích hoạt Resonance Liberation sẽ kích hoạt Dâng Sóng Bóng Tối, trong đó Sát Thương Havoc được tăng thêm {2}.</t>
         </is>
       </c>
     </row>
@@ -29541,7 +29541,7 @@
       <c r="M433" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Forte Circuit]&lt;/color&gt;
-Khi Resonance Skill - Kẻ Cướp Mạng gây sát thương, Tấn Công sẽ tăng {0} trong {1} giây, tối đa {2} lần.</t>
+Khi Resonance Skill - Kẻ Cướp Mạng gây sát thương, ATK sẽ tăng {0} trong {1} giây, tối đa {2} lần.</t>
         </is>
       </c>
     </row>
@@ -29608,7 +29608,7 @@
       <c r="M434" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Forte Circuit]&lt;/color&gt;
-Khi Resonance Skill - Kẻ Đoạt Mạng gây sát thương, Tấn Công được tăng lên.</t>
+Khi Resonance Skill - Kẻ Đoạt Mạng gây sát thương, ATK được tăng lên.</t>
         </is>
       </c>
     </row>
@@ -29675,7 +29675,7 @@
       <c r="M435" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Forte Circuit]&lt;/color&gt;
-Khi ở Trạng Thái Bùng Nổ Bóng Tối, trúng mục tiêu bằng Basic Attack sẽ giảm {0} giây Cooldown chiêu Resonance Skill, và trúng mục tiêu bằng Basic Attack Giai Đoạn {1} sẽ kích hoạt thêm Sự Sụp Đổ Bóng Tối, gây Havoc DMG bằng {3} Attack của Rover: Havoc &lt;SapTag=2&gt;{2}&lt;/SapTag&gt; {Cus:Sap,S=lần P=lần SapTag=2}, được tính là Sát Thương Resonance Liberation.</t>
+Khi ở Trạng Thái Bùng Nổ Bóng Tối, trúng mục tiêu bằng Đòn Cơ Bản sẽ giảm {0} giây Thời gian hồi chiêu Resonance Skill, và trúng mục tiêu bằng Đòn Cơ Bản Giai Đoạn {1} sẽ kích hoạt thêm Sự Sụp Đổ Bóng Tối, gây Sát Thương Havoc bằng {3} ATK của Rover: Havoc &lt;SapTag=2&gt;{2}&lt;/SapTag&gt; {Cus:Sap,S=lần P=lần SapTag=2}, được tính là Sát Thương Resonance Liberation.</t>
         </is>
       </c>
     </row>
@@ -29810,8 +29810,8 @@
       <c r="M437" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Resonance Liberation]&lt;/color&gt;
-Attack tăng thêm {0}.
-Trong trạng thái Resonance Liberation, Hộp Ma Pháp Nổ liên tục rơi bên cạnh Roccia và tấn công mục tiêu trong {2} giây, gây Havoc DMG bằng {1} Attack của Roccia, được tính là sát thương Heavy Attack.</t>
+ATK tăng thêm {0}.
+Trong trạng thái Resonance Liberation, Hộp Ma Pháp Nổ liên tục rơi bên cạnh Roccia và tấn công mục tiêu trong {2} giây, gây DMG Havoc bằng {1} ATK của Roccia, được tính là DMG Đòn ATK Mạnh.</t>
         </is>
       </c>
     </row>
@@ -29878,7 +29878,7 @@
       <c r="M438" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Resonance Liberation]&lt;/color&gt;
-Tấn Công được tăng lên. Trong trạng thái Resonance Liberation, Hộp Ma Pháp Nổ liên tục rơi xuống để tấn công mục tiêu.</t>
+ATK được tăng lên. Trong trạng thái Resonance Liberation, Hộp Ma Pháp Nổ liên tục rơi xuống để tấn công mục tiêu.</t>
         </is>
       </c>
     </row>
@@ -29946,8 +29946,8 @@
       <c r="M439" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Resonance Skill]&lt;/color&gt;
-Cooldown chiêu của Resonance Skill giảm xuống {0} giây, và phạm vi hút được mở rộng. Khi thi triển Resonance Skill, Roccia miễn nhiễm với gián đoạn và hồi phục thêm &lt;SapTag=1&gt;{1}&lt;/SapTag&gt; {Cus:Sap,S=điểm P=điểm SapTag=1} Trí Tưởng.
-Thi triển Heavy Attack và Resonance Skill sẽ tăng Attack của Roccia thêm {2} trong {3} giây.</t>
+Thời gian hồi chiêu của Resonance Skill giảm xuống {0} giây, và phạm vi hút được mở rộng. Khi thi triển Resonance Skill, Roccia miễn nhiễm với gián đoạn và hồi phục thêm &lt;SapTag=1&gt;{1}&lt;/SapTag&gt; {Cus:Sap,S=điểm P=điểm SapTag=1} Trí Tưởng.
+Thi triển Đòn ATK Mạnh và Resonance Skill sẽ tăng ATK của Roccia thêm {2} trong {3} giây.</t>
         </is>
       </c>
     </row>
@@ -30014,7 +30014,7 @@
       <c r="M440" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Resonance Skill]&lt;/color&gt;
-Resonance Skill được tăng cường đặc biệt. Thi triển Heavy Attack hoặc Resonance Skill sẽ tăng Attack.</t>
+Resonance Skill được tăng cường đặc biệt. Thi triển Đòn ATK Mạnh hoặc Resonance Skill sẽ tăng ATK.</t>
         </is>
       </c>
     </row>
@@ -30083,9 +30083,9 @@
       <c r="M441" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Basic Attack]&lt;/color&gt;
-Khi thi triển Basic Attack - Ảo Ảnh Chân Thực, Roccia miễn nhiễm với gián đoạn và nhận một Lớp Shield tương đương {0} HP tối đa của Roccia trong {1} giây.
-Hệ số sát thương của Stage 2 Ảo Ảnh Chân Thực tăng thêm {2}, phạm vi tấn công cũng được mở rộng.
-Hệ số sát thương của Stage 3 Ảo Ảnh Chân Thực tăng thêm {3}, phạm vi tấn công được mở rộng đáng kể.</t>
+Khi thi triển Basic Attack - Ảo Ảnh Chân Thực, Roccia miễn nhiễm với gián đoạn và nhận một Lớp Khiên tương đương {0} HP tối đa của Roccia trong {1} giây.
+Hệ số DMG của Giai Đoạn 2 Ảo Ảnh Chân Thực tăng thêm {2}, phạm vi tấn công cũng được mở rộng.
+Hệ số DMG của Giai Đoạn 3 Ảo Ảnh Chân Thực tăng thêm {3}, phạm vi tấn công được mở rộng đáng kể.</t>
         </is>
       </c>
     </row>
@@ -30152,7 +30152,7 @@
       <c r="M442" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Basic Attack]&lt;/color&gt;
-Basic Attack - Thật sự Fantasy nhận được những cải tiến đặc biệt.</t>
+Basic Attack - Real Fantasy nhận được những cải tiến đặc biệt.</t>
         </is>
       </c>
     </row>
@@ -30219,7 +30219,7 @@
       <c r="M443" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Basic Attack]&lt;/color&gt;
-Khi Basic Attack - Ảo Ảnh Thực trúng mục tiêu và Tưởng Tượng không dưới {0} điểm, sẽ tạo thêm một Quả Bom Pháo Hoa, gây Havoc DMG bằng {1} Attack của Roccia, được tính là Sát Thương Heavy Attack.</t>
+Khi Basic Attack - Ảo Ảnh Thực trúng mục tiêu và Tưởng Tượng không dưới {0} điểm, sẽ tạo thêm một Quả Bom Pháo Hoa, gây Sát Thương Havoc bằng {1} ATK của Roccia, được tính là Sát Thương Đòn Heavy Attack.</t>
         </is>
       </c>
     </row>
@@ -30286,7 +30286,7 @@
       <c r="M444" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Basic Attack]&lt;/color&gt;
-Sau khi sử dụng Basic Attack - Thật sự Fantasy, lần Thật sự Fantasy tiếp theo sẽ gây thêm sát thương diện rộng.</t>
+Sau khi sử dụng Basic Attack - Real Fantasy, lần Real Fantasy tiếp theo sẽ gây thêm sát thương diện rộng.</t>
         </is>
       </c>
     </row>
@@ -30355,9 +30355,9 @@
       <c r="M445" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Basic Attack]&lt;/color&gt;
-Roccia nhận thêm {0} Havoc DMG Bonus. Khi Roccia đang trên chiến trường và không ở trên không, hồi phục &lt;SapTag=1&gt;{1}&lt;/SapTag&gt; {Cus:Sap,S=điểm P=điểm SapTag=1} Tưởng Tượng mỗi giây.
-Khi lao về phía trước hoặc đánh trúng mục tiêu bằng Heavy Attack, Roccia miễn nhiễm với hiệu ứng gián đoạn.
-Khi Stage 4 Basic Attack, Heavy Attack và Basic Attack - Ảo Ảnh Thực gây sát thương, một Hộp Ma Pháp Đông Đặc sẽ được tạo ra để tấn công mục tiêu, gây Havoc DMG bằng {2} Attack của Roccia 4 lần, được tính là Sát Thương Heavy Attack.</t>
+Roccia nhận thêm {0} Tăng Sát Thương Havoc. Khi Roccia đang trên chiến trường và không ở trên không, hồi phục &lt;SapTag=1&gt;{1}&lt;/SapTag&gt; {Cus:Sap,S=điểm P=điểm SapTag=1} Tưởng Tượng mỗi giây.
+Khi lao về phía trước hoặc đánh trúng mục tiêu bằng Đòn Heavy Attack, Roccia miễn nhiễm với hiệu ứng gián đoạn.
+Khi Giai Đoạn 4 Basic Attack, Đòn Heavy Attack và Basic Attack - Ảo Ảnh Thực gây DMG, một Hộp Ma Pháp Đông Đặc sẽ được tạo ra để tấn công mục tiêu, gây Sát Thương Havoc bằng {2} ATK của Roccia 4 lần, được tính là Sát Thương Đòn Heavy Attack.</t>
         </is>
       </c>
     </row>
@@ -30426,9 +30426,9 @@
       <c r="M446" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Basic Attack]&lt;/color&gt;
-Nhận thêm Havoc DMG. Tự động hồi phục Forte Gauge khi Roccia đang ở trên mặt đất và không ở giữa không trung.
-Khi lao về phía trước hoặc đánh trúng mục tiêu bằng Heavy Attack, Roccia miễn nhiễm với gián đoạn.
-Một số đòn Basic Attack có thể tạo ra Condensed Magic Box để gây thêm sát thương.</t>
+Nhận thêm Sát Thương Havoc. Tự động hồi phục Forte Gauge khi Roccia đang ở trên mặt đất và không ở giữa không trung.
+Khi lao về phía trước hoặc đánh trúng mục tiêu bằng Đòn Heavy Attack, Roccia miễn nhiễm với gián đoạn.
+Một số đòn Basic Attack có thể tạo ra Condensed Magic Box để gây thêm DMG.</t>
         </is>
       </c>
     </row>
@@ -30496,8 +30496,8 @@
       <c r="M447" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Resonance Skill]&lt;/color&gt;
-Mỗi lần sử dụng Resonance Skill - Ảo Ảnh Lấp Lánh &lt;SapTag=0&gt;{0}&lt;/SapTag&gt; {Cus:Sap,S=lần P=lần SapTag=0}, lần thi triển Ảo Ảnh Lấp Lánh tiếp theo sẽ trở thành Ảo Ảnh Lấp Lánh Cường Hóa, gây sát thương Ảo Ảnh Lấp Lánh cộng thêm Havoc DMG bằng {2} Attack của Cantarella &lt;SapTag=1&gt;{1}&lt;/SapTag&gt; {Cus:Sap,S=lần P=lần SapTag=1}, sau đó tạo ra Dư Âm Thủy Triều &lt;SapTag=3&gt;{3}&lt;/SapTag&gt; {Cus:Sap,S=lần P=lần SapTag=3}, gây Havoc DMG bằng {4} Attack của Cantarella, được tính là sát thương Basic Attack.
-Khi hiệu ứng Giật Điện kích hoạt, Cooldown chiêu của Ảo Ảnh Lấp Lánh giảm {5} giây.</t>
+Mỗi lần sử dụng Resonance Skill - Ảo Ảnh Lấp Lánh &lt;SapTag=0&gt;{0}&lt;/SapTag&gt; {Cus:Sap,S=lần P=lần SapTag=0}, lần thi triển Ảo Ảnh Lấp Lánh tiếp theo sẽ trở thành Ảo Ảnh Lấp Lánh Cường Hóa, gây DMG Ảo Ảnh Lấp Lánh cộng thêm DMG Havoc bằng {2} ATK của Cantarella &lt;SapTag=1&gt;{1}&lt;/SapTag&gt; {Cus:Sap,S=lần P=lần SapTag=1}, sau đó tạo ra Dư Âm Thủy Triều &lt;SapTag=3&gt;{3}&lt;/SapTag&gt; {Cus:Sap,S=lần P=lần SapTag=3}, gây DMG Havoc bằng {4} ATK của Cantarella, được tính là DMG Đòn Basic Attack.
+Khi hiệu ứng Giật Điện kích hoạt, Thời gian hồi chiêu của Ảo Ảnh Lấp Lánh giảm {5} giây.</t>
         </is>
       </c>
     </row>
@@ -30632,8 +30632,8 @@
       <c r="M449" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Heavy Attack]&lt;/color&gt;
-Khi sử dụng Heavy Attack Delusive Dive để vào trạng thái Mirage, hồi phục thêm &lt;SapTag=0&gt;{0}&lt;/SapTag&gt; {Cus:Sap,S=điểm P=điểm SapTag=0} Trance và tạo ra Tidal Reverberation &lt;SapTag=1&gt;{1}&lt;/SapTag&gt; {Cus:Sap,S=lần P=lần SapTag=1}, gây Havoc DMG bằng {2} Attack của Cantarella, được tính là sát thương Basic Attack.
-Resonance Skill - Flickering Reverie và Forte Circuit - Perception Drain gây tổng sát thương cao hơn {3}, và Jolt gây tổng sát thương cao hơn {4}.</t>
+Khi sử dụng Heavy Attack Delusive Dive để vào trạng thái Mirage, hồi phục thêm &lt;SapTag=0&gt;{0}&lt;/SapTag&gt; {Cus:Sap,S=điểm P=điểm SapTag=0} Trance và tạo ra Tidal Reverberation &lt;SapTag=1&gt;{1}&lt;/SapTag&gt; {Cus:Sap,S=lần P=lần SapTag=1}, gây DMG Havoc bằng {2} ATK của Cantarella, được tính là DMG Basic Attack.
+Resonance Skill - Flickering Reverie và Forte Circuit - Perception Drain gây tổng DMG cao hơn {3}, và Jolt gây tổng DMG cao hơn {4}.</t>
         </is>
       </c>
     </row>
@@ -30773,10 +30773,10 @@
       <c r="M451" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Basic Attack]&lt;/color&gt;
-Đánh trúng mục tiêu bằng Basic Attack Phantom Sting Giai Đoạn {0} sẽ tạo ra Tidal Reverberation &lt;SapTag=1&gt;{1}&lt;/SapTag&gt; {Cus:Sap,S=lần P=lần SapTag=1}.
+Đánh trúng mục tiêu bằng Đòn Basic Attack Phantom Sting Giai Đoạn {0} sẽ tạo ra Tidal Reverberation &lt;SapTag=1&gt;{1}&lt;/SapTag&gt; {Cus:Sap,S=lần P=lần SapTag=1}.
 Khi tất cả Tidal Reverberation trúng mục tiêu, chúng sẽ gây hiệu ứng Daze và tạo ra Wavelet &lt;SapTag=2&gt;{2}&lt;/SapTag&gt; {Cus:Sap,S=lần P=lần SapTag=2} xung quanh mục tiêu bị trúng.
-- Daze: Movement Speed của mục tiêu bị giảm trong {3} giây. Khi mục tiêu nhận sát thương, Daze sẽ bị loại bỏ để kích hoạt Jolt một lần.
-- Wavelet gây Havoc DMG bằng {4} Attack của Cantarella khi trúng mục tiêu, được tính là Sát Thương Basic Attack.
+- Daze: Tốc Độ Di Chuyển của mục tiêu bị giảm trong {3} giây. Khi mục tiêu nhận DMG, Daze sẽ bị loại bỏ để kích hoạt Jolt một lần.
+- Wavelet gây Sát Thương Havoc bằng {4} ATK của Cantarella khi trúng mục tiêu, được tính là Sát Thương Basic Attack.
 - Tidal Reverberation có thể trúng tối đa {5} mục tiêu.</t>
         </is>
       </c>
@@ -30844,7 +30844,7 @@
       <c r="M452" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Basic Attack]&lt;/color&gt;
-Đánh trúng mục tiêu bằng Basic Attack 3 được tăng cường sẽ gây sát thương diện rộng, gây hiệu ứng Daze lên mục tiêu và kích hoạt Jolt ở lần gây sát thương tiếp theo.</t>
+Đánh trúng mục tiêu bằng Đòn Basic Attack 3 được tăng cường sẽ gây sát thương diện rộng, gây hiệu ứng Daze lên mục tiêu và kích hoạt Jolt ở lần gây sát thương tiếp theo.</t>
         </is>
       </c>
     </row>
@@ -30913,9 +30913,9 @@
       <c r="M453" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Forte Circuit]&lt;/color&gt;
-Cooldown chiêu của Forte Circuit - Hút Cảm Giác giảm {0}.
-Kích hoạt Hút Cảm Giác sẽ tạo ra Echo Thủy Triều &lt;SapTag=1&gt;{1}&lt;/SapTag&gt; {Cus:Sap,S=lần P=lần SapTag=1}, gây Havoc DMG bằng {2} Attack của Cantarella, được tính là Sát Thương Basic Attack.
-Kích hoạt Hút Cảm Giác sẽ kết thúc Mirage, hồi &lt;SapTag=3&gt;{3}&lt;/SapTag&gt; {Cus:Sap,S=điểm P=điểm SapTag=1} Trance và tái kích hoạt Mirage trong {4} giây.</t>
+Thời gian hồi chiêu của Forte Circuit - Hút Cảm Giác giảm {0}.
+Kích hoạt Hút Cảm Giác sẽ tạo ra Tiếng Vang Thủy Triều &lt;SapTag=1&gt;{1}&lt;/SapTag&gt; {Cus:Sap,S=lần P=lần SapTag=1}, gây Sát Thương Havoc bằng {2} ATK của Cantarella, được tính là Sát Thương Basic Attack.
+Kích hoạt Hút Cảm Giác sẽ kết thúc Ảo Ảnh, hồi &lt;SapTag=3&gt;{3}&lt;/SapTag&gt; {Cus:Sap,S=điểm P=điểm SapTag=1} Trance và tái kích hoạt Ảo Ảnh trong {4} giây.</t>
         </is>
       </c>
     </row>
@@ -31049,7 +31049,7 @@
       <c r="M455" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Resonance Liberation]&lt;/color&gt;
-Những Kẻ Dệt Giấc mộng được triệu hồi bởi Resonance Liberation - Dưới Biển sâu sẽ tạo thêm Hồi Âm Thủy Triều &lt;SapTag=1&gt;{1}&lt;/SapTag&gt; {Cus:Sap,S=lần P=lần SapTag=1} cho mỗi &lt;SapTag=0&gt;{0}&lt;/SapTag&gt; {Cus:Sap,S=lần P=lần SapTag=0} sát thương gây ra, gây Havoc DMG bằng {2} Attack của Cantarella, được tính là Sát Thương Basic Attack.</t>
+Những Kẻ Dệt Giấc mộng được triệu hồi bởi Resonance Liberation - Dưới Biển sâu sẽ tạo thêm Hồi Âm Thủy Triều &lt;SapTag=1&gt;{1}&lt;/SapTag&gt; {Cus:Sap,S=lần P=lần SapTag=1} cho mỗi &lt;SapTag=0&gt;{0}&lt;/SapTag&gt; {Cus:Sap,S=lần P=lần SapTag=0} DMG gây ra, gây Sát Thương Havoc bằng {2} ATK của Cantarella, được tính là Sát Thương Đòn Cơ Bản.</t>
         </is>
       </c>
     </row>
@@ -31182,8 +31182,8 @@
       </c>
       <c r="M457" t="inlineStr">
         <is>
-          <t>&lt;color=#c49e55&gt;[Forte Circuit]&lt;/color&gt; Sử dụng Heavy Attack - Khúc Kết Đỏ Thẫm tăng Crit. Rate {0} và Crit. DMG {1} trong {2} giây.
-Sát Thương gây ra bởi Basic Attack - Vận Mệnh và Kết Cục cùng Resonance Skill - Lời Thì Thầm Trong Giấc Mộng Kinh Hoàng sẽ được khuếch đại {3}.</t>
+          <t>&lt;color=#c49e55&gt;[Forte Circuit]&lt;/color&gt; Sử dụng Đòn Heavy Attack - Khúc Kết Đỏ Thẫm tăng Crit. Rate {0} và Crit. DMG {1} trong {2} giây.
+Sát Thương gây ra bởi Đòn Basic Attack - Vận Mệnh và Kết Cục cùng Resonance Skill - Lời Thì Thầm Trong Giấc Mộng Kinh Hoàng sẽ được khuếch đại {3}.</t>
         </is>
       </c>
     </row>
@@ -31249,8 +31249,8 @@
       </c>
       <c r="M458" t="inlineStr">
         <is>
-          <t>&lt;color=#c49e55&gt;[Forte Circuit]&lt;/color&gt; Sử dụng Heavy Attack - Khúc Kết Đỏ Thẫm sẽ kích hoạt hiệu ứng tăng cường.
-Sát Thương gây ra bởi Basic Attack - Vận Mệnh và Kết Cục cùng Resonance Skill - Lời Thì Thầm Trong Giấc Mộng Kinh Hoàng sẽ được tăng lên.</t>
+          <t>&lt;color=#c49e55&gt;[Forte Circuit]&lt;/color&gt; Sử dụng Đòn Heavy Attack - Khúc Kết Đỏ Thẫm sẽ kích hoạt hiệu ứng tăng cường.
+Sát Thương gây ra bởi Đòn Basic Attack - Vận Mệnh và Kết Cục cùng Resonance Skill - Lời Thì Thầm Trong Giấc Mộng Kinh Hoàng sẽ được tăng lên.</t>
         </is>
       </c>
     </row>
@@ -31316,8 +31316,8 @@
       </c>
       <c r="M459" t="inlineStr">
         <is>
-          <t>&lt;color=#c49e55&gt;[Forte Circuit]&lt;/color&gt; Khi sử dụng Basic Attack Stage 3 hoặc Resonance Skill - Lời Thì Thầm Trong Giấc Mộng Phù Du, chuyển sang trạng thái Lời Thì Thầm. Basic Attack Thay Thế - Vận Mệnh và Kết Cục cùng Resonance Skill Thay Thế - Lời Thì Thầm Trong Giấc Mộng Kinh Hoàng sẽ khả dụng trong {0} giây.
-Basic Attack - Vận Mệnh và Kết Cục cùng Resonance Skill - Lời Thì Thầm Trong Giấc Mộng Kinh Hoàng gây thêm Havoc DMG bằng {1} Attack của Phrolova.</t>
+          <t>&lt;color=#c49e55&gt;[Forte Circuit]&lt;/color&gt; Khi sử dụng Basic Attack Giai Đoạn 3 hoặc Resonance Skill - Lời Thì Thầm Trong Giấc Mộng Phù Du, chuyển sang trạng thái Lời Thì Thầm. Đòn Basic Attack Thay Thế - Vận Mệnh và Kết Cục cùng Resonance Skill Thay Thế - Lời Thì Thầm Trong Giấc Mộng Kinh Hoàng sẽ khả dụng trong {0} giây.
+Đòn Basic Attack - Vận Mệnh và Kết Cục cùng Resonance Skill - Lời Thì Thầm Trong Giấc Mộng Kinh Hoàng gây thêm Sát Thương Havoc bằng {1} ATK của Phrolova.</t>
         </is>
       </c>
     </row>
@@ -31383,8 +31383,8 @@
       </c>
       <c r="M460" t="inlineStr">
         <is>
-          <t>&lt;color=#c49e55&gt;[Forte Circuit]&lt;/color&gt; Phrolova bước vào trạng thái Tiếng Thì Thầm. Kỹ Năng Basic Thay Thế - Vận Mệnh và Kết Cục cùng Resonance Skill Thay Thế - Tiếng Thì Thầm Trong Giấc Mơ Kinh Hoàng được kích hoạt.
-Kỹ Năng Basic - Vận Mệnh và Kết Cục cùng Resonance Skill - Tiếng Thì Thầm Trong Giấc Mơ Kinh Hoàng gây thêm sát thương.</t>
+          <t>&lt;color=#c49e55&gt;[Forte Circuit]&lt;/color&gt; Phrolova bước vào trạng thái Tiếng Thì Thầm. Kỹ Năng Cơ Bản Thay Thế - Vận Mệnh và Kết Cục cùng Resonance Skill Thay Thế - Tiếng Thì Thầm Trong Giấc Mơ Kinh Hoàng được kích hoạt.
+Kỹ Năng Cơ Bản - Vận Mệnh và Kết Cục cùng Resonance Skill - Tiếng Thì Thầm Trong Giấc Mơ Kinh Hoàng gây thêm sát thương.</t>
         </is>
       </c>
     </row>
@@ -31449,7 +31449,7 @@
       </c>
       <c r="M461" t="inlineStr">
         <is>
-          <t>&lt;color=#c49e55&gt;[Special Enhancement]&lt;/color&gt; Khi không ở trạng thái Maestro, các kỹ năng của Phrolova sẽ triệu hồi thêm xích gây Havoc DMG bằng {0} Tấn Công của cô khi trúng mục tiêu, được tính là Sát Thương Kỹ Năng Echo, sau đó ngẫu nhiên nhận 1 Volatile Ghi chú - Strings hoặc Volatile Ghi chú - Winds. Hiệu ứng này có thể kích hoạt mỗi {1} giây một lần.</t>
+          <t>&lt;color=#c49e55&gt;[Tăng Cường Đặc Biệt]&lt;/color&gt; Khi không ở trạng thái Maestro, các kỹ năng của Phrolova sẽ triệu hồi thêm xích gây Sát Thương Havoc bằng {0} ATK của cô khi trúng mục tiêu, được tính là Sát Thương Kỹ Năng Echo, sau đó ngẫu nhiên nhận 1 Volatile Note - Strings hoặc Volatile Note - Winds. Hiệu ứng này có thể kích hoạt mỗi {1} giây một lần.</t>
         </is>
       </c>
     </row>
@@ -31514,7 +31514,7 @@
       </c>
       <c r="M462" t="inlineStr">
         <is>
-          <t>&lt;color=#c49e55&gt;[Special Enhancement]&lt;/color&gt; Khi không ở trạng thái Maestro, các kỹ năng của Phrolova sẽ triệu hồi thêm xích khi trúng mục tiêu để gây sát thương bổ sung, sau đó nhận ngẫu nhiên 1 Volatile Ghi chú.</t>
+          <t>&lt;color=#c49e55&gt;[Tăng Cường Đặc Biệt]&lt;/color&gt; Khi không ở trạng thái Maestro, các kỹ năng của Phrolova sẽ triệu hồi thêm xích khi trúng mục tiêu để gây sát thương bổ sung, sau đó nhận ngẫu nhiên 1 Volatile Note.</t>
         </is>
       </c>
     </row>
@@ -31579,7 +31579,7 @@
       </c>
       <c r="M463" t="inlineStr">
         <is>
-          <t>&lt;color=#c49e55&gt;[Resonance Liberation]&lt;/color&gt; Khi ở trạng thái Maestro, Attack của Phrolova tăng {0}. Giai đoạn 1 và 2 của Basic Attack - Hecate gây thêm Havoc DMG bằng {1} Attack của Phrolova. Attack Nâng Cao - Hecate gây thêm Havoc DMG bằng {2} Attack của Phrolova.</t>
+          <t>&lt;color=#c49e55&gt;[Resonance Liberation]&lt;/color&gt; Khi ở trạng thái Maestro, ATK của Phrolova tăng {0}. Giai đoạn 1 và 2 của Basic Attack - Hecate gây thêm Sát Thương Havoc bằng {1} ATK của Phrolova. ATK Nâng Cao - Hecate gây thêm Sát Thương Havoc bằng {2} ATK của Phrolova.</t>
         </is>
       </c>
     </row>
@@ -31644,7 +31644,7 @@
       </c>
       <c r="M464" t="inlineStr">
         <is>
-          <t>&lt;color=#c49e55&gt;[Resonance Liberation]&lt;/color&gt; Khi ở trạng thái Maestro, Attack của Phrolova được tăng cường. Giai đoạn 1 và 2 của Basic Attack - Hecate, cùng Attack Nâng Cao - Hecate gây thêm sát thương.</t>
+          <t>&lt;color=#c49e55&gt;[Resonance Liberation]&lt;/color&gt; Khi ở trạng thái Maestro, ATK của Phrolova được tăng cường. Giai đoạn 1 và 2 của Basic Attack - Hecate, cùng ATK Nâng Cao - Hecate gây thêm sát thương.</t>
         </is>
       </c>
     </row>
@@ -31709,7 +31709,7 @@
       </c>
       <c r="M465" t="inlineStr">
         <is>
-          <t>&lt;color=#c49e55&gt;[Forte Circuit]&lt;/color&gt; Basic Attack - Vận Mệnh và Kết Cục cùng Resonance Skill - Lời Thì Thầm giảm Havoc RES của mục tiêu {0} khi trúng đích, tối đa {2} lần, hiệu ứng kéo dài {1} giây.</t>
+          <t>&lt;color=#c49e55&gt;[Forte Circuit]&lt;/color&gt; Đòn Basic Attack - Vận Mệnh và Kết Cục cùng Resonance Skill - Lời Thì Thầm giảm Kháng Havoc của mục tiêu {0} khi trúng đích, tối đa {2} lần, hiệu ứng kéo dài {1} giây.</t>
         </is>
       </c>
     </row>
@@ -31774,7 +31774,7 @@
       </c>
       <c r="M466" t="inlineStr">
         <is>
-          <t>&lt;color=#c49e55&gt;[Forte Circuit]&lt;/color&gt; Basic Attack - Vận Mệnh và Kết Cục cùng Resonance Skill - Lời Thì Thầm giảm Havoc RES của mục tiêu khi trúng đích.</t>
+          <t>&lt;color=#c49e55&gt;[Forte Circuit]&lt;/color&gt; Đòn Basic Attack - Vận Mệnh và Kết Cục cùng Resonance Skill - Lời Thì Thầm giảm Kháng Havoc của mục tiêu khi trúng đích.</t>
         </is>
       </c>
     </row>
@@ -31839,7 +31839,7 @@
       </c>
       <c r="M467" t="inlineStr">
         <is>
-          <t>Sát thương Skill Echo tăng thêm 22,5%.</t>
+          <t>DMG Kỹ năng Echo tăng thêm 22,5%.</t>
         </is>
       </c>
     </row>
@@ -31904,7 +31904,7 @@
       </c>
       <c r="M468" t="inlineStr">
         <is>
-          <t>DMG của Echo Skill tăng nhẹ.</t>
+          <t>DMG Kỹ năng Echo tăng nhẹ.</t>
         </is>
       </c>
     </row>
@@ -31969,7 +31969,7 @@
       </c>
       <c r="M469" t="inlineStr">
         <is>
-          <t>Sát thương Skill Echo tăng thêm 45%.</t>
+          <t>DMG Kỹ năng Echo tăng thêm 45%.</t>
         </is>
       </c>
     </row>
@@ -32034,7 +32034,7 @@
       </c>
       <c r="M470" t="inlineStr">
         <is>
-          <t>DMG của Echo Skill tăng vừa.</t>
+          <t>DMG Kỹ năng Echo tăng vừa phải.</t>
         </is>
       </c>
     </row>
@@ -32099,7 +32099,7 @@
       </c>
       <c r="M471" t="inlineStr">
         <is>
-          <t>Sát thương Skill Echo tăng thêm 67,5%.</t>
+          <t>DMG Kỹ năng Echo tăng thêm 67,5%.</t>
         </is>
       </c>
     </row>
@@ -32164,7 +32164,7 @@
       </c>
       <c r="M472" t="inlineStr">
         <is>
-          <t>DMG của Echo Skill tăng mạnh.</t>
+          <t>Sát Thương Kỹ Năng Âm Hưởng Tăng Mạnh</t>
         </is>
       </c>
     </row>
@@ -32229,7 +32229,7 @@
       </c>
       <c r="M473" t="inlineStr">
         <is>
-          <t>Tất cả Resonators trong đội miễn nhiễm với gián đoạn và mọi loại Sát Thương gây ra được tăng thêm 22,5%.</t>
+          <t>Tất cả Resonator trong đội miễn nhiễm với gián đoạn và mọi loại Sát Thương gây ra được tăng thêm 22,5%.</t>
         </is>
       </c>
     </row>
@@ -32294,7 +32294,7 @@
       </c>
       <c r="M474" t="inlineStr">
         <is>
-          <t>Tất cả Resonators trong đội miễn nhiễm với gián đoạn và gây thêm Sát Thương.</t>
+          <t>Tất cả Resonator trong đội miễn nhiễm với gián đoạn và gây thêm Sát Thương.</t>
         </is>
       </c>
     </row>
@@ -32359,7 +32359,7 @@
       </c>
       <c r="M475" t="inlineStr">
         <is>
-          <t>Khi bước vào [Divined Dream], HP của tất cả Resonators trong đội sẽ giảm xuống còn 1 và nhận một Lớp Shield tương đương 100% HP tối đa.</t>
+          <t>Khi bước vào [Giấc Mộng Tiên Tri], HP của tất cả Resonator trong đội sẽ giảm xuống còn 1 và nhận một Lớp Khiên tương đương 100% HP tối đa.</t>
         </is>
       </c>
     </row>
@@ -32489,7 +32489,7 @@
       </c>
       <c r="M477" t="inlineStr">
         <is>
-          <t>Gây sát thương trong trạng thái [Divined Dream] sẽ kéo dài thời gian hiệu lực thêm 1 giây.</t>
+          <t>Gây sát thương trong trạng thái [Giấc Mộng Tiên Tri] sẽ kéo dài thời gian hiệu lực thêm 1 giây.</t>
         </is>
       </c>
     </row>
@@ -32554,7 +32554,7 @@
       </c>
       <c r="M478" t="inlineStr">
         <is>
-          <t>Gây sát thương trong trạng thái [Divined Dream] sẽ kéo dài thời gian hiệu lực.</t>
+          <t>Gây sát thương trong trạng thái [Giấc Mộng Tiên Tri] sẽ kéo dài thời gian hiệu lực.</t>
         </is>
       </c>
     </row>
@@ -32749,7 +32749,7 @@
       </c>
       <c r="M481" t="inlineStr">
         <is>
-          <t>Khi [Sigil] gây sát thương, nó tăng 2.5% Sát thương cho tất cả Resonators trong đội trong 1 giây, tối đa 100 tầng. Tất cả tầng sẽ mất khi thời gian kết thúc.</t>
+          <t>Khi [Sigil] gây DMG, nó tăng 2.5% DMG cho tất cả Resonator trong đội trong 1 giây, tối đa 100 tầng. Tất cả tầng sẽ mất khi thời gian kết thúc.</t>
         </is>
       </c>
     </row>
@@ -32814,7 +32814,7 @@
       </c>
       <c r="M482" t="inlineStr">
         <is>
-          <t>Khi [Sigil] gây sát thương, tất cả Resonators trong đội gây thêm sát thương. Có thể cộng dồn.</t>
+          <t>Khi [Sigil] gây DMG, tất cả Resonator trong đội gây thêm DMG. Có thể cộng dồn.</t>
         </is>
       </c>
     </row>
@@ -33009,7 +33009,7 @@
       </c>
       <c r="M485" t="inlineStr">
         <is>
-          <t>Thời gian kích hoạt Huy hiệu kéo dài 25%, nhưng tất cả Resonators trong đội nhận thêm 60% Tăng Sát Thương.</t>
+          <t>Thời gian kích hoạt Huy hiệu kéo dài 25%, nhưng tất cả Resonator trong đội nhận thêm 60% Tăng Sát Thương.</t>
         </is>
       </c>
     </row>
@@ -33074,7 +33074,7 @@
       </c>
       <c r="M486" t="inlineStr">
         <is>
-          <t>Thời gian kích hoạt Huy hiệu kéo dài, nhưng tất cả Resonators trong đội nhận Tăng Sát Thương.</t>
+          <t>Thời gian kích hoạt Huy hiệu kéo dài, nhưng tất cả Resonator trong đội nhận Tăng Sát Thương.</t>
         </is>
       </c>
     </row>
@@ -33269,7 +33269,7 @@
       </c>
       <c r="M489" t="inlineStr">
         <is>
-          <t>Increase Hiệu Ứng Phá Nhịp lên 40.</t>
+          <t>Tăng Hiệu Ứng Phá Nhịp lên 40.</t>
         </is>
       </c>
     </row>
@@ -33334,7 +33334,7 @@
       </c>
       <c r="M490" t="inlineStr">
         <is>
-          <t>Increase Hiệu Ứng Phá Nhịp lên 80.</t>
+          <t>Tăng Hiệu Ứng Phá Nhịp lên 80.</t>
         </is>
       </c>
     </row>
@@ -33399,7 +33399,7 @@
       </c>
       <c r="M491" t="inlineStr">
         <is>
-          <t>Increase Hiệu Ứng Phá Nhịp lên 120.</t>
+          <t>Tăng Hiệu Ứng Phá Nhịp lên 120.</t>
         </is>
       </c>
     </row>
@@ -33464,7 +33464,7 @@
       </c>
       <c r="M492" t="inlineStr">
         <is>
-          <t>Increase tốc độ tích lũy Off-Tune lên 40%.</t>
+          <t>Tăng tốc độ tích lũy Off-Tune lên 40%.</t>
         </is>
       </c>
     </row>
@@ -33529,7 +33529,7 @@
       </c>
       <c r="M493" t="inlineStr">
         <is>
-          <t>Increase tốc độ tích lũy Off-Tune lên 80%.</t>
+          <t>Tăng tốc độ tích lũy Off-Tune lên 80%.</t>
         </is>
       </c>
     </row>
@@ -33594,7 +33594,7 @@
       </c>
       <c r="M494" t="inlineStr">
         <is>
-          <t>Increase tốc độ tích lũy Off-Tune lên 120%.</t>
+          <t>Tăng tốc độ tích lũy Off-Tune lên 120%.</t>
         </is>
       </c>
     </row>
@@ -33659,7 +33659,7 @@
       </c>
       <c r="M495" t="inlineStr">
         <is>
-          <t>Sau khi gây Sát Thương Vỡ Nhạc, Resonators trong đội sẽ bỏ qua 5% Kháng của mục tiêu đối với tất cả thuộc tính khi gây sát thương trong 10s, có thể chồng chất lên đến 10 lần. Tất cả hiệu ứng chồng chất sẽ biến mất khi thời gian kết thúc.</t>
+          <t>Sau khi gây Sát Thương Vỡ Nhạc, Resonator trong đội sẽ bỏ qua 5% Kháng của mục tiêu đối với tất cả thuộc tính khi gây DMG trong 10s, có thể chồng chất lên đến 10 lần. Tất cả hiệu ứng chồng chất sẽ biến mất khi thời gian kết thúc.</t>
         </is>
       </c>
     </row>
@@ -33724,7 +33724,7 @@
       </c>
       <c r="M496" t="inlineStr">
         <is>
-          <t>Sau khi gây Sát Thương Vỡ Nhạc, Resonators trong đội sẽ bỏ qua Kháng của mục tiêu đối với tất cả thuộc tính khi gây sát thương.</t>
+          <t>Sau khi gây Sát Thương Vỡ Nhạc, Resonator trong đội sẽ bỏ qua Kháng của mục tiêu đối với tất cả thuộc tính khi gây DMG.</t>
         </is>
       </c>
     </row>
@@ -33789,7 +33789,7 @@
       </c>
       <c r="M497" t="inlineStr">
         <is>
-          <t>Khi Resonator gây sát thương lên kẻ địch bị Tác Động Nhịp - Giao Thoa, mỗi tầng Tác Động Nhịp - Giao Thoa làm tăng Crit. DMG của đòn tấn công này thêm 30%, tối đa 120%.</t>
+          <t>Khi Resonator gây DMG lên kẻ địch bị Tác Động Nhịp - Giao Thoa, mỗi tầng Tác Động Nhịp - Giao Thoa làm tăng Crit. DMG của đòn tấn công này thêm 30%, tối đa 120%.</t>
         </is>
       </c>
     </row>
@@ -33854,7 +33854,7 @@
       </c>
       <c r="M498" t="inlineStr">
         <is>
-          <t>Tăng sát thương gây ra cho kẻ địch đang chịu hiệu ứng Giai Tune Căng Thẳng - Nhiễu Loạn.</t>
+          <t>Tăng sát thương gây ra cho kẻ địch đang chịu hiệu ứng Giai Điệu Căng Thẳng - Nhiễu Loạn.</t>
         </is>
       </c>
     </row>
@@ -33984,7 +33984,7 @@
       </c>
       <c r="M500" t="inlineStr">
         <is>
-          <t>Resonator nhận Tăng Cường Đột Tune Break Số dựa trên tỷ lệ tích lũy Mất Tần Số.</t>
+          <t>Resonator nhận Tăng Cường Đột Phá Tần Số dựa trên tỷ lệ tích lũy Mất Tần Số.</t>
         </is>
       </c>
     </row>
@@ -34049,7 +34049,7 @@
       </c>
       <c r="M501" t="inlineStr">
         <is>
-          <t>Khi ở trong [Divined Dream], mọi mục tiêu xung quanh sẽ bị ảnh hưởng bởi Tune Rupture - Interfered mỗi giây. Hiệu ứng này cũng được kích hoạt ngay khi bước vào [Divined Dream].</t>
+          <t>Khi ở trong [Giấc Mộng Tiên Tri], mọi mục tiêu xung quanh sẽ bị ảnh hưởng bởi Tune Rupture - Interfered mỗi giây. Hiệu ứng này cũng được kích hoạt ngay khi bước vào [Giấc Mộng Tiên Tri].</t>
         </is>
       </c>
     </row>
